--- a/TrackingList.xlsx
+++ b/TrackingList.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="台灣股票" sheetId="1" r:id="rId1"/>
@@ -663,569 +663,587 @@
     <t>00636</t>
   </si>
   <si>
+    <t>00632R</t>
+  </si>
+  <si>
+    <t>00633L</t>
+  </si>
+  <si>
+    <t>00635U</t>
+  </si>
+  <si>
+    <t>00637L</t>
+  </si>
+  <si>
+    <t>00640L</t>
+  </si>
+  <si>
+    <t>00642U</t>
+  </si>
+  <si>
+    <t>00650L</t>
+  </si>
+  <si>
+    <t>00655L</t>
+  </si>
+  <si>
+    <t>00663L</t>
+  </si>
+  <si>
+    <t>00664R</t>
+  </si>
+  <si>
+    <t>00665L</t>
+  </si>
+  <si>
+    <t>00669R</t>
+  </si>
+  <si>
+    <t>00670L</t>
+  </si>
+  <si>
+    <t>00671R</t>
+  </si>
+  <si>
+    <t>00673R</t>
+  </si>
+  <si>
+    <t>00674R</t>
+  </si>
+  <si>
+    <t>00675L</t>
+  </si>
+  <si>
+    <t>00676R</t>
+  </si>
+  <si>
+    <t>00680L</t>
+  </si>
+  <si>
+    <t>00685L</t>
+  </si>
+  <si>
+    <t>00688L</t>
+  </si>
+  <si>
+    <t>00693U</t>
+  </si>
+  <si>
+    <t>00706L</t>
+  </si>
+  <si>
+    <t>00708L</t>
+  </si>
+  <si>
+    <t>00710B</t>
+  </si>
+  <si>
+    <t>00711B</t>
+  </si>
+  <si>
+    <t>00715L</t>
+  </si>
+  <si>
+    <t>00738U</t>
+  </si>
+  <si>
+    <t>00753L</t>
+  </si>
+  <si>
+    <t>00763U</t>
+  </si>
+  <si>
+    <t>00775B</t>
+  </si>
+  <si>
+    <t>00865B</t>
+  </si>
+  <si>
+    <t>00945B</t>
+  </si>
+  <si>
+    <t>00953B</t>
+  </si>
+  <si>
+    <t>00985B</t>
+  </si>
+  <si>
+    <t>00639</t>
+  </si>
+  <si>
+    <t>00643</t>
+  </si>
+  <si>
+    <t>00645</t>
+  </si>
+  <si>
+    <t>00646</t>
+  </si>
+  <si>
+    <t>00652</t>
+  </si>
+  <si>
+    <t>00661</t>
+  </si>
+  <si>
+    <t>00662</t>
+  </si>
+  <si>
+    <t>00690</t>
+  </si>
+  <si>
+    <t>00692</t>
+  </si>
+  <si>
+    <t>00701</t>
+  </si>
+  <si>
+    <t>00712</t>
+  </si>
+  <si>
+    <t>00713</t>
+  </si>
+  <si>
+    <t>00717</t>
+  </si>
+  <si>
+    <t>00728</t>
+  </si>
+  <si>
+    <t>00730</t>
+  </si>
+  <si>
+    <t>00731</t>
+  </si>
+  <si>
+    <t>00733</t>
+  </si>
+  <si>
+    <t>00735</t>
+  </si>
+  <si>
+    <t>00752</t>
+  </si>
+  <si>
+    <t>00757</t>
+  </si>
+  <si>
+    <t>00762</t>
+  </si>
+  <si>
+    <t>00770</t>
+  </si>
+  <si>
+    <t>00830</t>
+  </si>
+  <si>
+    <t>00850</t>
+  </si>
+  <si>
+    <t>00861</t>
+  </si>
+  <si>
+    <t>00876</t>
+  </si>
+  <si>
+    <t>00878</t>
+  </si>
+  <si>
+    <t>00881</t>
+  </si>
+  <si>
+    <t>00882</t>
+  </si>
+  <si>
+    <t>00885</t>
+  </si>
+  <si>
+    <t>00888</t>
+  </si>
+  <si>
+    <t>00891</t>
+  </si>
+  <si>
+    <t>00892</t>
+  </si>
+  <si>
+    <t>00893</t>
+  </si>
+  <si>
+    <t>00894</t>
+  </si>
+  <si>
+    <t>00895</t>
+  </si>
+  <si>
+    <t>00896</t>
+  </si>
+  <si>
+    <t>00897</t>
+  </si>
+  <si>
+    <t>00898</t>
+  </si>
+  <si>
+    <t>00900</t>
+  </si>
+  <si>
+    <t>00901</t>
+  </si>
+  <si>
+    <t>00902</t>
+  </si>
+  <si>
+    <t>00903</t>
+  </si>
+  <si>
+    <t>00904</t>
+  </si>
+  <si>
+    <t>00905</t>
+  </si>
+  <si>
+    <t>00907</t>
+  </si>
+  <si>
+    <t>00909</t>
+  </si>
+  <si>
+    <t>00910</t>
+  </si>
+  <si>
+    <t>00912</t>
+  </si>
+  <si>
+    <t>00915</t>
+  </si>
+  <si>
+    <t>00916</t>
+  </si>
+  <si>
+    <t>00917</t>
+  </si>
+  <si>
+    <t>00918</t>
+  </si>
+  <si>
+    <t>00919</t>
+  </si>
+  <si>
+    <t>00921</t>
+  </si>
+  <si>
+    <t>00922</t>
+  </si>
+  <si>
+    <t>00923</t>
+  </si>
+  <si>
+    <t>00924</t>
+  </si>
+  <si>
+    <t>00926</t>
+  </si>
+  <si>
+    <t>00927</t>
+  </si>
+  <si>
+    <t>00928</t>
+  </si>
+  <si>
+    <t>00929</t>
+  </si>
+  <si>
+    <t>00930</t>
+  </si>
+  <si>
+    <t>00932</t>
+  </si>
+  <si>
+    <t>00934</t>
+  </si>
+  <si>
+    <t>00935</t>
+  </si>
+  <si>
+    <t>00936</t>
+  </si>
+  <si>
+    <t>00938</t>
+  </si>
+  <si>
+    <t>00939</t>
+  </si>
+  <si>
+    <t>00940</t>
+  </si>
+  <si>
+    <t>00941</t>
+  </si>
+  <si>
+    <t>00944</t>
+  </si>
+  <si>
+    <t>00946</t>
+  </si>
+  <si>
+    <t>00947</t>
+  </si>
+  <si>
+    <t>00949</t>
+  </si>
+  <si>
+    <t>00951</t>
+  </si>
+  <si>
+    <t>00952</t>
+  </si>
+  <si>
+    <t>00954</t>
+  </si>
+  <si>
+    <t>00960</t>
+  </si>
+  <si>
+    <t>00961</t>
+  </si>
+  <si>
+    <t>00963</t>
+  </si>
+  <si>
+    <t>00965</t>
+  </si>
+  <si>
+    <t>00971</t>
+  </si>
+  <si>
+    <t>PHYS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FCX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CRWD</t>
+  </si>
+  <si>
+    <t>PANW</t>
+  </si>
+  <si>
+    <t>LUNC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RENDER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TCEHY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BABA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZH</t>
+  </si>
+  <si>
+    <t>JKS</t>
+  </si>
+  <si>
+    <t>BIDU</t>
+  </si>
+  <si>
+    <t>WB</t>
+  </si>
+  <si>
+    <t>SVA</t>
+  </si>
+  <si>
+    <t>JD</t>
+  </si>
+  <si>
+    <t>NOAH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PDD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NTES</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BILI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CSIQ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DQ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LNVGY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CBAT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LU</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VNET</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GDS</t>
+  </si>
+  <si>
+    <t>PAYP</t>
+  </si>
+  <si>
+    <t>TM</t>
+  </si>
+  <si>
+    <t>HMC</t>
+  </si>
+  <si>
+    <t>NSANY</t>
+  </si>
+  <si>
+    <t>SONY</t>
+  </si>
+  <si>
+    <t>LSRCY</t>
+  </si>
+  <si>
+    <t>MUFG</t>
+  </si>
+  <si>
+    <t>NTTYY</t>
+  </si>
+  <si>
+    <t>SMFG</t>
+  </si>
+  <si>
+    <t>ITOCY</t>
+  </si>
+  <si>
+    <t>ASML</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SAP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ADD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>202605 TOP30</t>
+  </si>
+  <si>
+    <t>202605 TOP30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>202605 S&amp;P100</t>
+  </si>
+  <si>
+    <t>202605 S&amp;P100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26/05 Taiwan 50</t>
+  </si>
+  <si>
+    <t>26/05 Taiwan 50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>00631L</t>
-  </si>
-  <si>
-    <t>00632R</t>
-  </si>
-  <si>
-    <t>00633L</t>
-  </si>
-  <si>
-    <t>00635U</t>
-  </si>
-  <si>
-    <t>00637L</t>
-  </si>
-  <si>
-    <t>00640L</t>
-  </si>
-  <si>
-    <t>00642U</t>
-  </si>
-  <si>
-    <t>00650L</t>
-  </si>
-  <si>
-    <t>00655L</t>
-  </si>
-  <si>
-    <t>00663L</t>
-  </si>
-  <si>
-    <t>00664R</t>
-  </si>
-  <si>
-    <t>00665L</t>
-  </si>
-  <si>
-    <t>00669R</t>
-  </si>
-  <si>
-    <t>00670L</t>
-  </si>
-  <si>
-    <t>00671R</t>
-  </si>
-  <si>
-    <t>00673R</t>
-  </si>
-  <si>
-    <t>00674R</t>
-  </si>
-  <si>
-    <t>00675L</t>
-  </si>
-  <si>
-    <t>00676R</t>
-  </si>
-  <si>
-    <t>00680L</t>
-  </si>
-  <si>
-    <t>00685L</t>
-  </si>
-  <si>
-    <t>00688L</t>
-  </si>
-  <si>
-    <t>00693U</t>
-  </si>
-  <si>
-    <t>00706L</t>
-  </si>
-  <si>
-    <t>00708L</t>
-  </si>
-  <si>
-    <t>00710B</t>
-  </si>
-  <si>
-    <t>00711B</t>
-  </si>
-  <si>
-    <t>00715L</t>
-  </si>
-  <si>
-    <t>00738U</t>
-  </si>
-  <si>
-    <t>00753L</t>
-  </si>
-  <si>
-    <t>00763U</t>
-  </si>
-  <si>
-    <t>00775B</t>
-  </si>
-  <si>
-    <t>00865B</t>
-  </si>
-  <si>
-    <t>00945B</t>
-  </si>
-  <si>
-    <t>00953B</t>
-  </si>
-  <si>
-    <t>00985B</t>
-  </si>
-  <si>
-    <t>00639</t>
-  </si>
-  <si>
-    <t>00643</t>
-  </si>
-  <si>
-    <t>00645</t>
-  </si>
-  <si>
-    <t>00646</t>
-  </si>
-  <si>
-    <t>00652</t>
-  </si>
-  <si>
-    <t>00661</t>
-  </si>
-  <si>
-    <t>00662</t>
-  </si>
-  <si>
-    <t>00690</t>
-  </si>
-  <si>
-    <t>00692</t>
-  </si>
-  <si>
-    <t>00701</t>
-  </si>
-  <si>
-    <t>00712</t>
-  </si>
-  <si>
-    <t>00713</t>
-  </si>
-  <si>
-    <t>00717</t>
-  </si>
-  <si>
-    <t>00728</t>
-  </si>
-  <si>
-    <t>00730</t>
-  </si>
-  <si>
-    <t>00731</t>
-  </si>
-  <si>
-    <t>00733</t>
-  </si>
-  <si>
-    <t>00735</t>
-  </si>
-  <si>
-    <t>00752</t>
-  </si>
-  <si>
-    <t>00757</t>
-  </si>
-  <si>
-    <t>00762</t>
-  </si>
-  <si>
-    <t>00770</t>
-  </si>
-  <si>
-    <t>00830</t>
-  </si>
-  <si>
-    <t>00850</t>
-  </si>
-  <si>
-    <t>00861</t>
-  </si>
-  <si>
-    <t>00876</t>
-  </si>
-  <si>
-    <t>00878</t>
-  </si>
-  <si>
-    <t>00881</t>
-  </si>
-  <si>
-    <t>00882</t>
-  </si>
-  <si>
-    <t>00885</t>
-  </si>
-  <si>
-    <t>00888</t>
-  </si>
-  <si>
-    <t>00891</t>
-  </si>
-  <si>
-    <t>00892</t>
-  </si>
-  <si>
-    <t>00893</t>
-  </si>
-  <si>
-    <t>00894</t>
-  </si>
-  <si>
-    <t>00895</t>
-  </si>
-  <si>
-    <t>00896</t>
-  </si>
-  <si>
-    <t>00897</t>
-  </si>
-  <si>
-    <t>00898</t>
-  </si>
-  <si>
-    <t>00900</t>
-  </si>
-  <si>
-    <t>00901</t>
-  </si>
-  <si>
-    <t>00902</t>
-  </si>
-  <si>
-    <t>00903</t>
-  </si>
-  <si>
-    <t>00904</t>
-  </si>
-  <si>
-    <t>00905</t>
-  </si>
-  <si>
-    <t>00907</t>
-  </si>
-  <si>
-    <t>00909</t>
-  </si>
-  <si>
-    <t>00910</t>
-  </si>
-  <si>
-    <t>00912</t>
-  </si>
-  <si>
-    <t>00915</t>
-  </si>
-  <si>
-    <t>00916</t>
-  </si>
-  <si>
-    <t>00917</t>
-  </si>
-  <si>
-    <t>00918</t>
-  </si>
-  <si>
-    <t>00919</t>
-  </si>
-  <si>
-    <t>00921</t>
-  </si>
-  <si>
-    <t>00922</t>
-  </si>
-  <si>
-    <t>00923</t>
-  </si>
-  <si>
-    <t>00924</t>
-  </si>
-  <si>
-    <t>00926</t>
-  </si>
-  <si>
-    <t>00927</t>
-  </si>
-  <si>
-    <t>00928</t>
-  </si>
-  <si>
-    <t>00929</t>
-  </si>
-  <si>
-    <t>00930</t>
-  </si>
-  <si>
-    <t>00932</t>
-  </si>
-  <si>
-    <t>00934</t>
-  </si>
-  <si>
-    <t>00935</t>
-  </si>
-  <si>
-    <t>00936</t>
-  </si>
-  <si>
-    <t>00938</t>
-  </si>
-  <si>
-    <t>00939</t>
-  </si>
-  <si>
-    <t>00940</t>
-  </si>
-  <si>
-    <t>00941</t>
-  </si>
-  <si>
-    <t>00944</t>
-  </si>
-  <si>
-    <t>00946</t>
-  </si>
-  <si>
-    <t>00947</t>
-  </si>
-  <si>
-    <t>00949</t>
-  </si>
-  <si>
-    <t>00951</t>
-  </si>
-  <si>
-    <t>00952</t>
-  </si>
-  <si>
-    <t>00954</t>
-  </si>
-  <si>
-    <t>00960</t>
-  </si>
-  <si>
-    <t>00961</t>
-  </si>
-  <si>
-    <t>00963</t>
-  </si>
-  <si>
-    <t>00965</t>
-  </si>
-  <si>
-    <t>00971</t>
-  </si>
-  <si>
-    <t>06203</t>
-  </si>
-  <si>
-    <t>06205</t>
-  </si>
-  <si>
-    <t>06206</t>
-  </si>
-  <si>
-    <t>06208</t>
-  </si>
-  <si>
-    <t>09800</t>
-  </si>
-  <si>
-    <t>09801</t>
-  </si>
-  <si>
-    <t>09802</t>
-  </si>
-  <si>
-    <t>09803</t>
-  </si>
-  <si>
-    <t>09804</t>
-  </si>
-  <si>
-    <t>09805</t>
-  </si>
-  <si>
-    <t>09808</t>
-  </si>
-  <si>
-    <t>09811</t>
-  </si>
-  <si>
-    <t>09813</t>
-  </si>
-  <si>
-    <t>09816</t>
-  </si>
-  <si>
-    <t>09818</t>
-  </si>
-  <si>
-    <t>09819</t>
-  </si>
-  <si>
-    <t>09820</t>
-  </si>
-  <si>
-    <t>PHYS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FCX</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CRWD</t>
-  </si>
-  <si>
-    <t>PANW</t>
-  </si>
-  <si>
-    <t>LUNC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RENDER</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TCEHY</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BABA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ZH</t>
-  </si>
-  <si>
-    <t>JKS</t>
-  </si>
-  <si>
-    <t>BIDU</t>
-  </si>
-  <si>
-    <t>WB</t>
-  </si>
-  <si>
-    <t>SVA</t>
-  </si>
-  <si>
-    <t>JD</t>
-  </si>
-  <si>
-    <t>NOAH</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PDD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NTES</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LI</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BILI</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CSIQ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DQ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LNVGY</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CBAT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LU</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>VNET</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GDS</t>
-  </si>
-  <si>
-    <t>PAYP</t>
-  </si>
-  <si>
-    <t>TM</t>
-  </si>
-  <si>
-    <t>HMC</t>
-  </si>
-  <si>
-    <t>NSANY</t>
-  </si>
-  <si>
-    <t>SONY</t>
-  </si>
-  <si>
-    <t>LSRCY</t>
-  </si>
-  <si>
-    <t>MUFG</t>
-  </si>
-  <si>
-    <t>NTTYY</t>
-  </si>
-  <si>
-    <t>SMFG</t>
-  </si>
-  <si>
-    <t>ITOCY</t>
-  </si>
-  <si>
-    <t>ASML</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SAP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ADD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>202605 TOP30</t>
-  </si>
-  <si>
-    <t>202605 TOP30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>202605 S&amp;P100</t>
-  </si>
-  <si>
-    <t>202605 S&amp;P100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26/05 Taiwan 50</t>
-  </si>
-  <si>
-    <t>26/05 Taiwan 50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>009800</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>006203</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>006205</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>006206</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>006208</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>009801</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>009802</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>009803</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>009804</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>009805</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>009808</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>009811</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>009813</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>009816</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>009818</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>009819</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>009820</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1281,13 +1299,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1579,7 +1598,7 @@
         <v>2330</v>
       </c>
       <c r="B1" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -1587,7 +1606,7 @@
         <v>2308</v>
       </c>
       <c r="B2" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -1595,7 +1614,7 @@
         <v>2317</v>
       </c>
       <c r="B3" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -1603,7 +1622,7 @@
         <v>2454</v>
       </c>
       <c r="B4" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -1611,7 +1630,7 @@
         <v>3711</v>
       </c>
       <c r="B5" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -1619,7 +1638,7 @@
         <v>2891</v>
       </c>
       <c r="B6" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -1627,7 +1646,7 @@
         <v>2345</v>
       </c>
       <c r="B7" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -1635,7 +1654,7 @@
         <v>2383</v>
       </c>
       <c r="B8" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -1643,7 +1662,7 @@
         <v>2382</v>
       </c>
       <c r="B9" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -1651,7 +1670,7 @@
         <v>2881</v>
       </c>
       <c r="B10" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -1659,7 +1678,7 @@
         <v>2882</v>
       </c>
       <c r="B11" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -1667,7 +1686,7 @@
         <v>2303</v>
       </c>
       <c r="B12" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -1675,7 +1694,7 @@
         <v>3017</v>
       </c>
       <c r="B13" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
@@ -1683,7 +1702,7 @@
         <v>2360</v>
       </c>
       <c r="B14" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
@@ -1691,7 +1710,7 @@
         <v>2887</v>
       </c>
       <c r="B15" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -1699,7 +1718,7 @@
         <v>2412</v>
       </c>
       <c r="B16" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -1707,7 +1726,7 @@
         <v>2884</v>
       </c>
       <c r="B17" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -1715,7 +1734,7 @@
         <v>2885</v>
       </c>
       <c r="B18" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
@@ -1723,7 +1742,7 @@
         <v>2886</v>
       </c>
       <c r="B19" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
@@ -1731,7 +1750,7 @@
         <v>2890</v>
       </c>
       <c r="B20" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
@@ -1739,7 +1758,7 @@
         <v>2357</v>
       </c>
       <c r="B21" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
@@ -1747,7 +1766,7 @@
         <v>3231</v>
       </c>
       <c r="B22" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
@@ -1755,7 +1774,7 @@
         <v>2327</v>
       </c>
       <c r="B23" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
@@ -1763,7 +1782,7 @@
         <v>1303</v>
       </c>
       <c r="B24" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
@@ -1771,7 +1790,7 @@
         <v>1216</v>
       </c>
       <c r="B25" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
@@ -1779,7 +1798,7 @@
         <v>6669</v>
       </c>
       <c r="B26" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
@@ -1787,7 +1806,7 @@
         <v>3653</v>
       </c>
       <c r="B27" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
@@ -1795,7 +1814,7 @@
         <v>2880</v>
       </c>
       <c r="B28" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
@@ -1803,7 +1822,7 @@
         <v>2892</v>
       </c>
       <c r="B29" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
@@ -1811,7 +1830,7 @@
         <v>2883</v>
       </c>
       <c r="B30" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
@@ -1819,7 +1838,7 @@
         <v>2368</v>
       </c>
       <c r="B31" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
@@ -1827,7 +1846,7 @@
         <v>2449</v>
       </c>
       <c r="B32" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
@@ -1835,7 +1854,7 @@
         <v>2344</v>
       </c>
       <c r="B33" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
@@ -1843,7 +1862,7 @@
         <v>2301</v>
       </c>
       <c r="B34" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
@@ -1851,7 +1870,7 @@
         <v>5880</v>
       </c>
       <c r="B35" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
@@ -1859,7 +1878,7 @@
         <v>2408</v>
       </c>
       <c r="B36" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
@@ -1867,7 +1886,7 @@
         <v>2603</v>
       </c>
       <c r="B37" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
@@ -1875,7 +1894,7 @@
         <v>2002</v>
       </c>
       <c r="B38" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
@@ -1883,7 +1902,7 @@
         <v>3008</v>
       </c>
       <c r="B39" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
@@ -1891,7 +1910,7 @@
         <v>3661</v>
       </c>
       <c r="B40" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
@@ -1899,7 +1918,7 @@
         <v>7769</v>
       </c>
       <c r="B41" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
@@ -1907,7 +1926,7 @@
         <v>1301</v>
       </c>
       <c r="B42" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
@@ -1915,7 +1934,7 @@
         <v>2059</v>
       </c>
       <c r="B43" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
@@ -1923,7 +1942,7 @@
         <v>4904</v>
       </c>
       <c r="B44" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
@@ -1931,7 +1950,7 @@
         <v>3045</v>
       </c>
       <c r="B45" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
@@ -1939,7 +1958,7 @@
         <v>2395</v>
       </c>
       <c r="B46" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
@@ -1947,7 +1966,7 @@
         <v>2207</v>
       </c>
       <c r="B47" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
@@ -1955,7 +1974,7 @@
         <v>6919</v>
       </c>
       <c r="B48" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
@@ -1963,7 +1982,7 @@
         <v>6505</v>
       </c>
       <c r="B49" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
@@ -2045,682 +2064,682 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A90" s="2" t="s">
-        <v>325</v>
+      <c r="A90" s="6" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A91" s="2" t="s">
-        <v>326</v>
+      <c r="A91" s="6" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A92" s="2" t="s">
-        <v>327</v>
+      <c r="A92" s="6" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A93" s="2" t="s">
-        <v>328</v>
+      <c r="A93" s="6" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A94" s="2" t="s">
-        <v>329</v>
+      <c r="A94" s="6" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A95" s="2" t="s">
-        <v>330</v>
+      <c r="A95" s="6" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A96" s="2" t="s">
-        <v>331</v>
+      <c r="A96" s="6" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A97" s="2" t="s">
-        <v>332</v>
+      <c r="A97" s="6" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A98" s="2" t="s">
-        <v>333</v>
+      <c r="A98" s="6" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A99" s="2" t="s">
-        <v>334</v>
+      <c r="A99" s="6" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A100" s="2" t="s">
-        <v>335</v>
+      <c r="A100" s="6" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A101" s="2" t="s">
-        <v>336</v>
+      <c r="A101" s="6" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A102" s="2" t="s">
-        <v>337</v>
+      <c r="A102" s="6" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A103" s="2" t="s">
-        <v>338</v>
+      <c r="A103" s="6" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A104" s="2" t="s">
-        <v>339</v>
+      <c r="A104" s="6" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A105" s="2" t="s">
-        <v>340</v>
+      <c r="A105" s="6" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A106" s="2" t="s">
-        <v>341</v>
+      <c r="A106" s="6" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>206</v>
+        <v>369</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -2743,7 +2762,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>342</v>
+        <v>324</v>
       </c>
       <c r="B1" s="1"/>
     </row>
@@ -3108,7 +3127,7 @@
         <v>7</v>
       </c>
       <c r="B1" t="s">
-        <v>384</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -3116,7 +3135,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>384</v>
+        <v>366</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -3124,7 +3143,7 @@
         <v>88</v>
       </c>
       <c r="B3" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -3132,7 +3151,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -3140,7 +3159,7 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -3148,7 +3167,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -3156,7 +3175,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -3164,7 +3183,7 @@
         <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -3172,7 +3191,7 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -3180,7 +3199,7 @@
         <v>89</v>
       </c>
       <c r="B10" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -3188,7 +3207,7 @@
         <v>90</v>
       </c>
       <c r="B11" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -3196,7 +3215,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -3204,7 +3223,7 @@
         <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
@@ -3212,7 +3231,7 @@
         <v>91</v>
       </c>
       <c r="B14" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
@@ -3220,7 +3239,7 @@
         <v>92</v>
       </c>
       <c r="B15" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -3228,7 +3247,7 @@
         <v>93</v>
       </c>
       <c r="B16" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -3236,7 +3255,7 @@
         <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -3244,7 +3263,7 @@
         <v>94</v>
       </c>
       <c r="B18" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
@@ -3252,7 +3271,7 @@
         <v>95</v>
       </c>
       <c r="B19" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
@@ -3260,7 +3279,7 @@
         <v>96</v>
       </c>
       <c r="B20" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
@@ -3268,7 +3287,7 @@
         <v>23</v>
       </c>
       <c r="B21" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
@@ -3276,7 +3295,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
@@ -3284,7 +3303,7 @@
         <v>97</v>
       </c>
       <c r="B23" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
@@ -3292,7 +3311,7 @@
         <v>98</v>
       </c>
       <c r="B24" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
@@ -3300,7 +3319,7 @@
         <v>99</v>
       </c>
       <c r="B25" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
@@ -3308,7 +3327,7 @@
         <v>100</v>
       </c>
       <c r="B26" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
@@ -3316,7 +3335,7 @@
         <v>101</v>
       </c>
       <c r="B27" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
@@ -3324,7 +3343,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
@@ -3332,7 +3351,7 @@
         <v>102</v>
       </c>
       <c r="B29" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
@@ -3340,7 +3359,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
@@ -3348,7 +3367,7 @@
         <v>103</v>
       </c>
       <c r="B31" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
@@ -3356,7 +3375,7 @@
         <v>104</v>
       </c>
       <c r="B32" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
@@ -3364,7 +3383,7 @@
         <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
@@ -3372,7 +3391,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
@@ -3380,7 +3399,7 @@
         <v>105</v>
       </c>
       <c r="B35" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
@@ -3388,7 +3407,7 @@
         <v>106</v>
       </c>
       <c r="B36" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
@@ -3396,7 +3415,7 @@
         <v>107</v>
       </c>
       <c r="B37" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
@@ -3404,7 +3423,7 @@
         <v>108</v>
       </c>
       <c r="B38" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
@@ -3412,7 +3431,7 @@
         <v>109</v>
       </c>
       <c r="B39" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
@@ -3420,7 +3439,7 @@
         <v>110</v>
       </c>
       <c r="B40" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
@@ -3428,7 +3447,7 @@
         <v>111</v>
       </c>
       <c r="B41" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
@@ -3436,7 +3455,7 @@
         <v>112</v>
       </c>
       <c r="B42" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
@@ -3444,7 +3463,7 @@
         <v>113</v>
       </c>
       <c r="B43" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
@@ -3452,7 +3471,7 @@
         <v>114</v>
       </c>
       <c r="B44" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
@@ -3460,7 +3479,7 @@
         <v>115</v>
       </c>
       <c r="B45" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
@@ -3468,7 +3487,7 @@
         <v>116</v>
       </c>
       <c r="B46" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
@@ -3476,7 +3495,7 @@
         <v>117</v>
       </c>
       <c r="B47" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
@@ -3484,7 +3503,7 @@
         <v>118</v>
       </c>
       <c r="B48" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
@@ -3492,7 +3511,7 @@
         <v>119</v>
       </c>
       <c r="B49" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
@@ -3500,7 +3519,7 @@
         <v>120</v>
       </c>
       <c r="B50" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
@@ -3508,7 +3527,7 @@
         <v>121</v>
       </c>
       <c r="B51" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
@@ -3516,7 +3535,7 @@
         <v>122</v>
       </c>
       <c r="B52" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
@@ -3524,7 +3543,7 @@
         <v>123</v>
       </c>
       <c r="B53" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
@@ -3532,7 +3551,7 @@
         <v>124</v>
       </c>
       <c r="B54" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
@@ -3540,7 +3559,7 @@
         <v>125</v>
       </c>
       <c r="B55" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
@@ -3548,7 +3567,7 @@
         <v>126</v>
       </c>
       <c r="B56" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
@@ -3556,7 +3575,7 @@
         <v>127</v>
       </c>
       <c r="B57" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
@@ -3564,7 +3583,7 @@
         <v>128</v>
       </c>
       <c r="B58" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
@@ -3572,7 +3591,7 @@
         <v>129</v>
       </c>
       <c r="B59" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
@@ -3580,7 +3599,7 @@
         <v>130</v>
       </c>
       <c r="B60" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
@@ -3588,7 +3607,7 @@
         <v>32</v>
       </c>
       <c r="B61" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
@@ -3596,7 +3615,7 @@
         <v>131</v>
       </c>
       <c r="B62" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
@@ -3604,7 +3623,7 @@
         <v>132</v>
       </c>
       <c r="B63" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
@@ -3612,7 +3631,7 @@
         <v>133</v>
       </c>
       <c r="B64" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
@@ -3620,7 +3639,7 @@
         <v>134</v>
       </c>
       <c r="B65" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
@@ -3628,7 +3647,7 @@
         <v>135</v>
       </c>
       <c r="B66" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
@@ -3636,7 +3655,7 @@
         <v>136</v>
       </c>
       <c r="B67" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
@@ -3644,7 +3663,7 @@
         <v>137</v>
       </c>
       <c r="B68" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
@@ -3652,7 +3671,7 @@
         <v>138</v>
       </c>
       <c r="B69" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
@@ -3660,7 +3679,7 @@
         <v>139</v>
       </c>
       <c r="B70" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
@@ -3668,7 +3687,7 @@
         <v>140</v>
       </c>
       <c r="B71" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
@@ -3676,7 +3695,7 @@
         <v>141</v>
       </c>
       <c r="B72" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
@@ -3684,7 +3703,7 @@
         <v>142</v>
       </c>
       <c r="B73" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
@@ -3692,7 +3711,7 @@
         <v>143</v>
       </c>
       <c r="B74" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
@@ -3700,7 +3719,7 @@
         <v>144</v>
       </c>
       <c r="B75" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
@@ -3708,7 +3727,7 @@
         <v>145</v>
       </c>
       <c r="B76" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
@@ -3716,7 +3735,7 @@
         <v>146</v>
       </c>
       <c r="B77" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
@@ -3724,7 +3743,7 @@
         <v>147</v>
       </c>
       <c r="B78" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
@@ -3732,7 +3751,7 @@
         <v>148</v>
       </c>
       <c r="B79" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
@@ -3740,7 +3759,7 @@
         <v>149</v>
       </c>
       <c r="B80" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
@@ -3748,7 +3767,7 @@
         <v>150</v>
       </c>
       <c r="B81" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
@@ -3756,7 +3775,7 @@
         <v>151</v>
       </c>
       <c r="B82" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
@@ -3764,7 +3783,7 @@
         <v>152</v>
       </c>
       <c r="B83" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
@@ -3772,7 +3791,7 @@
         <v>33</v>
       </c>
       <c r="B84" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
@@ -3780,7 +3799,7 @@
         <v>153</v>
       </c>
       <c r="B85" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
@@ -3788,7 +3807,7 @@
         <v>154</v>
       </c>
       <c r="B86" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
@@ -3796,7 +3815,7 @@
         <v>155</v>
       </c>
       <c r="B87" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
@@ -3804,7 +3823,7 @@
         <v>156</v>
       </c>
       <c r="B88" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
@@ -3812,7 +3831,7 @@
         <v>157</v>
       </c>
       <c r="B89" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
@@ -3820,7 +3839,7 @@
         <v>158</v>
       </c>
       <c r="B90" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
@@ -3828,7 +3847,7 @@
         <v>159</v>
       </c>
       <c r="B91" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
@@ -3836,7 +3855,7 @@
         <v>160</v>
       </c>
       <c r="B92" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
@@ -3844,7 +3863,7 @@
         <v>161</v>
       </c>
       <c r="B93" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
@@ -3852,7 +3871,7 @@
         <v>162</v>
       </c>
       <c r="B94" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
@@ -3860,7 +3879,7 @@
         <v>163</v>
       </c>
       <c r="B95" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
@@ -3868,7 +3887,7 @@
         <v>164</v>
       </c>
       <c r="B96" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
@@ -3876,7 +3895,7 @@
         <v>165</v>
       </c>
       <c r="B97" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
@@ -3884,7 +3903,7 @@
         <v>166</v>
       </c>
       <c r="B98" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
@@ -3892,7 +3911,7 @@
         <v>167</v>
       </c>
       <c r="B99" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
@@ -3900,7 +3919,7 @@
         <v>168</v>
       </c>
       <c r="B100" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
@@ -3908,182 +3927,182 @@
         <v>169</v>
       </c>
       <c r="B101" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>343</v>
+        <v>325</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>344</v>
+        <v>326</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>345</v>
+        <v>327</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>348</v>
+        <v>330</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>349</v>
+        <v>331</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
-        <v>350</v>
+        <v>332</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
-        <v>351</v>
+        <v>333</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
-        <v>352</v>
+        <v>334</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
-        <v>353</v>
+        <v>335</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
-        <v>354</v>
+        <v>336</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
-        <v>355</v>
+        <v>337</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
-        <v>356</v>
+        <v>338</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
-        <v>357</v>
+        <v>339</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
-        <v>358</v>
+        <v>340</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
-        <v>359</v>
+        <v>341</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
-        <v>360</v>
+        <v>342</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
-        <v>361</v>
+        <v>343</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
-        <v>364</v>
+        <v>346</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A122" s="4" t="s">
-        <v>365</v>
+        <v>347</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A123" s="4" t="s">
-        <v>366</v>
+        <v>348</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>367</v>
+        <v>349</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>369</v>
+        <v>351</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>371</v>
+        <v>353</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>375</v>
+        <v>357</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>376</v>
+        <v>358</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>377</v>
+        <v>359</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A136" s="5" t="s">
-        <v>379</v>
+        <v>361</v>
       </c>
     </row>
   </sheetData>
@@ -4106,7 +4125,7 @@
         <v>170</v>
       </c>
       <c r="B1" t="s">
-        <v>382</v>
+        <v>364</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -4114,7 +4133,7 @@
         <v>171</v>
       </c>
       <c r="B2" t="s">
-        <v>382</v>
+        <v>364</v>
       </c>
       <c r="H2" s="3"/>
       <c r="M2" s="3"/>
@@ -4124,7 +4143,7 @@
         <v>172</v>
       </c>
       <c r="B3" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="H3" s="3"/>
       <c r="M3" s="3"/>
@@ -4134,7 +4153,7 @@
         <v>185</v>
       </c>
       <c r="B4" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="H4" s="3"/>
       <c r="M4" s="3"/>
@@ -4144,7 +4163,7 @@
         <v>186</v>
       </c>
       <c r="B5" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="H5" s="3"/>
       <c r="M5" s="3"/>
@@ -4154,7 +4173,7 @@
         <v>173</v>
       </c>
       <c r="B6" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="H6" s="3"/>
       <c r="M6" s="3"/>
@@ -4164,7 +4183,7 @@
         <v>174</v>
       </c>
       <c r="B7" t="s">
-        <v>382</v>
+        <v>364</v>
       </c>
       <c r="M7" s="3"/>
     </row>
@@ -4173,7 +4192,7 @@
         <v>187</v>
       </c>
       <c r="B8" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="H8" s="3"/>
       <c r="M8" s="3"/>
@@ -4183,7 +4202,7 @@
         <v>188</v>
       </c>
       <c r="B9" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="H9" s="3"/>
       <c r="M9" s="3"/>
@@ -4193,7 +4212,7 @@
         <v>189</v>
       </c>
       <c r="B10" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="H10" s="3"/>
       <c r="M10" s="3"/>
@@ -4203,7 +4222,7 @@
         <v>175</v>
       </c>
       <c r="B11" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="M11" s="3"/>
     </row>
@@ -4212,7 +4231,7 @@
         <v>190</v>
       </c>
       <c r="B12" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="H12" s="3"/>
       <c r="M12" s="3"/>
@@ -4222,7 +4241,7 @@
         <v>191</v>
       </c>
       <c r="B13" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="H13" s="3"/>
       <c r="M13" s="3"/>
@@ -4232,7 +4251,7 @@
         <v>192</v>
       </c>
       <c r="B14" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="H14" s="3"/>
       <c r="M14" s="3"/>
@@ -4242,7 +4261,7 @@
         <v>195</v>
       </c>
       <c r="B15" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="H15" s="3"/>
       <c r="M15" s="3"/>
@@ -4252,7 +4271,7 @@
         <v>193</v>
       </c>
       <c r="B16" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="M16" s="3"/>
     </row>
@@ -4261,7 +4280,7 @@
         <v>194</v>
       </c>
       <c r="B17" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="H17" s="3"/>
       <c r="M17" s="3"/>
@@ -4271,7 +4290,7 @@
         <v>176</v>
       </c>
       <c r="B18" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="H18" s="3"/>
       <c r="M18" s="3"/>
@@ -4281,7 +4300,7 @@
         <v>177</v>
       </c>
       <c r="B19" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="H19" s="3"/>
       <c r="M19" s="3"/>
@@ -4291,7 +4310,7 @@
         <v>179</v>
       </c>
       <c r="B20" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="H20" s="3"/>
       <c r="M20" s="3"/>
@@ -4301,7 +4320,7 @@
         <v>178</v>
       </c>
       <c r="B21" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="H21" s="3"/>
       <c r="M21" s="3"/>
@@ -4311,7 +4330,7 @@
         <v>196</v>
       </c>
       <c r="B22" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="M22" s="3"/>
     </row>
@@ -4320,7 +4339,7 @@
         <v>197</v>
       </c>
       <c r="B23" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="H23" s="3"/>
       <c r="M23" s="3"/>
@@ -4330,7 +4349,7 @@
         <v>198</v>
       </c>
       <c r="B24" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="H24" s="3"/>
       <c r="M24" s="3"/>
@@ -4340,7 +4359,7 @@
         <v>199</v>
       </c>
       <c r="B25" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="H25" s="3"/>
       <c r="M25" s="3"/>
@@ -4350,7 +4369,7 @@
         <v>180</v>
       </c>
       <c r="B26" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="H26" s="3"/>
       <c r="M26" s="3"/>
@@ -4360,7 +4379,7 @@
         <v>181</v>
       </c>
       <c r="B27" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="M27" s="3"/>
     </row>
@@ -4369,7 +4388,7 @@
         <v>182</v>
       </c>
       <c r="B28" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="H28" s="3"/>
       <c r="M28" s="3"/>
@@ -4379,7 +4398,7 @@
         <v>183</v>
       </c>
       <c r="B29" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="H29" s="3"/>
       <c r="M29" s="3"/>
@@ -4389,27 +4408,27 @@
         <v>184</v>
       </c>
       <c r="B30" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="H30" s="3"/>
       <c r="M30" s="3"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
       <c r="B31" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="H31" s="3"/>
       <c r="M31" s="3"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>347</v>
+        <v>329</v>
       </c>
       <c r="B32" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="H32" s="3"/>
       <c r="M32" s="3"/>

--- a/TrackingList.xlsx
+++ b/TrackingList.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11580" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18096" windowHeight="7932" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="台灣股票" sheetId="1" r:id="rId1"/>
@@ -15,10 +20,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">台灣ETF!$B$1:$B$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">美國股票!$D$1:$F$430</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">虛擬貨幣!$G$2:$Q$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">美國股票!$D$1:$F$430</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="493">
   <si>
     <t>26/05 Taiwan 50</t>
   </si>
@@ -605,9 +610,6 @@
     <t>FNGG</t>
   </si>
   <si>
-    <t>FNGU</t>
-  </si>
-  <si>
     <t>FPA</t>
   </si>
   <si>
@@ -632,9 +634,6 @@
     <t>GRID</t>
   </si>
   <si>
-    <t>GUSH</t>
-  </si>
-  <si>
     <t>HACK</t>
   </si>
   <si>
@@ -686,9 +685,6 @@
     <t>KSTR</t>
   </si>
   <si>
-    <t>LABU</t>
-  </si>
-  <si>
     <t>LIT</t>
   </si>
   <si>
@@ -824,9 +820,6 @@
     <t>SMH</t>
   </si>
   <si>
-    <t>SOXL</t>
-  </si>
-  <si>
     <t>SOXQ</t>
   </si>
   <si>
@@ -848,9 +841,6 @@
     <t>TAN</t>
   </si>
   <si>
-    <t>TECL</t>
-  </si>
-  <si>
     <t>THNQ</t>
   </si>
   <si>
@@ -863,15 +853,6 @@
     <t>TLT</t>
   </si>
   <si>
-    <t>TMF</t>
-  </si>
-  <si>
-    <t>TNA</t>
-  </si>
-  <si>
-    <t>TQQQ</t>
-  </si>
-  <si>
     <t>TRFK</t>
   </si>
   <si>
@@ -887,9 +868,6 @@
     <t>UGL</t>
   </si>
   <si>
-    <t>UPRO</t>
-  </si>
-  <si>
     <t>UPV</t>
   </si>
   <si>
@@ -1013,9 +991,6 @@
     <t>XTL</t>
   </si>
   <si>
-    <t>YINN</t>
-  </si>
-  <si>
     <t>AAPL</t>
   </si>
   <si>
@@ -1523,27 +1498,55 @@
     <t>LUNC</t>
   </si>
   <si>
-    <t>ADD</t>
-  </si>
-  <si>
     <t>RENDER</t>
+  </si>
+  <si>
+    <t>CEG</t>
+  </si>
+  <si>
+    <t>CCJ</t>
+  </si>
+  <si>
+    <t>ETN</t>
+  </si>
+  <si>
+    <t>SRVR</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PSLY</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ONDO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="_-&quot;NT$&quot;* #,##0.00_-;\-&quot;NT$&quot;* #,##0.00_-;_-&quot;NT$&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;NT$&quot;* #,##0_-;\-&quot;NT$&quot;* #,##0_-;_-&quot;NT$&quot;* &quot;-&quot;_-;_-@_-"/>
-  </numFmts>
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1551,167 +1554,31 @@
       <sz val="10"/>
       <color rgb="FF202122"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF232A31"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1724,194 +1591,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1919,253 +1600,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2174,60 +1613,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -2238,6 +1666,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2495,19 +1926,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:B55"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B57"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.62857142857143" customWidth="1"/>
+    <col min="1" max="1" width="9.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1">
         <v>1216</v>
       </c>
@@ -2515,7 +1946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1301</v>
       </c>
@@ -2523,7 +1954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1303</v>
       </c>
@@ -2531,22 +1962,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1503</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1513</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1519</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2002</v>
       </c>
@@ -2554,7 +1985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2059</v>
       </c>
@@ -2562,7 +1993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2207</v>
       </c>
@@ -2570,7 +2001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2301</v>
       </c>
@@ -2578,7 +2009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2303</v>
       </c>
@@ -2586,7 +2017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2308</v>
       </c>
@@ -2594,7 +2025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2317</v>
       </c>
@@ -2602,7 +2033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2327</v>
       </c>
@@ -2610,7 +2041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2330</v>
       </c>
@@ -2618,7 +2049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2344</v>
       </c>
@@ -2626,7 +2057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2345</v>
       </c>
@@ -2634,7 +2065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2357</v>
       </c>
@@ -2642,7 +2073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2360</v>
       </c>
@@ -2650,7 +2081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2368</v>
       </c>
@@ -2658,7 +2089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2382</v>
       </c>
@@ -2666,7 +2097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2383</v>
       </c>
@@ -2674,7 +2105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2395</v>
       </c>
@@ -2682,7 +2113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>2408</v>
       </c>
@@ -2690,7 +2121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>2412</v>
       </c>
@@ -2698,7 +2129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>2449</v>
       </c>
@@ -2706,7 +2137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>2454</v>
       </c>
@@ -2714,7 +2145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>2603</v>
       </c>
@@ -2722,7 +2153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>2880</v>
       </c>
@@ -2730,7 +2161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>2881</v>
       </c>
@@ -2738,7 +2169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>2882</v>
       </c>
@@ -2746,7 +2177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>2883</v>
       </c>
@@ -2754,7 +2185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>2884</v>
       </c>
@@ -2762,7 +2193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>2885</v>
       </c>
@@ -2770,7 +2201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>2886</v>
       </c>
@@ -2778,7 +2209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>2887</v>
       </c>
@@ -2786,7 +2217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>2890</v>
       </c>
@@ -2794,7 +2225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>2891</v>
       </c>
@@ -2802,7 +2233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>2892</v>
       </c>
@@ -2810,7 +2241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>3008</v>
       </c>
@@ -2818,7 +2249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>3017</v>
       </c>
@@ -2826,7 +2257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>3045</v>
       </c>
@@ -2834,12 +2265,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>3131</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>3231</v>
       </c>
@@ -2847,12 +2278,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>3324</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>3653</v>
       </c>
@@ -2860,7 +2291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>3661</v>
       </c>
@@ -2868,7 +2299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>3711</v>
       </c>
@@ -2876,7 +2307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>4904</v>
       </c>
@@ -2884,7 +2315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>5880</v>
       </c>
@@ -2892,7 +2323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>6505</v>
       </c>
@@ -2900,12 +2331,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>6640</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>6669</v>
       </c>
@@ -2913,7 +2344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>6919</v>
       </c>
@@ -2921,741 +2352,756 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>7769</v>
       </c>
       <c r="B55" t="s">
         <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>8996</v>
       </c>
     </row>
   </sheetData>
   <sortState ref="A1:B55">
     <sortCondition ref="A1"/>
   </sortState>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <conditionalFormatting sqref="A68:A1048576 A1:A55">
+    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A56:A66">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:A142"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B142"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.5047619047619" style="6" customWidth="1"/>
-    <col min="2" max="2" width="9.5047619047619" style="7" customWidth="1"/>
+    <col min="1" max="1" width="9.5" style="6" customWidth="1"/>
+    <col min="2" max="2" width="9.5" style="7" customWidth="1"/>
     <col min="3" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="50" spans="1:1">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="51" spans="1:1">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="54" spans="1:1">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="61" spans="1:1">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="62" spans="1:1">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="63" spans="1:1">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="64" spans="1:1">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="65" spans="1:1">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="66" spans="1:1">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="67" spans="1:1">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="68" spans="1:1">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="69" spans="1:1">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="70" spans="1:1">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="71" spans="1:1">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="72" spans="1:1">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="73" spans="1:1">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="74" spans="1:1">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="75" spans="1:1">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75" s="6" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="76" spans="1:1">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76" s="6" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="77" spans="1:1">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A77" s="6" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="78" spans="1:1">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A78" s="6" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="79" spans="1:1">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79" s="6" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="80" spans="1:1">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A80" s="6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="81" spans="1:1">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" s="6" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="82" spans="1:1">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82" s="6" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:1">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" s="6" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="84" spans="1:1">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" s="6" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="85" spans="1:1">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" s="6" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="86" spans="1:1">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86" s="6" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="87" spans="1:1">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A87" s="6" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="88" spans="1:1">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A88" s="6" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="89" spans="1:1">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A89" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="90" spans="1:1">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A90" s="6" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="91" spans="1:1">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" s="6" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="92" spans="1:1">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A92" s="6" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="93" spans="1:1">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A93" s="6" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="94" spans="1:1">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A94" s="6" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="95" spans="1:1">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A95" s="6" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="96" spans="1:1">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A96" s="6" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="97" spans="1:1">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A97" s="6" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="98" spans="1:1">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A98" s="6" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="99" spans="1:1">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A99" s="6" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="100" spans="1:1">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A100" s="6" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="101" spans="1:1">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A101" s="6" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="102" spans="1:1">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A102" s="6" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="103" spans="1:1">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A103" s="6" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="104" spans="1:1">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A104" s="6" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="105" spans="1:1">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A105" s="6" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="106" spans="1:1">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A106" s="6" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="107" spans="1:1">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A107" s="6" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="108" spans="1:1">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A108" s="6" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="109" spans="1:1">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A109" s="6" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="110" spans="1:1">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A110" s="6" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="111" spans="1:1">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A111" s="6" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="112" spans="1:1">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A112" s="6" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="113" spans="1:1">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A113" s="6" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="114" spans="1:1">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A114" s="6" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="115" spans="1:1">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A115" s="6" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="116" spans="1:1">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A116" s="6" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="117" spans="1:1">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A117" s="6" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="118" spans="1:1">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A118" s="6" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="119" spans="1:1">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A119" s="6" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="120" spans="1:1">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A120" s="6" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="121" spans="1:1">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A121" s="6" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="122" spans="1:1">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A122" s="6" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="123" spans="1:1">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A123" s="6" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="124" spans="1:1">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A124" s="6" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="125" spans="1:1">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A125" s="6" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="126" spans="1:1">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A126" s="6" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="127" spans="1:1">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A127" s="6" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="128" spans="1:1">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A128" s="6" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="129" spans="1:1">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A129" s="8" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="130" spans="1:1">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A130" s="8" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="131" spans="1:1">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A131" s="8" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="132" spans="1:1">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A132" s="8" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="133" spans="1:1">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A133" s="8" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="134" spans="1:1">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A134" s="8" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="135" spans="1:1">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A135" s="8" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="136" spans="1:1">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A136" s="8" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="137" spans="1:1">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A137" s="8" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="138" spans="1:1">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A138" s="8" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="139" spans="1:1">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A139" s="8" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="140" spans="1:1">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A140" s="8" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="141" spans="1:1">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A141" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="142" spans="1:1">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A142" s="6" t="s">
         <v>142</v>
       </c>
@@ -3664,936 +3110,907 @@
   <sortState ref="A1:A142">
     <sortCondition ref="A1"/>
   </sortState>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I216"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.6285714285714" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11.625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="50" spans="1:1">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="51" spans="1:1">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="54" spans="1:1">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="61" spans="1:1">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="62" spans="1:1">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="63" spans="1:1">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="64" spans="1:1">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="65" spans="1:1">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="66" spans="1:1">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="67" spans="1:1">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="68" spans="1:1">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="69" spans="1:1">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="70" spans="1:1">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="71" spans="1:1">
-      <c r="A71" s="5" t="s">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="72" spans="1:1">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="73" spans="1:1">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="74" spans="1:1">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="75" spans="1:1">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="76" spans="1:1">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="77" spans="1:1">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="78" spans="1:1">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="79" spans="1:1">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="80" spans="1:1">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="81" spans="1:1">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="82" spans="1:1">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="83" spans="1:1">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="84" spans="1:1">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="85" spans="1:1">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="86" spans="1:1">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="87" spans="1:1">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="88" spans="1:1">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="89" spans="1:1">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="90" spans="1:1">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="91" spans="1:1">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="92" spans="1:1">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="93" spans="1:1">
-      <c r="A93" s="5" t="s">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A93" s="10" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A94" s="5" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="94" spans="1:1">
-      <c r="A94" s="5" t="s">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A95" s="5" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="95" spans="1:1">
-      <c r="A95" s="5" t="s">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A96" s="5" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="96" spans="1:1">
-      <c r="A96" s="5" t="s">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A97" s="5" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="97" spans="1:1">
-      <c r="A97" s="5" t="s">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A98" s="5" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="98" spans="1:1">
-      <c r="A98" s="5" t="s">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A99" s="5" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="99" spans="1:1">
-      <c r="A99" s="5" t="s">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A100" s="5" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="100" spans="1:1">
-      <c r="A100" s="5" t="s">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A101" s="5" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="101" spans="1:1">
-      <c r="A101" s="5" t="s">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A102" s="5" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="102" spans="1:1">
-      <c r="A102" s="5" t="s">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A103" s="5" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="103" spans="1:1">
-      <c r="A103" s="5" t="s">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A104" s="5" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="104" spans="1:1">
-      <c r="A104" s="5" t="s">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A105" s="5" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="105" spans="1:1">
-      <c r="A105" s="5" t="s">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A106" s="5" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="106" spans="1:1">
-      <c r="A106" s="5" t="s">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A107" s="5" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="107" spans="1:1">
-      <c r="A107" s="5" t="s">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A108" s="5" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="108" spans="1:1">
-      <c r="A108" s="5" t="s">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A109" s="5" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="109" spans="1:1">
-      <c r="A109" s="5" t="s">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A110" s="5" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="110" spans="1:1">
-      <c r="A110" s="5" t="s">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A111" s="5" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="111" spans="1:1">
-      <c r="A111" s="5" t="s">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A112" s="5" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="112" spans="1:1">
-      <c r="A112" s="5" t="s">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A113" s="5" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="113" spans="1:1">
-      <c r="A113" s="5" t="s">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A114" s="5" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="114" spans="1:1">
-      <c r="A114" s="5" t="s">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A115" s="5" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="115" spans="1:1">
-      <c r="A115" s="5" t="s">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A116" s="5" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="116" spans="1:1">
-      <c r="A116" s="5" t="s">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A117" s="5" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="117" spans="1:1">
-      <c r="A117" s="5" t="s">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A118" s="5" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="118" spans="1:1">
-      <c r="A118" s="5" t="s">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A119" s="5" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="119" spans="1:1">
-      <c r="A119" s="5" t="s">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A120" s="5" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="120" spans="1:1">
-      <c r="A120" s="5" t="s">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A121" s="5" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="121" spans="1:1">
-      <c r="A121" s="5" t="s">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A122" s="10" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A123" s="5" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="122" spans="1:1">
-      <c r="A122" s="5" t="s">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A124" s="5" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="123" spans="1:1">
-      <c r="A123" s="5" t="s">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A125" s="5" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="124" spans="1:1">
-      <c r="A124" s="5" t="s">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A126" s="5" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="125" spans="1:1">
-      <c r="A125" s="5" t="s">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A127" s="5" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="126" spans="1:1">
-      <c r="A126" s="5" t="s">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A128" s="5" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="127" spans="1:1">
-      <c r="A127" s="5" t="s">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A129" s="5" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="128" spans="1:1">
-      <c r="A128" s="5" t="s">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A130" s="5" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="129" spans="1:1">
-      <c r="A129" s="5" t="s">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A131" s="5" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="130" spans="1:1">
-      <c r="A130" s="5" t="s">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A132" s="5" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="131" spans="1:1">
-      <c r="A131" s="5" t="s">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A133" s="5" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="132" spans="1:1">
-      <c r="A132" s="5" t="s">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A134" s="5" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="133" spans="1:1">
-      <c r="A133" s="5" t="s">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A135" s="5" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="134" spans="1:1">
-      <c r="A134" s="5" t="s">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A136" s="5" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="135" spans="1:1">
-      <c r="A135" s="5" t="s">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A137" s="5" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="136" spans="1:1">
-      <c r="A136" s="5" t="s">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A138" s="5" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="137" spans="1:1">
-      <c r="A137" s="5" t="s">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A139" s="5" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="138" spans="1:1">
-      <c r="A138" s="5" t="s">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A140" s="5" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="139" spans="1:1">
-      <c r="A139" s="5" t="s">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A141" s="5" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="140" spans="1:1">
-      <c r="A140" s="5" t="s">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A142" s="5" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="141" spans="1:1">
-      <c r="A141" s="5" t="s">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A143" s="5" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="142" spans="1:1">
-      <c r="A142" s="5" t="s">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A144" s="5" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="143" spans="1:1">
-      <c r="A143" s="5" t="s">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A145" s="5" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="144" spans="1:1">
-      <c r="A144" s="5" t="s">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A146" s="5" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="145" spans="1:1">
-      <c r="A145" s="5" t="s">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A147" s="5" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="146" spans="1:1">
-      <c r="A146" s="5" t="s">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A148" s="5" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="147" spans="1:1">
-      <c r="A147" s="5" t="s">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A149" s="5" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="148" spans="1:1">
-      <c r="A148" s="5" t="s">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A150" s="5" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="149" spans="1:1">
-      <c r="A149" s="5" t="s">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A151" s="5" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="150" spans="1:1">
-      <c r="A150" s="5" t="s">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A152" s="5" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="151" spans="1:1">
-      <c r="A151" s="5" t="s">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A153" s="5" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="152" spans="1:1">
-      <c r="A152" s="5" t="s">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A154" s="5" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="153" spans="1:1">
-      <c r="A153" s="5" t="s">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A155" s="5" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="154" spans="1:1">
-      <c r="A154" s="5" t="s">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A156" s="5" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="155" spans="1:1">
-      <c r="A155" s="5" t="s">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A157" s="5" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="156" spans="1:1">
-      <c r="A156" s="5" t="s">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A158" s="5" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="157" spans="1:1">
-      <c r="A157" s="5" t="s">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A159" s="5" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="158" spans="1:1">
-      <c r="A158" s="5" t="s">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A160" s="5" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="159" spans="1:1">
-      <c r="A159" s="5" t="s">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A161" s="5" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="160" spans="1:1">
-      <c r="A160" s="5" t="s">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A162" s="5" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="161" spans="1:1">
-      <c r="A161" s="5" t="s">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A163" s="5" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="162" spans="1:1">
-      <c r="A162" s="5" t="s">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A164" s="5" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="163" spans="1:1">
-      <c r="A163" s="5" t="s">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A165" s="5" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="164" spans="1:1">
-      <c r="A164" s="5" t="s">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A166" s="5" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="165" spans="1:1">
-      <c r="A165" s="5" t="s">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A167" s="5" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="166" spans="1:1">
-      <c r="A166" s="5" t="s">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A168" s="5" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="167" spans="1:1">
-      <c r="A167" s="5" t="s">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A169" s="5" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="168" spans="1:1">
-      <c r="A168" s="5" t="s">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A170" s="5" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="169" spans="1:1">
-      <c r="A169" s="5" t="s">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A171" s="5" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="170" spans="1:1">
-      <c r="A170" s="5" t="s">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A172" s="5" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="171" spans="1:1">
-      <c r="A171" s="5" t="s">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A173" s="5" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="172" spans="1:1">
-      <c r="A172" s="5" t="s">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A174" s="5" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="173" spans="1:1">
-      <c r="A173" s="5" t="s">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A175" s="5" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="174" spans="1:1">
-      <c r="A174" s="5" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="175" spans="1:1">
-      <c r="A175" s="5" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="176" spans="1:1">
-      <c r="A176" s="5" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="177" spans="1:1">
-      <c r="A177" s="5" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="178" spans="1:1">
-      <c r="A178" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="179" spans="1:1">
-      <c r="A179" s="5" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="180" spans="1:1">
-      <c r="A180" s="5" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="181" spans="1:1">
-      <c r="A181" s="5" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="182" spans="1:1">
-      <c r="A182" s="5" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="183" spans="1:1">
-      <c r="A183" s="5" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="203" spans="2:9">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A186" s="10"/>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A187" s="10"/>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A189" s="10"/>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A191" s="10"/>
+    </row>
+    <row r="203" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B203" s="5"/>
       <c r="C203" s="5"/>
       <c r="D203" s="5"/>
@@ -4603,7 +4020,7 @@
       <c r="H203" s="5"/>
       <c r="I203" s="5"/>
     </row>
-    <row r="204" spans="2:9">
+    <row r="204" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B204" s="5"/>
       <c r="C204" s="5"/>
       <c r="D204" s="5"/>
@@ -4613,7 +4030,7 @@
       <c r="H204" s="5"/>
       <c r="I204" s="5"/>
     </row>
-    <row r="205" spans="2:9">
+    <row r="205" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B205" s="5"/>
       <c r="C205" s="5"/>
       <c r="D205" s="5"/>
@@ -4623,7 +4040,7 @@
       <c r="H205" s="5"/>
       <c r="I205" s="5"/>
     </row>
-    <row r="206" spans="2:9">
+    <row r="206" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B206" s="5"/>
       <c r="C206" s="5"/>
       <c r="D206" s="5"/>
@@ -4633,7 +4050,7 @@
       <c r="H206" s="5"/>
       <c r="I206" s="5"/>
     </row>
-    <row r="207" spans="2:9">
+    <row r="207" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B207" s="5"/>
       <c r="C207" s="5"/>
       <c r="D207" s="5"/>
@@ -4643,7 +4060,7 @@
       <c r="H207" s="5"/>
       <c r="I207" s="5"/>
     </row>
-    <row r="208" spans="2:9">
+    <row r="208" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B208" s="5"/>
       <c r="C208" s="5"/>
       <c r="D208" s="5"/>
@@ -4653,7 +4070,7 @@
       <c r="H208" s="5"/>
       <c r="I208" s="5"/>
     </row>
-    <row r="209" spans="2:9">
+    <row r="209" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B209" s="5"/>
       <c r="C209" s="5"/>
       <c r="D209" s="5"/>
@@ -4663,7 +4080,7 @@
       <c r="H209" s="5"/>
       <c r="I209" s="5"/>
     </row>
-    <row r="210" spans="2:9">
+    <row r="210" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B210" s="5"/>
       <c r="C210" s="5"/>
       <c r="D210" s="5"/>
@@ -4673,7 +4090,7 @@
       <c r="H210" s="5"/>
       <c r="I210" s="5"/>
     </row>
-    <row r="211" spans="2:9">
+    <row r="211" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B211" s="5"/>
       <c r="C211" s="5"/>
       <c r="D211" s="5"/>
@@ -4683,7 +4100,7 @@
       <c r="H211" s="5"/>
       <c r="I211" s="5"/>
     </row>
-    <row r="212" spans="2:9">
+    <row r="212" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B212" s="5"/>
       <c r="C212" s="5"/>
       <c r="D212" s="5"/>
@@ -4693,7 +4110,7 @@
       <c r="H212" s="5"/>
       <c r="I212" s="5"/>
     </row>
-    <row r="213" spans="2:9">
+    <row r="213" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B213" s="5"/>
       <c r="C213" s="5"/>
       <c r="D213" s="5"/>
@@ -4703,7 +4120,7 @@
       <c r="H213" s="5"/>
       <c r="I213" s="5"/>
     </row>
-    <row r="214" spans="2:9">
+    <row r="214" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B214" s="5"/>
       <c r="C214" s="5"/>
       <c r="D214" s="5"/>
@@ -4713,7 +4130,7 @@
       <c r="H214" s="5"/>
       <c r="I214" s="5"/>
     </row>
-    <row r="215" spans="2:9">
+    <row r="215" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B215" s="5"/>
       <c r="C215" s="5"/>
       <c r="D215" s="5"/>
@@ -4723,7 +4140,7 @@
       <c r="H215" s="5"/>
       <c r="I215" s="5"/>
     </row>
-    <row r="216" spans="2:9">
+    <row r="216" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B216" s="5"/>
       <c r="C216" s="5"/>
       <c r="D216" s="5"/>
@@ -4735,2673 +4152,2696 @@
     </row>
   </sheetData>
   <sortState ref="A1:A216">
-    <sortCondition ref="A1"/>
+    <sortCondition ref="A124"/>
   </sortState>
-  <conditionalFormatting sqref="A$1:A$1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <conditionalFormatting sqref="A1:A183 A192:A1048576">
+    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A191:A1048576 A189 A1:A187">
+    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="A15" r:id="rId1" display="BWET" tooltip="https://etfdb.com/etf/BWET/"/>
-    <hyperlink ref="A58" r:id="rId2" display="HYDR" tooltip="https://etfdb.com/etf/HYDR/"/>
-    <hyperlink ref="A41" r:id="rId3" display="EWY" tooltip="https://etfdb.com/etf/EWY/"/>
-    <hyperlink ref="A44" r:id="rId4" display="FLKR" tooltip="https://etfdb.com/etf/FLKR/"/>
-    <hyperlink ref="A51" r:id="rId5" display="FTXL" tooltip="https://etfdb.com/etf/FTXL/"/>
-    <hyperlink ref="A95" r:id="rId6" display="PSI" tooltip="https://etfdb.com/etf/PSI/"/>
-    <hyperlink ref="A104" r:id="rId7" display="REMX" tooltip="https://etfdb.com/etf/REMX/"/>
-    <hyperlink ref="A122" r:id="rId8" display="SOXX" tooltip="https://etfdb.com/etf/SOXX/"/>
-    <hyperlink ref="A181" r:id="rId9" display="XSD" tooltip="https://etfdb.com/etf/XSD/"/>
-    <hyperlink ref="A121" r:id="rId10" display="SOXQ" tooltip="https://etfdb.com/etf/SOXQ/"/>
-    <hyperlink ref="A8" r:id="rId11" display="BBC" tooltip="https://etfdb.com/etf/BBC/"/>
-    <hyperlink ref="A116" r:id="rId12" display="SLVP" tooltip="https://etfdb.com/etf/SLVP/"/>
-    <hyperlink ref="A112" r:id="rId13" display="SHOC" tooltip="https://etfdb.com/etf/SHOC/"/>
-    <hyperlink ref="A86" r:id="rId14" display="PBW" tooltip="https://etfdb.com/etf/PBW/"/>
-    <hyperlink ref="A139" r:id="rId15" display="UFO" tooltip="https://etfdb.com/etf/UFO/"/>
-    <hyperlink ref="A24" r:id="rId16" display="CTEC" tooltip="https://etfdb.com/etf/CTEC/"/>
-    <hyperlink ref="A21" r:id="rId17" display="COPX" tooltip="https://etfdb.com/etf/COPX/"/>
-    <hyperlink ref="A5" r:id="rId18" display="AIVC" tooltip="https://etfdb.com/etf/AIVC/"/>
-    <hyperlink ref="A25" r:id="rId19" display="CTEX" tooltip="https://etfdb.com/etf/CTEX/"/>
-    <hyperlink ref="A182" r:id="rId20" display="XTL" tooltip="https://etfdb.com/etf/XTL/"/>
-    <hyperlink ref="A80" r:id="rId21" display="MNRS" tooltip="https://etfdb.com/etf/MNRS/"/>
-    <hyperlink ref="A144" r:id="rId22" display="URA" tooltip="https://etfdb.com/etf/URA/"/>
-    <hyperlink ref="A130" r:id="rId23" display="TINY" tooltip="https://etfdb.com/etf/TINY/"/>
-    <hyperlink ref="A66" r:id="rId24" display="IGPT" tooltip="https://etfdb.com/etf/IGPT/"/>
-    <hyperlink ref="A20" r:id="rId25" display="CNXT" tooltip="https://etfdb.com/etf/CNXT/"/>
-    <hyperlink ref="A106" r:id="rId26" display="ROKT" tooltip="https://etfdb.com/etf/ROKT/"/>
-    <hyperlink ref="A16" r:id="rId27" display="CARZ" tooltip="https://etfdb.com/etf/CARZ/"/>
-    <hyperlink ref="A98" r:id="rId28" display="QCLN" tooltip="https://etfdb.com/etf/QCLN/"/>
-    <hyperlink ref="A166" r:id="rId29" display="XES" tooltip="https://etfdb.com/etf/XES/"/>
-    <hyperlink ref="A54" r:id="rId30" display="GOEX" tooltip="https://etfdb.com/etf/GOEX/"/>
-    <hyperlink ref="A53" r:id="rId31" display="GDXJ" tooltip="https://etfdb.com/etf/GDXJ/"/>
-    <hyperlink ref="A45" r:id="rId32" display="FLTW" tooltip="https://etfdb.com/etf/FLTW/"/>
-    <hyperlink ref="A19" r:id="rId33" display="CNRG" tooltip="https://etfdb.com/etf/CNRG/"/>
-    <hyperlink ref="A96" r:id="rId34" display="PTF" tooltip="https://etfdb.com/etf/PTF/"/>
-    <hyperlink ref="A105" r:id="rId35" display="RING" tooltip="https://etfdb.com/etf/RING/"/>
-    <hyperlink ref="A109" r:id="rId36" display="SBIO" tooltip="https://etfdb.com/etf/SBIO/"/>
-    <hyperlink ref="A97" r:id="rId37" display="PXJ" tooltip="https://etfdb.com/etf/PXJ/"/>
-    <hyperlink ref="A110" r:id="rId38" display="SGDJ" tooltip="https://etfdb.com/etf/SGDJ/"/>
-    <hyperlink ref="A84" r:id="rId39" display="OIH" tooltip="https://etfdb.com/etf/OIH/"/>
-    <hyperlink ref="A85" r:id="rId40" display="PBD" tooltip="https://etfdb.com/etf/PBD/"/>
-    <hyperlink ref="A40" r:id="rId41" display="EWT" tooltip="https://etfdb.com/etf/EWT/"/>
-    <hyperlink ref="A94" r:id="rId42" display="PSCT" tooltip="https://etfdb.com/etf/PSCT/"/>
-    <hyperlink ref="A3" r:id="rId43" display="AIA" tooltip="https://etfdb.com/etf/AIA/"/>
-    <hyperlink ref="A50" r:id="rId44" display="FRNW" tooltip="https://etfdb.com/etf/FRNW/"/>
-    <hyperlink ref="A61" r:id="rId45" display="IBLC" tooltip="https://etfdb.com/etf/IBLC/"/>
-    <hyperlink ref="A31" r:id="rId46" display="DRIV" tooltip="https://etfdb.com/etf/DRIV/"/>
-    <hyperlink ref="A26" r:id="rId47" display="DAPP" tooltip="https://etfdb.com/etf/DAPP/"/>
-    <hyperlink ref="A65" r:id="rId48" display="IEZ" tooltip="https://etfdb.com/etf/IEZ/"/>
-    <hyperlink ref="A126" r:id="rId49" display="STCE" tooltip="https://etfdb.com/etf/STCE/"/>
-    <hyperlink ref="A136" r:id="rId50" display="TRFK" tooltip="https://etfdb.com/etf/TRFK/"/>
-    <hyperlink ref="A37" r:id="rId51" display="EPU" tooltip="https://etfdb.com/etf/EPU/"/>
-    <hyperlink ref="A49" r:id="rId52" display="FRDM" tooltip="https://etfdb.com/etf/FRDM/"/>
-    <hyperlink ref="A102" r:id="rId53" display="QQQS" tooltip="https://etfdb.com/etf/QQQS/"/>
-    <hyperlink ref="A103" r:id="rId54" display="QTUM" tooltip="https://etfdb.com/etf/QTUM/"/>
-    <hyperlink ref="A111" r:id="rId55" display="SGDM" tooltip="https://etfdb.com/etf/SGDM/"/>
-    <hyperlink ref="A7" r:id="rId56" display="AUMI" tooltip="https://etfdb.com/etf/AUMI/"/>
-    <hyperlink ref="A48" r:id="rId57" display="FPA" tooltip="https://etfdb.com/etf/FPA/"/>
-    <hyperlink ref="A71" r:id="rId58" display="KNCT" tooltip="https://etfdb.com/etf/KNCT/"/>
-    <hyperlink ref="A32" r:id="rId59" display="DTCR" tooltip="https://etfdb.com/etf/DTCR/"/>
-    <hyperlink ref="A73" r:id="rId60" display="KSTR" tooltip="https://etfdb.com/etf/KSTR/"/>
-    <hyperlink ref="A63" r:id="rId61" display="ICLN" tooltip="https://etfdb.com/etf/ICLN/"/>
-    <hyperlink ref="A11" r:id="rId62" display="BITQ" tooltip="https://etfdb.com/etf/BITQ/"/>
-    <hyperlink ref="A156" r:id="rId63" display="VLUE" tooltip="https://etfdb.com/etf/VLUE/"/>
-    <hyperlink ref="A118" r:id="rId64" display="SLX" tooltip="https://etfdb.com/etf/SLX/"/>
-    <hyperlink ref="A69" r:id="rId65" display="KARS" tooltip="https://etfdb.com/etf/KARS/"/>
-    <hyperlink ref="A4" r:id="rId66" display="AIRR" tooltip="https://etfdb.com/etf/AIRR/"/>
-    <hyperlink ref="A23" r:id="rId67" display="CSD" tooltip="https://etfdb.com/etf/CSD/"/>
-    <hyperlink ref="A22" r:id="rId68" display="CRAK" tooltip="https://etfdb.com/etf/CRAK/"/>
-    <hyperlink ref="A165" r:id="rId69" display="XBI" tooltip="https://etfdb.com/etf/XBI/"/>
-    <hyperlink ref="A101" r:id="rId70" display="QQQA" tooltip="https://etfdb.com/etf/QQQA/"/>
-    <hyperlink ref="A70" r:id="rId71" display="KEMX" tooltip="https://etfdb.com/etf/KEMX/"/>
-    <hyperlink ref="A76" r:id="rId72" display="LOUP" tooltip="https://etfdb.com/etf/LOUP/"/>
-    <hyperlink ref="A90" r:id="rId73" display="PIE" tooltip="https://etfdb.com/etf/PIE/"/>
-    <hyperlink ref="A36" r:id="rId74" display="EMXC" tooltip="https://etfdb.com/etf/EMXC/"/>
-    <hyperlink ref="A91" r:id="rId75" display="PRN" tooltip="https://etfdb.com/etf/PRN/"/>
-    <hyperlink ref="A13" r:id="rId76" display="BOAT" tooltip="https://etfdb.com/etf/BOAT/"/>
-    <hyperlink ref="A123" r:id="rId77" display="SPHB" tooltip="https://etfdb.com/etf/SPHB/"/>
-    <hyperlink ref="A92" r:id="rId78" display="PSCE" tooltip="https://etfdb.com/etf/PSCE/"/>
-    <hyperlink ref="A68" r:id="rId79" display="IXN" tooltip="https://etfdb.com/etf/IXN/"/>
-    <hyperlink ref="A129" r:id="rId80" display="THNQ" tooltip="https://etfdb.com/etf/THNQ/"/>
-    <hyperlink ref="A42" r:id="rId81" display="FAN" tooltip="https://etfdb.com/etf/FAN/"/>
-    <hyperlink ref="A62" r:id="rId82" display="IBRN" tooltip="https://etfdb.com/etf/IBRN/"/>
-    <hyperlink ref="A157" r:id="rId83" display="VNAM" tooltip="https://etfdb.com/etf/VNAM/"/>
-    <hyperlink ref="A93" r:id="rId84" display="PSCM" tooltip="https://etfdb.com/etf/PSCM/"/>
-    <hyperlink ref="A83" r:id="rId85" display="NXTG" tooltip="https://etfdb.com/etf/NXTG/"/>
-    <hyperlink ref="A180" r:id="rId86" display="XNTK" tooltip="https://etfdb.com/etf/XNTK/"/>
-    <hyperlink ref="A35" r:id="rId87" display="EIS" tooltip="https://etfdb.com/etf/EIS/"/>
-    <hyperlink ref="A2" r:id="rId88" display="AGEM" tooltip="https://etfdb.com/etf/AGEM/"/>
-    <hyperlink ref="A6" r:id="rId89" display="ASHS" tooltip="https://etfdb.com/etf/ASHS/"/>
-    <hyperlink ref="A43" r:id="rId90" display="FDTS" tooltip="https://etfdb.com/etf/FDTS/"/>
+    <hyperlink ref="A15" r:id="rId1" tooltip="https://etfdb.com/etf/BWET/"/>
+    <hyperlink ref="A56" r:id="rId2" tooltip="https://etfdb.com/etf/HYDR/"/>
+    <hyperlink ref="A41" r:id="rId3" tooltip="https://etfdb.com/etf/EWY/"/>
+    <hyperlink ref="A44" r:id="rId4" tooltip="https://etfdb.com/etf/FLKR/"/>
+    <hyperlink ref="A50" r:id="rId5" tooltip="https://etfdb.com/etf/FTXL/"/>
+    <hyperlink ref="A92" r:id="rId6" tooltip="https://etfdb.com/etf/PSI/"/>
+    <hyperlink ref="A102" r:id="rId7" tooltip="https://etfdb.com/etf/REMX/"/>
+    <hyperlink ref="A119" r:id="rId8" tooltip="https://etfdb.com/etf/SOXX/"/>
+    <hyperlink ref="A174" r:id="rId9" tooltip="https://etfdb.com/etf/XSD/"/>
+    <hyperlink ref="A118" r:id="rId10" tooltip="https://etfdb.com/etf/SOXQ/"/>
+    <hyperlink ref="A8" r:id="rId11" tooltip="https://etfdb.com/etf/BBC/"/>
+    <hyperlink ref="A114" r:id="rId12" tooltip="https://etfdb.com/etf/SLVP/"/>
+    <hyperlink ref="A110" r:id="rId13" tooltip="https://etfdb.com/etf/SHOC/"/>
+    <hyperlink ref="A83" r:id="rId14" tooltip="https://etfdb.com/etf/PBW/"/>
+    <hyperlink ref="A133" r:id="rId15" tooltip="https://etfdb.com/etf/UFO/"/>
+    <hyperlink ref="A24" r:id="rId16" tooltip="https://etfdb.com/etf/CTEC/"/>
+    <hyperlink ref="A21" r:id="rId17" tooltip="https://etfdb.com/etf/COPX/"/>
+    <hyperlink ref="A5" r:id="rId18" tooltip="https://etfdb.com/etf/AIVC/"/>
+    <hyperlink ref="A25" r:id="rId19" tooltip="https://etfdb.com/etf/CTEX/"/>
+    <hyperlink ref="A175" r:id="rId20" tooltip="https://etfdb.com/etf/XTL/"/>
+    <hyperlink ref="A77" r:id="rId21" tooltip="https://etfdb.com/etf/MNRS/"/>
+    <hyperlink ref="A137" r:id="rId22" tooltip="https://etfdb.com/etf/URA/"/>
+    <hyperlink ref="A127" r:id="rId23" tooltip="https://etfdb.com/etf/TINY/"/>
+    <hyperlink ref="A64" r:id="rId24" tooltip="https://etfdb.com/etf/IGPT/"/>
+    <hyperlink ref="A20" r:id="rId25" tooltip="https://etfdb.com/etf/CNXT/"/>
+    <hyperlink ref="A104" r:id="rId26" tooltip="https://etfdb.com/etf/ROKT/"/>
+    <hyperlink ref="A16" r:id="rId27" tooltip="https://etfdb.com/etf/CARZ/"/>
+    <hyperlink ref="A96" r:id="rId28" tooltip="https://etfdb.com/etf/QCLN/"/>
+    <hyperlink ref="A159" r:id="rId29" tooltip="https://etfdb.com/etf/XES/"/>
+    <hyperlink ref="A53" r:id="rId30" tooltip="https://etfdb.com/etf/GOEX/"/>
+    <hyperlink ref="A52" r:id="rId31" tooltip="https://etfdb.com/etf/GDXJ/"/>
+    <hyperlink ref="A45" r:id="rId32" tooltip="https://etfdb.com/etf/FLTW/"/>
+    <hyperlink ref="A19" r:id="rId33" tooltip="https://etfdb.com/etf/CNRG/"/>
+    <hyperlink ref="A94" r:id="rId34" tooltip="https://etfdb.com/etf/PTF/"/>
+    <hyperlink ref="A103" r:id="rId35" tooltip="https://etfdb.com/etf/RING/"/>
+    <hyperlink ref="A107" r:id="rId36" tooltip="https://etfdb.com/etf/SBIO/"/>
+    <hyperlink ref="A95" r:id="rId37" tooltip="https://etfdb.com/etf/PXJ/"/>
+    <hyperlink ref="A108" r:id="rId38" tooltip="https://etfdb.com/etf/SGDJ/"/>
+    <hyperlink ref="A81" r:id="rId39" tooltip="https://etfdb.com/etf/OIH/"/>
+    <hyperlink ref="A82" r:id="rId40" tooltip="https://etfdb.com/etf/PBD/"/>
+    <hyperlink ref="A40" r:id="rId41" tooltip="https://etfdb.com/etf/EWT/"/>
+    <hyperlink ref="A91" r:id="rId42" tooltip="https://etfdb.com/etf/PSCT/"/>
+    <hyperlink ref="A3" r:id="rId43" tooltip="https://etfdb.com/etf/AIA/"/>
+    <hyperlink ref="A49" r:id="rId44" tooltip="https://etfdb.com/etf/FRNW/"/>
+    <hyperlink ref="A59" r:id="rId45" tooltip="https://etfdb.com/etf/IBLC/"/>
+    <hyperlink ref="A31" r:id="rId46" tooltip="https://etfdb.com/etf/DRIV/"/>
+    <hyperlink ref="A26" r:id="rId47" tooltip="https://etfdb.com/etf/DAPP/"/>
+    <hyperlink ref="A63" r:id="rId48" tooltip="https://etfdb.com/etf/IEZ/"/>
+    <hyperlink ref="A124" r:id="rId49" tooltip="https://etfdb.com/etf/STCE/"/>
+    <hyperlink ref="A130" r:id="rId50" tooltip="https://etfdb.com/etf/TRFK/"/>
+    <hyperlink ref="A37" r:id="rId51" tooltip="https://etfdb.com/etf/EPU/"/>
+    <hyperlink ref="A48" r:id="rId52" tooltip="https://etfdb.com/etf/FRDM/"/>
+    <hyperlink ref="A100" r:id="rId53" tooltip="https://etfdb.com/etf/QQQS/"/>
+    <hyperlink ref="A101" r:id="rId54" tooltip="https://etfdb.com/etf/QTUM/"/>
+    <hyperlink ref="A109" r:id="rId55" tooltip="https://etfdb.com/etf/SGDM/"/>
+    <hyperlink ref="A7" r:id="rId56" tooltip="https://etfdb.com/etf/AUMI/"/>
+    <hyperlink ref="A47" r:id="rId57" tooltip="https://etfdb.com/etf/FPA/"/>
+    <hyperlink ref="A69" r:id="rId58" tooltip="https://etfdb.com/etf/KNCT/"/>
+    <hyperlink ref="A32" r:id="rId59" tooltip="https://etfdb.com/etf/DTCR/"/>
+    <hyperlink ref="A61" r:id="rId60" tooltip="https://etfdb.com/etf/ICLN/"/>
+    <hyperlink ref="A11" r:id="rId61" tooltip="https://etfdb.com/etf/BITQ/"/>
+    <hyperlink ref="A149" r:id="rId62" tooltip="https://etfdb.com/etf/VLUE/"/>
+    <hyperlink ref="A116" r:id="rId63" tooltip="https://etfdb.com/etf/SLX/"/>
+    <hyperlink ref="A67" r:id="rId64" tooltip="https://etfdb.com/etf/KARS/"/>
+    <hyperlink ref="A4" r:id="rId65" tooltip="https://etfdb.com/etf/AIRR/"/>
+    <hyperlink ref="A23" r:id="rId66" tooltip="https://etfdb.com/etf/CSD/"/>
+    <hyperlink ref="A22" r:id="rId67" tooltip="https://etfdb.com/etf/CRAK/"/>
+    <hyperlink ref="A158" r:id="rId68" tooltip="https://etfdb.com/etf/XBI/"/>
+    <hyperlink ref="A99" r:id="rId69" tooltip="https://etfdb.com/etf/QQQA/"/>
+    <hyperlink ref="A68" r:id="rId70" tooltip="https://etfdb.com/etf/KEMX/"/>
+    <hyperlink ref="A73" r:id="rId71" tooltip="https://etfdb.com/etf/LOUP/"/>
+    <hyperlink ref="A87" r:id="rId72" tooltip="https://etfdb.com/etf/PIE/"/>
+    <hyperlink ref="A36" r:id="rId73" tooltip="https://etfdb.com/etf/EMXC/"/>
+    <hyperlink ref="A88" r:id="rId74" tooltip="https://etfdb.com/etf/PRN/"/>
+    <hyperlink ref="A13" r:id="rId75" tooltip="https://etfdb.com/etf/BOAT/"/>
+    <hyperlink ref="A120" r:id="rId76" tooltip="https://etfdb.com/etf/SPHB/"/>
+    <hyperlink ref="A89" r:id="rId77" tooltip="https://etfdb.com/etf/PSCE/"/>
+    <hyperlink ref="A66" r:id="rId78" tooltip="https://etfdb.com/etf/IXN/"/>
+    <hyperlink ref="A126" r:id="rId79" tooltip="https://etfdb.com/etf/THNQ/"/>
+    <hyperlink ref="A42" r:id="rId80" tooltip="https://etfdb.com/etf/FAN/"/>
+    <hyperlink ref="A60" r:id="rId81" tooltip="https://etfdb.com/etf/IBRN/"/>
+    <hyperlink ref="A150" r:id="rId82" tooltip="https://etfdb.com/etf/VNAM/"/>
+    <hyperlink ref="A90" r:id="rId83" tooltip="https://etfdb.com/etf/PSCM/"/>
+    <hyperlink ref="A80" r:id="rId84" tooltip="https://etfdb.com/etf/NXTG/"/>
+    <hyperlink ref="A173" r:id="rId85" tooltip="https://etfdb.com/etf/XNTK/"/>
+    <hyperlink ref="A35" r:id="rId86" tooltip="https://etfdb.com/etf/EIS/"/>
+    <hyperlink ref="A2" r:id="rId87" tooltip="https://etfdb.com/etf/AGEM/"/>
+    <hyperlink ref="A6" r:id="rId88" tooltip="https://etfdb.com/etf/ASHS/"/>
+    <hyperlink ref="A43" r:id="rId89" tooltip="https://etfdb.com/etf/FDTS/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F430"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="13.1428571428571" customWidth="1"/>
+    <col min="5" max="5" width="13.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B2" t="s">
+        <v>317</v>
+      </c>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>319</v>
+      </c>
+      <c r="B3" t="s">
+        <v>317</v>
+      </c>
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>320</v>
+      </c>
+      <c r="B4" t="s">
+        <v>317</v>
+      </c>
+      <c r="F4" s="1"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>321</v>
+      </c>
+      <c r="B5" t="s">
+        <v>317</v>
+      </c>
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>322</v>
+      </c>
+      <c r="B6" t="s">
+        <v>317</v>
+      </c>
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>323</v>
+      </c>
+      <c r="B7" t="s">
+        <v>317</v>
+      </c>
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>324</v>
+      </c>
+      <c r="B8" t="s">
+        <v>317</v>
+      </c>
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>325</v>
+      </c>
+      <c r="B9" t="s">
+        <v>317</v>
+      </c>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>326</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B10" t="s">
+        <v>317</v>
+      </c>
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>328</v>
       </c>
-      <c r="B2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F2" s="1"/>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
+      <c r="B12" t="s">
+        <v>317</v>
+      </c>
+      <c r="F12" s="1"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>329</v>
       </c>
-      <c r="B3" t="s">
-        <v>327</v>
-      </c>
-      <c r="F3" s="1"/>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
+      <c r="B13" t="s">
+        <v>317</v>
+      </c>
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>330</v>
       </c>
-      <c r="B4" t="s">
-        <v>327</v>
-      </c>
-      <c r="F4" s="1"/>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
+      <c r="B14" t="s">
+        <v>317</v>
+      </c>
+      <c r="F14" s="1"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>331</v>
       </c>
-      <c r="B5" t="s">
-        <v>327</v>
-      </c>
-      <c r="F5" s="1"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
+      <c r="F15" s="1"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>332</v>
       </c>
-      <c r="B6" t="s">
-        <v>327</v>
-      </c>
-      <c r="F6" s="1"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
+      <c r="B16" t="s">
+        <v>317</v>
+      </c>
+      <c r="F16" s="1"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="B7" t="s">
-        <v>327</v>
-      </c>
-      <c r="F7" s="1"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
+      <c r="F17" s="1"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="B8" t="s">
-        <v>327</v>
-      </c>
-      <c r="F8" s="1"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
+      <c r="F18" s="1"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>335</v>
       </c>
-      <c r="B9" t="s">
-        <v>327</v>
-      </c>
-      <c r="F9" s="1"/>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
+      <c r="B19" t="s">
+        <v>317</v>
+      </c>
+      <c r="F19" s="1"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>336</v>
       </c>
-      <c r="B10" t="s">
-        <v>327</v>
-      </c>
-      <c r="F10" s="1"/>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" t="s">
+      <c r="B20" t="s">
+        <v>317</v>
+      </c>
+      <c r="F20" s="1"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>337</v>
       </c>
-      <c r="F11" s="1"/>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" t="s">
+      <c r="B21" t="s">
+        <v>317</v>
+      </c>
+      <c r="F21" s="1"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>338</v>
       </c>
-      <c r="B12" t="s">
-        <v>327</v>
-      </c>
-      <c r="F12" s="1"/>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" t="s">
+      <c r="B22" t="s">
+        <v>317</v>
+      </c>
+      <c r="F22" s="1"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>339</v>
       </c>
-      <c r="B13" t="s">
-        <v>327</v>
-      </c>
-      <c r="F13" s="1"/>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" t="s">
+      <c r="B23" t="s">
+        <v>317</v>
+      </c>
+      <c r="F23" s="1"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>340</v>
       </c>
-      <c r="B14" t="s">
-        <v>327</v>
-      </c>
-      <c r="F14" s="1"/>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" t="s">
+      <c r="B24" t="s">
+        <v>317</v>
+      </c>
+      <c r="F24" s="1"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>341</v>
       </c>
-      <c r="F15" s="1"/>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" t="s">
+      <c r="B25" t="s">
+        <v>317</v>
+      </c>
+      <c r="F25" s="1"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="B16" t="s">
-        <v>327</v>
-      </c>
-      <c r="F16" s="1"/>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="2" t="s">
+      <c r="F26" s="1"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>343</v>
       </c>
-      <c r="F17" s="1"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="2" t="s">
+      <c r="B27" t="s">
+        <v>317</v>
+      </c>
+      <c r="F27" s="1"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>344</v>
       </c>
-      <c r="F18" s="1"/>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" t="s">
+      <c r="B28" t="s">
+        <v>317</v>
+      </c>
+      <c r="F28" s="1"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>345</v>
       </c>
-      <c r="B19" t="s">
-        <v>327</v>
-      </c>
-      <c r="F19" s="1"/>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" t="s">
+      <c r="B29" t="s">
+        <v>317</v>
+      </c>
+      <c r="F29" s="1"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>346</v>
       </c>
-      <c r="B20" t="s">
-        <v>327</v>
-      </c>
-      <c r="F20" s="1"/>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" t="s">
+      <c r="B30" t="s">
+        <v>317</v>
+      </c>
+      <c r="F30" s="1"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>347</v>
       </c>
-      <c r="B21" t="s">
-        <v>327</v>
-      </c>
-      <c r="F21" s="1"/>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" t="s">
+      <c r="B31" t="s">
+        <v>317</v>
+      </c>
+      <c r="F31" s="1"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>348</v>
       </c>
-      <c r="B22" t="s">
-        <v>327</v>
-      </c>
-      <c r="F22" s="1"/>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" t="s">
+      <c r="B32" t="s">
+        <v>317</v>
+      </c>
+      <c r="F32" s="1"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>349</v>
       </c>
-      <c r="B23" t="s">
-        <v>327</v>
-      </c>
-      <c r="F23" s="1"/>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" t="s">
+      <c r="F33" s="1"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>350</v>
       </c>
-      <c r="B24" t="s">
-        <v>327</v>
-      </c>
-      <c r="F24" s="1"/>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" t="s">
+      <c r="B34" t="s">
+        <v>317</v>
+      </c>
+      <c r="F34" s="1"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="B25" t="s">
-        <v>327</v>
-      </c>
-      <c r="F25" s="1"/>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="2" t="s">
+      <c r="F35" s="1"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>352</v>
       </c>
-      <c r="F26" s="1"/>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" t="s">
+      <c r="B36" t="s">
+        <v>317</v>
+      </c>
+      <c r="F36" s="1"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>353</v>
       </c>
-      <c r="B27" t="s">
-        <v>327</v>
-      </c>
-      <c r="F27" s="1"/>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" t="s">
+      <c r="B37" t="s">
+        <v>317</v>
+      </c>
+      <c r="F37" s="1"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>354</v>
       </c>
-      <c r="B28" t="s">
-        <v>327</v>
-      </c>
-      <c r="F28" s="1"/>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" t="s">
+      <c r="B38" t="s">
+        <v>317</v>
+      </c>
+      <c r="F38" s="1"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>355</v>
       </c>
-      <c r="B29" t="s">
-        <v>327</v>
-      </c>
-      <c r="F29" s="1"/>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" t="s">
+      <c r="B39" t="s">
+        <v>317</v>
+      </c>
+      <c r="F39" s="1"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>356</v>
       </c>
-      <c r="B30" t="s">
-        <v>327</v>
-      </c>
-      <c r="F30" s="1"/>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" t="s">
+      <c r="B40" t="s">
+        <v>317</v>
+      </c>
+      <c r="F40" s="1"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="B31" t="s">
-        <v>327</v>
-      </c>
-      <c r="F31" s="1"/>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" t="s">
+      <c r="F41" s="1"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>358</v>
       </c>
-      <c r="B32" t="s">
-        <v>327</v>
-      </c>
-      <c r="F32" s="1"/>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" t="s">
+      <c r="B42" t="s">
+        <v>317</v>
+      </c>
+      <c r="F42" s="1"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>359</v>
       </c>
-      <c r="F33" s="1"/>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" t="s">
+      <c r="B43" t="s">
+        <v>317</v>
+      </c>
+      <c r="F43" s="1"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>360</v>
       </c>
-      <c r="B34" t="s">
-        <v>327</v>
-      </c>
-      <c r="F34" s="1"/>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="2" t="s">
+      <c r="F44" s="1"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>361</v>
       </c>
-      <c r="F35" s="1"/>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" t="s">
+      <c r="B45" t="s">
+        <v>317</v>
+      </c>
+      <c r="F45" s="1"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
         <v>362</v>
       </c>
-      <c r="B36" t="s">
-        <v>327</v>
-      </c>
-      <c r="F36" s="1"/>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" t="s">
+      <c r="B46" t="s">
+        <v>317</v>
+      </c>
+      <c r="F46" s="1"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
         <v>363</v>
       </c>
-      <c r="B37" t="s">
-        <v>327</v>
-      </c>
-      <c r="F37" s="1"/>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" t="s">
+      <c r="F47" s="1"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
         <v>364</v>
       </c>
-      <c r="B38" t="s">
-        <v>327</v>
-      </c>
-      <c r="F38" s="1"/>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" t="s">
+      <c r="B48" t="s">
+        <v>317</v>
+      </c>
+      <c r="F48" s="1"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
         <v>365</v>
       </c>
-      <c r="B39" t="s">
-        <v>327</v>
-      </c>
-      <c r="F39" s="1"/>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" t="s">
+      <c r="B49" t="s">
+        <v>317</v>
+      </c>
+      <c r="F49" s="1"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
         <v>366</v>
       </c>
-      <c r="B40" t="s">
-        <v>327</v>
-      </c>
-      <c r="F40" s="1"/>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" s="2" t="s">
+      <c r="B50" t="s">
+        <v>317</v>
+      </c>
+      <c r="F50" s="1"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
         <v>367</v>
       </c>
-      <c r="F41" s="1"/>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42" t="s">
+      <c r="B51" t="s">
+        <v>317</v>
+      </c>
+      <c r="F51" s="1"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
         <v>368</v>
       </c>
-      <c r="B42" t="s">
-        <v>327</v>
-      </c>
-      <c r="F42" s="1"/>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43" t="s">
+      <c r="B52" t="s">
+        <v>317</v>
+      </c>
+      <c r="F52" s="1"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
         <v>369</v>
       </c>
-      <c r="B43" t="s">
-        <v>327</v>
-      </c>
-      <c r="F43" s="1"/>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44" t="s">
+      <c r="B53" t="s">
+        <v>317</v>
+      </c>
+      <c r="F53" s="1"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
         <v>370</v>
       </c>
-      <c r="F44" s="1"/>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45" t="s">
+      <c r="B54" t="s">
+        <v>317</v>
+      </c>
+      <c r="F54" s="1"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
         <v>371</v>
       </c>
-      <c r="B45" t="s">
-        <v>327</v>
-      </c>
-      <c r="F45" s="1"/>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46" t="s">
+      <c r="B55" t="s">
+        <v>317</v>
+      </c>
+      <c r="F55" s="1"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
         <v>372</v>
       </c>
-      <c r="B46" t="s">
-        <v>327</v>
-      </c>
-      <c r="F46" s="1"/>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47" t="s">
+      <c r="F56" s="1"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
         <v>373</v>
       </c>
-      <c r="F47" s="1"/>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48" t="s">
+      <c r="B57" t="s">
+        <v>317</v>
+      </c>
+      <c r="F57" s="1"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
         <v>374</v>
       </c>
-      <c r="B48" t="s">
-        <v>327</v>
-      </c>
-      <c r="F48" s="1"/>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49" t="s">
+      <c r="B58" t="s">
+        <v>317</v>
+      </c>
+      <c r="F58" s="1"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
         <v>375</v>
       </c>
-      <c r="B49" t="s">
-        <v>327</v>
-      </c>
-      <c r="F49" s="1"/>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50" t="s">
+      <c r="B59" t="s">
+        <v>317</v>
+      </c>
+      <c r="F59" s="1"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
         <v>376</v>
       </c>
-      <c r="B50" t="s">
-        <v>327</v>
-      </c>
-      <c r="F50" s="1"/>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51" t="s">
+      <c r="B60" t="s">
+        <v>317</v>
+      </c>
+      <c r="F60" s="1"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
         <v>377</v>
       </c>
-      <c r="B51" t="s">
-        <v>327</v>
-      </c>
-      <c r="F51" s="1"/>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52" t="s">
+      <c r="B61" t="s">
+        <v>317</v>
+      </c>
+      <c r="F61" s="1"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
         <v>378</v>
       </c>
-      <c r="B52" t="s">
-        <v>327</v>
-      </c>
-      <c r="F52" s="1"/>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53" t="s">
+      <c r="F62" s="1"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B53" t="s">
-        <v>327</v>
-      </c>
-      <c r="F53" s="1"/>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54" t="s">
+      <c r="F63" s="1"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="B54" t="s">
-        <v>327</v>
-      </c>
-      <c r="F54" s="1"/>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55" t="s">
+      <c r="F64" s="1"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
         <v>381</v>
       </c>
-      <c r="B55" t="s">
-        <v>327</v>
-      </c>
-      <c r="F55" s="1"/>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56" t="s">
+      <c r="B65" t="s">
+        <v>317</v>
+      </c>
+      <c r="F65" s="1"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
         <v>382</v>
       </c>
-      <c r="F56" s="1"/>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57" t="s">
+      <c r="B66" t="s">
+        <v>317</v>
+      </c>
+      <c r="F66" s="1"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
         <v>383</v>
       </c>
-      <c r="B57" t="s">
-        <v>327</v>
-      </c>
-      <c r="F57" s="1"/>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58" t="s">
+      <c r="B67" t="s">
+        <v>317</v>
+      </c>
+      <c r="F67" s="1"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="B58" t="s">
-        <v>327</v>
-      </c>
-      <c r="F58" s="1"/>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59" t="s">
+      <c r="F68" s="1"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
         <v>385</v>
       </c>
-      <c r="B59" t="s">
-        <v>327</v>
-      </c>
-      <c r="F59" s="1"/>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60" t="s">
+      <c r="B69" t="s">
+        <v>317</v>
+      </c>
+      <c r="F69" s="1"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
         <v>386</v>
       </c>
-      <c r="B60" t="s">
-        <v>327</v>
-      </c>
-      <c r="F60" s="1"/>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61" t="s">
+      <c r="B70" t="s">
+        <v>317</v>
+      </c>
+      <c r="F70" s="1"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
         <v>387</v>
       </c>
-      <c r="B61" t="s">
-        <v>327</v>
-      </c>
-      <c r="F61" s="1"/>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62" t="s">
+      <c r="B71" t="s">
+        <v>317</v>
+      </c>
+      <c r="F71" s="1"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A72" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="F62" s="1"/>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63" s="2" t="s">
+      <c r="F72" s="1"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
         <v>389</v>
       </c>
-      <c r="F63" s="1"/>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64" s="2" t="s">
+      <c r="B73" t="s">
+        <v>317</v>
+      </c>
+      <c r="F73" s="1"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
         <v>390</v>
       </c>
-      <c r="F64" s="1"/>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65" t="s">
+      <c r="B74" t="s">
+        <v>317</v>
+      </c>
+      <c r="F74" s="1"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
         <v>391</v>
       </c>
-      <c r="B65" t="s">
-        <v>327</v>
-      </c>
-      <c r="F65" s="1"/>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66" t="s">
+      <c r="F75" s="1"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="B66" t="s">
-        <v>327</v>
-      </c>
-      <c r="F66" s="1"/>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67" t="s">
+      <c r="F76" s="1"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
         <v>393</v>
       </c>
-      <c r="B67" t="s">
-        <v>327</v>
-      </c>
-      <c r="F67" s="1"/>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68" s="2" t="s">
+      <c r="B77" t="s">
+        <v>317</v>
+      </c>
+      <c r="F77" s="1"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>394</v>
       </c>
-      <c r="F68" s="1"/>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69" t="s">
+      <c r="B78" t="s">
+        <v>317</v>
+      </c>
+      <c r="F78" s="1"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>395</v>
       </c>
-      <c r="B69" t="s">
-        <v>327</v>
-      </c>
-      <c r="F69" s="1"/>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70" t="s">
+      <c r="B79" t="s">
+        <v>317</v>
+      </c>
+      <c r="F79" s="1"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
         <v>396</v>
       </c>
-      <c r="B70" t="s">
-        <v>327</v>
-      </c>
-      <c r="F70" s="1"/>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71" t="s">
+      <c r="B80" t="s">
+        <v>317</v>
+      </c>
+      <c r="F80" s="1"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
         <v>397</v>
       </c>
-      <c r="B71" t="s">
-        <v>327</v>
-      </c>
-      <c r="F71" s="1"/>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72" s="2" t="s">
+      <c r="B81" t="s">
+        <v>317</v>
+      </c>
+      <c r="F81" s="1"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
         <v>398</v>
       </c>
-      <c r="F72" s="1"/>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73" t="s">
+      <c r="B82" t="s">
+        <v>317</v>
+      </c>
+      <c r="F82" s="1"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
         <v>399</v>
       </c>
-      <c r="B73" t="s">
-        <v>327</v>
-      </c>
-      <c r="F73" s="1"/>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74" t="s">
+      <c r="B83" t="s">
+        <v>317</v>
+      </c>
+      <c r="F83" s="1"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
         <v>400</v>
       </c>
-      <c r="B74" t="s">
-        <v>327</v>
-      </c>
-      <c r="F74" s="1"/>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75" t="s">
+      <c r="B84" t="s">
+        <v>317</v>
+      </c>
+      <c r="F84" s="1"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
         <v>401</v>
       </c>
-      <c r="F75" s="1"/>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76" s="2" t="s">
+      <c r="B85" t="s">
+        <v>317</v>
+      </c>
+      <c r="F85" s="1"/>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
         <v>402</v>
       </c>
-      <c r="F76" s="1"/>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77" t="s">
+      <c r="B86" t="s">
+        <v>317</v>
+      </c>
+      <c r="F86" s="1"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
         <v>403</v>
       </c>
-      <c r="B77" t="s">
-        <v>327</v>
-      </c>
-      <c r="F77" s="1"/>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78" t="s">
+      <c r="B87" t="s">
+        <v>317</v>
+      </c>
+      <c r="F87" s="1"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
         <v>404</v>
       </c>
-      <c r="B78" t="s">
-        <v>327</v>
-      </c>
-      <c r="F78" s="1"/>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79" t="s">
+      <c r="F88" s="1"/>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
         <v>405</v>
       </c>
-      <c r="B79" t="s">
-        <v>327</v>
-      </c>
-      <c r="F79" s="1"/>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80" t="s">
+      <c r="B89" t="s">
+        <v>317</v>
+      </c>
+      <c r="F89" s="1"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
         <v>406</v>
       </c>
-      <c r="B80" t="s">
-        <v>327</v>
-      </c>
-      <c r="F80" s="1"/>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81" t="s">
+      <c r="B90" t="s">
+        <v>317</v>
+      </c>
+      <c r="F90" s="1"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
         <v>407</v>
       </c>
-      <c r="B81" t="s">
-        <v>327</v>
-      </c>
-      <c r="F81" s="1"/>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82" t="s">
+      <c r="B91" t="s">
+        <v>317</v>
+      </c>
+      <c r="F91" s="1"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="B82" t="s">
-        <v>327</v>
-      </c>
-      <c r="F82" s="1"/>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83" t="s">
+      <c r="F92" s="1"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
         <v>409</v>
       </c>
-      <c r="B83" t="s">
-        <v>327</v>
-      </c>
-      <c r="F83" s="1"/>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84" t="s">
+      <c r="B93" t="s">
+        <v>317</v>
+      </c>
+      <c r="F93" s="1"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
         <v>410</v>
       </c>
-      <c r="B84" t="s">
-        <v>327</v>
-      </c>
-      <c r="F84" s="1"/>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85" t="s">
+      <c r="F94" s="1"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="B85" t="s">
-        <v>327</v>
-      </c>
-      <c r="F85" s="1"/>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86" t="s">
+      <c r="F95" s="1"/>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
         <v>412</v>
       </c>
-      <c r="B86" t="s">
-        <v>327</v>
-      </c>
-      <c r="F86" s="1"/>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87" t="s">
+      <c r="F96" s="1"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
         <v>413</v>
       </c>
-      <c r="B87" t="s">
-        <v>327</v>
-      </c>
-      <c r="F87" s="1"/>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88" t="s">
+      <c r="B97" t="s">
+        <v>317</v>
+      </c>
+      <c r="F97" s="1"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
         <v>414</v>
       </c>
-      <c r="F88" s="1"/>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89" t="s">
+      <c r="B98" t="s">
+        <v>317</v>
+      </c>
+      <c r="F98" s="1"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
         <v>415</v>
       </c>
-      <c r="B89" t="s">
-        <v>327</v>
-      </c>
-      <c r="F89" s="1"/>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90" t="s">
+      <c r="F99" s="1"/>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
         <v>416</v>
       </c>
-      <c r="B90" t="s">
-        <v>327</v>
-      </c>
-      <c r="F90" s="1"/>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91" t="s">
+      <c r="F100" s="1"/>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A101" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="B91" t="s">
-        <v>327</v>
-      </c>
-      <c r="F91" s="1"/>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92" s="2" t="s">
+      <c r="F101" s="1"/>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
         <v>418</v>
       </c>
-      <c r="F92" s="1"/>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93" t="s">
+      <c r="B102" t="s">
+        <v>317</v>
+      </c>
+      <c r="F102" s="1"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
         <v>419</v>
       </c>
-      <c r="B93" t="s">
-        <v>327</v>
-      </c>
-      <c r="F93" s="1"/>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94" t="s">
+      <c r="B103" t="s">
+        <v>317</v>
+      </c>
+      <c r="F103" s="1"/>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
         <v>420</v>
       </c>
-      <c r="F94" s="1"/>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95" s="2" t="s">
+      <c r="B104" t="s">
+        <v>317</v>
+      </c>
+      <c r="F104" s="1"/>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
         <v>421</v>
       </c>
-      <c r="F95" s="1"/>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96" t="s">
+      <c r="B105" t="s">
+        <v>317</v>
+      </c>
+      <c r="F105" s="1"/>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
         <v>422</v>
       </c>
-      <c r="F96" s="1"/>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="A97" t="s">
+      <c r="B106" t="s">
+        <v>317</v>
+      </c>
+      <c r="F106" s="1"/>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
         <v>423</v>
       </c>
-      <c r="B97" t="s">
-        <v>327</v>
-      </c>
-      <c r="F97" s="1"/>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="A98" t="s">
+      <c r="B107" t="s">
+        <v>317</v>
+      </c>
+      <c r="F107" s="1"/>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
         <v>424</v>
       </c>
-      <c r="B98" t="s">
-        <v>327</v>
-      </c>
-      <c r="F98" s="1"/>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="A99" t="s">
+      <c r="B108" t="s">
+        <v>317</v>
+      </c>
+      <c r="F108" s="1"/>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="F99" s="1"/>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="A100" t="s">
+      <c r="F109" s="1"/>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
         <v>426</v>
       </c>
-      <c r="F100" s="1"/>
-    </row>
-    <row r="101" spans="1:6">
-      <c r="A101" s="2" t="s">
+      <c r="B110" t="s">
+        <v>317</v>
+      </c>
+      <c r="F110" s="1"/>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
         <v>427</v>
       </c>
-      <c r="F101" s="1"/>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="A102" t="s">
+      <c r="B111" t="s">
+        <v>317</v>
+      </c>
+      <c r="F111" s="1"/>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
         <v>428</v>
       </c>
-      <c r="B102" t="s">
-        <v>327</v>
-      </c>
-      <c r="F102" s="1"/>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="A103" t="s">
+      <c r="F112" s="1"/>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
         <v>429</v>
       </c>
-      <c r="B103" t="s">
-        <v>327</v>
-      </c>
-      <c r="F103" s="1"/>
-    </row>
-    <row r="104" spans="1:6">
-      <c r="A104" t="s">
+      <c r="B113" t="s">
+        <v>317</v>
+      </c>
+      <c r="F113" s="1"/>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
         <v>430</v>
       </c>
-      <c r="B104" t="s">
-        <v>327</v>
-      </c>
-      <c r="F104" s="1"/>
-    </row>
-    <row r="105" spans="1:6">
-      <c r="A105" t="s">
+      <c r="F114" s="1"/>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
         <v>431</v>
       </c>
-      <c r="B105" t="s">
-        <v>327</v>
-      </c>
-      <c r="F105" s="1"/>
-    </row>
-    <row r="106" spans="1:6">
-      <c r="A106" t="s">
+      <c r="B115" t="s">
+        <v>317</v>
+      </c>
+      <c r="F115" s="1"/>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A116" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="B106" t="s">
-        <v>327</v>
-      </c>
-      <c r="F106" s="1"/>
-    </row>
-    <row r="107" spans="1:6">
-      <c r="A107" t="s">
+      <c r="F116" s="1"/>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
         <v>433</v>
       </c>
-      <c r="B107" t="s">
-        <v>327</v>
-      </c>
-      <c r="F107" s="1"/>
-    </row>
-    <row r="108" spans="1:6">
-      <c r="A108" t="s">
+      <c r="B117" t="s">
+        <v>317</v>
+      </c>
+      <c r="F117" s="1"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
         <v>434</v>
       </c>
-      <c r="B108" t="s">
-        <v>327</v>
-      </c>
-      <c r="F108" s="1"/>
-    </row>
-    <row r="109" spans="1:6">
-      <c r="A109" s="3" t="s">
+      <c r="F118" s="1"/>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
         <v>435</v>
       </c>
-      <c r="F109" s="1"/>
-    </row>
-    <row r="110" spans="1:6">
-      <c r="A110" t="s">
+      <c r="F119" s="1"/>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
         <v>436</v>
       </c>
-      <c r="B110" t="s">
-        <v>327</v>
-      </c>
-      <c r="F110" s="1"/>
-    </row>
-    <row r="111" spans="1:6">
-      <c r="A111" t="s">
+      <c r="B120" t="s">
+        <v>317</v>
+      </c>
+      <c r="F120" s="1"/>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
         <v>437</v>
       </c>
-      <c r="B111" t="s">
-        <v>327</v>
-      </c>
-      <c r="F111" s="1"/>
-    </row>
-    <row r="112" spans="1:6">
-      <c r="A112" t="s">
+      <c r="B121" t="s">
+        <v>317</v>
+      </c>
+      <c r="F121" s="1"/>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
         <v>438</v>
       </c>
-      <c r="F112" s="1"/>
-    </row>
-    <row r="113" spans="1:6">
-      <c r="A113" t="s">
+      <c r="B122" t="s">
+        <v>317</v>
+      </c>
+      <c r="F122" s="1"/>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
         <v>439</v>
       </c>
-      <c r="B113" t="s">
-        <v>327</v>
-      </c>
-      <c r="F113" s="1"/>
-    </row>
-    <row r="114" spans="1:6">
-      <c r="A114" t="s">
+      <c r="B123" t="s">
+        <v>317</v>
+      </c>
+      <c r="F123" s="1"/>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
         <v>440</v>
       </c>
-      <c r="F114" s="1"/>
-    </row>
-    <row r="115" spans="1:6">
-      <c r="A115" t="s">
+      <c r="B124" t="s">
+        <v>317</v>
+      </c>
+      <c r="F124" s="1"/>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
         <v>441</v>
       </c>
-      <c r="B115" t="s">
-        <v>327</v>
-      </c>
-      <c r="F115" s="1"/>
-    </row>
-    <row r="116" spans="1:6">
-      <c r="A116" s="2" t="s">
+      <c r="B125" t="s">
+        <v>317</v>
+      </c>
+      <c r="F125" s="1"/>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
         <v>442</v>
       </c>
-      <c r="F116" s="1"/>
-    </row>
-    <row r="117" spans="1:6">
-      <c r="A117" t="s">
+      <c r="B126" t="s">
+        <v>317</v>
+      </c>
+      <c r="F126" s="1"/>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
         <v>443</v>
       </c>
-      <c r="B117" t="s">
-        <v>327</v>
-      </c>
-      <c r="F117" s="1"/>
-    </row>
-    <row r="118" spans="1:6">
-      <c r="A118" t="s">
+      <c r="B127" t="s">
+        <v>317</v>
+      </c>
+      <c r="F127" s="1"/>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
         <v>444</v>
       </c>
-      <c r="F118" s="1"/>
-    </row>
-    <row r="119" spans="1:6">
-      <c r="A119" t="s">
+      <c r="B128" t="s">
+        <v>317</v>
+      </c>
+      <c r="F128" s="1"/>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
         <v>445</v>
       </c>
-      <c r="F119" s="1"/>
-    </row>
-    <row r="120" spans="1:6">
-      <c r="A120" t="s">
+      <c r="B129" t="s">
+        <v>317</v>
+      </c>
+      <c r="F129" s="1"/>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A130" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="B120" t="s">
-        <v>327</v>
-      </c>
-      <c r="F120" s="1"/>
-    </row>
-    <row r="121" spans="1:6">
-      <c r="A121" t="s">
+      <c r="F130" s="1"/>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
         <v>447</v>
       </c>
-      <c r="B121" t="s">
-        <v>327</v>
-      </c>
-      <c r="F121" s="1"/>
-    </row>
-    <row r="122" spans="1:6">
-      <c r="A122" t="s">
+      <c r="B131" t="s">
+        <v>317</v>
+      </c>
+      <c r="F131" s="1"/>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A132" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="B122" t="s">
-        <v>327</v>
-      </c>
-      <c r="F122" s="1"/>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="A123" t="s">
+      <c r="F132" s="1"/>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
         <v>449</v>
       </c>
-      <c r="B123" t="s">
-        <v>327</v>
-      </c>
-      <c r="F123" s="1"/>
-    </row>
-    <row r="124" spans="1:6">
-      <c r="A124" t="s">
+      <c r="B133" t="s">
+        <v>317</v>
+      </c>
+      <c r="F133" s="1"/>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
         <v>450</v>
       </c>
-      <c r="B124" t="s">
-        <v>327</v>
-      </c>
-      <c r="F124" s="1"/>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="A125" t="s">
+      <c r="B134" t="s">
+        <v>317</v>
+      </c>
+      <c r="F134" s="1"/>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
         <v>451</v>
       </c>
-      <c r="B125" t="s">
-        <v>327</v>
-      </c>
-      <c r="F125" s="1"/>
-    </row>
-    <row r="126" spans="1:6">
-      <c r="A126" t="s">
+      <c r="B135" t="s">
+        <v>317</v>
+      </c>
+      <c r="F135" s="1"/>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A136" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="B126" t="s">
-        <v>327</v>
-      </c>
-      <c r="F126" s="1"/>
-    </row>
-    <row r="127" spans="1:6">
-      <c r="A127" t="s">
-        <v>453</v>
-      </c>
-      <c r="B127" t="s">
-        <v>327</v>
-      </c>
-      <c r="F127" s="1"/>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="A128" t="s">
-        <v>454</v>
-      </c>
-      <c r="B128" t="s">
-        <v>327</v>
-      </c>
-      <c r="F128" s="1"/>
-    </row>
-    <row r="129" spans="1:6">
-      <c r="A129" t="s">
-        <v>455</v>
-      </c>
-      <c r="B129" t="s">
-        <v>327</v>
-      </c>
-      <c r="F129" s="1"/>
-    </row>
-    <row r="130" spans="1:6">
-      <c r="A130" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="F130" s="1"/>
-    </row>
-    <row r="131" spans="1:6">
-      <c r="A131" t="s">
-        <v>457</v>
-      </c>
-      <c r="B131" t="s">
-        <v>327</v>
-      </c>
-      <c r="F131" s="1"/>
-    </row>
-    <row r="132" spans="1:6">
-      <c r="A132" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="F132" s="1"/>
-    </row>
-    <row r="133" spans="1:6">
-      <c r="A133" t="s">
-        <v>459</v>
-      </c>
-      <c r="B133" t="s">
-        <v>327</v>
-      </c>
-      <c r="F133" s="1"/>
-    </row>
-    <row r="134" spans="1:6">
-      <c r="A134" t="s">
-        <v>460</v>
-      </c>
-      <c r="B134" t="s">
-        <v>327</v>
-      </c>
-      <c r="F134" s="1"/>
-    </row>
-    <row r="135" spans="1:6">
-      <c r="A135" t="s">
-        <v>461</v>
-      </c>
-      <c r="B135" t="s">
-        <v>327</v>
-      </c>
-      <c r="F135" s="1"/>
-    </row>
-    <row r="136" spans="1:6">
-      <c r="A136" s="2" t="s">
-        <v>462</v>
-      </c>
       <c r="F136" s="1"/>
     </row>
-    <row r="137" spans="1:6">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A137" s="9" t="s">
+        <v>486</v>
+      </c>
       <c r="F137" s="1"/>
     </row>
-    <row r="138" spans="1:6">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A138" s="9" t="s">
+        <v>487</v>
+      </c>
       <c r="F138" s="1"/>
     </row>
-    <row r="139" spans="1:6">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A139" s="9" t="s">
+        <v>488</v>
+      </c>
       <c r="F139" s="1"/>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F140" s="1"/>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A141" s="9"/>
       <c r="F141" s="1"/>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A142" s="9"/>
       <c r="F142" s="1"/>
     </row>
-    <row r="143" spans="1:6">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143" s="9"/>
       <c r="F143" s="1"/>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A144" s="9"/>
       <c r="F144" s="1"/>
     </row>
-    <row r="145" spans="6:6">
+    <row r="145" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F145" s="1"/>
     </row>
-    <row r="146" spans="6:6">
+    <row r="146" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F146" s="1"/>
     </row>
-    <row r="147" spans="6:6">
+    <row r="147" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F147" s="1"/>
     </row>
-    <row r="148" spans="6:6">
+    <row r="148" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F148" s="1"/>
     </row>
-    <row r="149" spans="6:6">
+    <row r="149" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F149" s="1"/>
     </row>
-    <row r="150" spans="6:6">
+    <row r="150" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F150" s="1"/>
     </row>
-    <row r="151" spans="6:6">
+    <row r="151" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F151" s="1"/>
     </row>
-    <row r="152" spans="6:6">
+    <row r="152" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F152" s="1"/>
     </row>
-    <row r="153" spans="6:6">
+    <row r="153" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F153" s="1"/>
     </row>
-    <row r="154" spans="6:6">
+    <row r="154" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F154" s="1"/>
     </row>
-    <row r="155" spans="6:6">
+    <row r="155" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F155" s="1"/>
     </row>
-    <row r="156" spans="6:6">
+    <row r="156" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F156" s="1"/>
     </row>
-    <row r="157" spans="6:6">
+    <row r="157" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F157" s="1"/>
     </row>
-    <row r="158" spans="6:6">
+    <row r="158" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F158" s="1"/>
     </row>
-    <row r="159" spans="6:6">
+    <row r="159" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F159" s="1"/>
     </row>
-    <row r="160" spans="6:6">
+    <row r="160" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F160" s="1"/>
     </row>
-    <row r="161" spans="6:6">
+    <row r="161" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F161" s="1"/>
     </row>
-    <row r="162" spans="6:6">
+    <row r="162" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F162" s="1"/>
     </row>
-    <row r="163" spans="6:6">
+    <row r="163" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F163" s="1"/>
     </row>
-    <row r="164" spans="6:6">
+    <row r="164" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F164" s="1"/>
     </row>
-    <row r="165" spans="6:6">
+    <row r="165" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F165" s="1"/>
     </row>
-    <row r="166" spans="6:6">
+    <row r="166" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F166" s="1"/>
     </row>
-    <row r="167" spans="6:6">
+    <row r="167" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F167" s="1"/>
     </row>
-    <row r="168" spans="6:6">
+    <row r="168" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F168" s="1"/>
     </row>
-    <row r="169" spans="6:6">
+    <row r="169" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F169" s="1"/>
     </row>
-    <row r="170" spans="6:6">
+    <row r="170" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F170" s="1"/>
     </row>
-    <row r="171" spans="6:6">
+    <row r="171" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F171" s="1"/>
     </row>
-    <row r="172" spans="6:6">
+    <row r="172" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F172" s="1"/>
     </row>
-    <row r="173" spans="6:6">
+    <row r="173" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F173" s="1"/>
     </row>
-    <row r="174" spans="6:6">
+    <row r="174" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F174" s="1"/>
     </row>
-    <row r="175" spans="6:6">
+    <row r="175" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F175" s="1"/>
     </row>
-    <row r="176" spans="6:6">
+    <row r="176" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F176" s="1"/>
     </row>
-    <row r="177" spans="6:6">
+    <row r="177" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F177" s="1"/>
     </row>
-    <row r="178" spans="6:6">
+    <row r="178" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F178" s="1"/>
     </row>
-    <row r="179" spans="6:6">
+    <row r="179" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F179" s="1"/>
     </row>
-    <row r="180" spans="6:6">
+    <row r="180" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F180" s="1"/>
     </row>
-    <row r="181" spans="6:6">
+    <row r="181" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F181" s="1"/>
     </row>
-    <row r="182" spans="6:6">
+    <row r="182" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F182" s="1"/>
     </row>
-    <row r="183" spans="6:6">
+    <row r="183" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F183" s="1"/>
     </row>
-    <row r="184" spans="6:6">
+    <row r="184" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F184" s="1"/>
     </row>
-    <row r="185" spans="6:6">
+    <row r="185" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F185" s="1"/>
     </row>
-    <row r="186" spans="6:6">
+    <row r="186" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F186" s="1"/>
     </row>
-    <row r="187" spans="6:6">
+    <row r="187" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F187" s="1"/>
     </row>
-    <row r="188" spans="6:6">
+    <row r="188" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F188" s="1"/>
     </row>
-    <row r="189" spans="6:6">
+    <row r="189" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F189" s="1"/>
     </row>
-    <row r="190" spans="6:6">
+    <row r="190" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F190" s="1"/>
     </row>
-    <row r="191" spans="6:6">
+    <row r="191" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F191" s="1"/>
     </row>
-    <row r="192" spans="6:6">
+    <row r="192" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F192" s="1"/>
     </row>
-    <row r="193" spans="6:6">
+    <row r="193" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F193" s="1"/>
     </row>
-    <row r="194" spans="6:6">
+    <row r="194" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F194" s="1"/>
     </row>
-    <row r="195" spans="6:6">
+    <row r="195" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F195" s="1"/>
     </row>
-    <row r="196" spans="6:6">
+    <row r="196" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F196" s="1"/>
     </row>
-    <row r="197" spans="6:6">
+    <row r="197" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F197" s="1"/>
     </row>
-    <row r="198" spans="6:6">
+    <row r="198" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F198" s="1"/>
     </row>
-    <row r="199" spans="6:6">
+    <row r="199" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F199" s="1"/>
     </row>
-    <row r="200" spans="6:6">
+    <row r="200" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F200" s="1"/>
     </row>
-    <row r="201" spans="6:6">
+    <row r="201" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F201" s="1"/>
     </row>
-    <row r="202" spans="6:6">
+    <row r="202" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F202" s="1"/>
     </row>
-    <row r="203" spans="6:6">
+    <row r="203" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F203" s="1"/>
     </row>
-    <row r="204" spans="6:6">
+    <row r="204" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F204" s="1"/>
     </row>
-    <row r="205" spans="6:6">
+    <row r="205" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F205" s="1"/>
     </row>
-    <row r="206" spans="6:6">
+    <row r="206" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F206" s="1"/>
     </row>
-    <row r="207" spans="6:6">
+    <row r="207" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F207" s="1"/>
     </row>
-    <row r="208" spans="6:6">
+    <row r="208" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F208" s="1"/>
     </row>
-    <row r="209" spans="6:6">
+    <row r="209" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F209" s="1"/>
     </row>
-    <row r="210" spans="6:6">
+    <row r="210" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F210" s="1"/>
     </row>
-    <row r="211" spans="6:6">
+    <row r="211" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F211" s="1"/>
     </row>
-    <row r="212" spans="6:6">
+    <row r="212" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F212" s="1"/>
     </row>
-    <row r="213" spans="6:6">
+    <row r="213" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F213" s="1"/>
     </row>
-    <row r="214" spans="6:6">
+    <row r="214" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F214" s="1"/>
     </row>
-    <row r="215" spans="6:6">
+    <row r="215" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F215" s="1"/>
     </row>
-    <row r="216" spans="6:6">
+    <row r="216" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F216" s="1"/>
     </row>
-    <row r="217" spans="6:6">
+    <row r="217" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F217" s="1"/>
     </row>
-    <row r="218" spans="6:6">
+    <row r="218" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F218" s="1"/>
     </row>
-    <row r="219" spans="6:6">
+    <row r="219" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F219" s="1"/>
     </row>
-    <row r="220" spans="6:6">
+    <row r="220" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F220" s="1"/>
     </row>
-    <row r="221" spans="6:6">
+    <row r="221" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F221" s="1"/>
     </row>
-    <row r="222" spans="6:6">
+    <row r="222" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F222" s="1"/>
     </row>
-    <row r="223" spans="6:6">
+    <row r="223" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F223" s="1"/>
     </row>
-    <row r="224" spans="6:6">
+    <row r="224" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F224" s="1"/>
     </row>
-    <row r="225" spans="6:6">
+    <row r="225" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F225" s="1"/>
     </row>
-    <row r="226" spans="6:6">
+    <row r="226" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F226" s="1"/>
     </row>
-    <row r="227" spans="6:6">
+    <row r="227" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F227" s="1"/>
     </row>
-    <row r="228" spans="6:6">
+    <row r="228" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F228" s="1"/>
     </row>
-    <row r="229" spans="6:6">
+    <row r="229" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F229" s="1"/>
     </row>
-    <row r="230" spans="6:6">
+    <row r="230" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F230" s="1"/>
     </row>
-    <row r="231" spans="6:6">
+    <row r="231" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F231" s="1"/>
     </row>
-    <row r="232" spans="6:6">
+    <row r="232" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F232" s="1"/>
     </row>
-    <row r="233" spans="6:6">
+    <row r="233" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F233" s="1"/>
     </row>
-    <row r="234" spans="6:6">
+    <row r="234" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F234" s="1"/>
     </row>
-    <row r="235" spans="6:6">
+    <row r="235" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F235" s="1"/>
     </row>
-    <row r="236" spans="6:6">
+    <row r="236" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F236" s="1"/>
     </row>
-    <row r="237" spans="6:6">
+    <row r="237" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F237" s="1"/>
     </row>
-    <row r="238" spans="6:6">
+    <row r="238" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F238" s="1"/>
     </row>
-    <row r="239" spans="6:6">
+    <row r="239" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F239" s="1"/>
     </row>
-    <row r="240" spans="6:6">
+    <row r="240" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F240" s="1"/>
     </row>
-    <row r="241" spans="6:6">
+    <row r="241" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F241" s="1"/>
     </row>
-    <row r="242" spans="6:6">
+    <row r="242" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F242" s="1"/>
     </row>
-    <row r="243" spans="6:6">
+    <row r="243" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F243" s="1"/>
     </row>
-    <row r="244" spans="6:6">
+    <row r="244" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F244" s="1"/>
     </row>
-    <row r="245" spans="6:6">
+    <row r="245" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F245" s="1"/>
     </row>
-    <row r="246" spans="6:6">
+    <row r="246" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F246" s="1"/>
     </row>
-    <row r="247" spans="6:6">
+    <row r="247" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F247" s="1"/>
     </row>
-    <row r="248" spans="6:6">
+    <row r="248" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F248" s="1"/>
     </row>
-    <row r="249" spans="6:6">
+    <row r="249" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F249" s="1"/>
     </row>
-    <row r="250" spans="6:6">
+    <row r="250" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F250" s="1"/>
     </row>
-    <row r="251" spans="6:6">
+    <row r="251" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F251" s="1"/>
     </row>
-    <row r="252" spans="6:6">
+    <row r="252" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F252" s="1"/>
     </row>
-    <row r="253" spans="6:6">
+    <row r="253" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F253" s="1"/>
     </row>
-    <row r="254" spans="6:6">
+    <row r="254" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F254" s="1"/>
     </row>
-    <row r="255" spans="6:6">
+    <row r="255" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F255" s="1"/>
     </row>
-    <row r="256" spans="6:6">
+    <row r="256" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F256" s="1"/>
     </row>
-    <row r="257" spans="6:6">
+    <row r="257" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F257" s="1"/>
     </row>
-    <row r="258" spans="6:6">
+    <row r="258" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F258" s="1"/>
     </row>
-    <row r="259" spans="6:6">
+    <row r="259" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F259" s="1"/>
     </row>
-    <row r="260" spans="6:6">
+    <row r="260" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F260" s="1"/>
     </row>
-    <row r="261" spans="6:6">
+    <row r="261" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F261" s="1"/>
     </row>
-    <row r="262" spans="6:6">
+    <row r="262" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F262" s="1"/>
     </row>
-    <row r="263" spans="6:6">
+    <row r="263" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F263" s="1"/>
     </row>
-    <row r="264" spans="6:6">
+    <row r="264" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F264" s="1"/>
     </row>
-    <row r="265" spans="6:6">
+    <row r="265" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F265" s="1"/>
     </row>
-    <row r="266" spans="6:6">
+    <row r="266" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F266" s="1"/>
     </row>
-    <row r="267" spans="6:6">
+    <row r="267" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F267" s="1"/>
     </row>
-    <row r="268" spans="6:6">
+    <row r="268" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F268" s="1"/>
     </row>
-    <row r="269" spans="6:6">
+    <row r="269" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F269" s="1"/>
     </row>
-    <row r="270" spans="6:6">
+    <row r="270" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F270" s="1"/>
     </row>
-    <row r="271" spans="6:6">
+    <row r="271" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F271" s="1"/>
     </row>
-    <row r="272" spans="6:6">
+    <row r="272" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F272" s="1"/>
     </row>
-    <row r="273" spans="6:6">
+    <row r="273" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F273" s="1"/>
     </row>
-    <row r="274" spans="6:6">
+    <row r="274" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F274" s="1"/>
     </row>
-    <row r="275" spans="6:6">
+    <row r="275" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F275" s="1"/>
     </row>
-    <row r="276" spans="6:6">
+    <row r="276" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F276" s="1"/>
     </row>
-    <row r="277" spans="6:6">
+    <row r="277" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F277" s="1"/>
     </row>
-    <row r="278" spans="6:6">
+    <row r="278" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F278" s="1"/>
     </row>
-    <row r="279" spans="6:6">
+    <row r="279" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F279" s="1"/>
     </row>
-    <row r="280" spans="6:6">
+    <row r="280" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F280" s="1"/>
     </row>
-    <row r="281" spans="6:6">
+    <row r="281" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F281" s="1"/>
     </row>
-    <row r="282" spans="6:6">
+    <row r="282" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F282" s="1"/>
     </row>
-    <row r="283" spans="6:6">
+    <row r="283" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F283" s="1"/>
     </row>
-    <row r="284" spans="6:6">
+    <row r="284" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F284" s="1"/>
     </row>
-    <row r="285" spans="6:6">
+    <row r="285" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F285" s="1"/>
     </row>
-    <row r="286" spans="6:6">
+    <row r="286" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F286" s="1"/>
     </row>
-    <row r="287" spans="6:6">
+    <row r="287" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F287" s="1"/>
     </row>
-    <row r="288" spans="6:6">
+    <row r="288" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F288" s="1"/>
     </row>
-    <row r="289" spans="6:6">
+    <row r="289" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F289" s="1"/>
     </row>
-    <row r="290" spans="6:6">
+    <row r="290" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F290" s="1"/>
     </row>
-    <row r="291" spans="6:6">
+    <row r="291" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F291" s="1"/>
     </row>
-    <row r="292" spans="6:6">
+    <row r="292" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F292" s="1"/>
     </row>
-    <row r="293" spans="6:6">
+    <row r="293" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F293" s="1"/>
     </row>
-    <row r="294" spans="6:6">
+    <row r="294" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F294" s="1"/>
     </row>
-    <row r="295" spans="6:6">
+    <row r="295" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F295" s="1"/>
     </row>
-    <row r="296" spans="6:6">
+    <row r="296" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F296" s="1"/>
     </row>
-    <row r="297" spans="6:6">
+    <row r="297" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F297" s="1"/>
     </row>
-    <row r="298" spans="6:6">
+    <row r="298" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F298" s="1"/>
     </row>
-    <row r="299" spans="6:6">
+    <row r="299" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F299" s="1"/>
     </row>
-    <row r="300" spans="6:6">
+    <row r="300" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F300" s="1"/>
     </row>
-    <row r="301" spans="6:6">
+    <row r="301" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F301" s="1"/>
     </row>
-    <row r="302" spans="6:6">
+    <row r="302" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F302" s="1"/>
     </row>
-    <row r="303" spans="6:6">
+    <row r="303" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F303" s="1"/>
     </row>
-    <row r="304" spans="6:6">
+    <row r="304" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F304" s="1"/>
     </row>
-    <row r="305" spans="6:6">
+    <row r="305" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F305" s="1"/>
     </row>
-    <row r="306" spans="6:6">
+    <row r="306" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F306" s="1"/>
     </row>
-    <row r="307" spans="6:6">
+    <row r="307" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F307" s="1"/>
     </row>
-    <row r="308" spans="6:6">
+    <row r="308" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F308" s="1"/>
     </row>
-    <row r="309" spans="6:6">
+    <row r="309" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F309" s="1"/>
     </row>
-    <row r="310" spans="6:6">
+    <row r="310" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F310" s="1"/>
     </row>
-    <row r="311" spans="6:6">
+    <row r="311" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F311" s="1"/>
     </row>
-    <row r="312" spans="6:6">
+    <row r="312" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F312" s="1"/>
     </row>
-    <row r="313" spans="6:6">
+    <row r="313" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F313" s="1"/>
     </row>
-    <row r="314" spans="6:6">
+    <row r="314" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F314" s="1"/>
     </row>
-    <row r="315" spans="6:6">
+    <row r="315" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F315" s="1"/>
     </row>
-    <row r="316" spans="6:6">
+    <row r="316" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F316" s="1"/>
     </row>
-    <row r="317" spans="6:6">
+    <row r="317" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F317" s="1"/>
     </row>
-    <row r="318" spans="6:6">
+    <row r="318" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F318" s="1"/>
     </row>
-    <row r="319" spans="6:6">
+    <row r="319" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F319" s="1"/>
     </row>
-    <row r="320" spans="6:6">
+    <row r="320" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F320" s="1"/>
     </row>
-    <row r="321" spans="6:6">
+    <row r="321" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F321" s="1"/>
     </row>
-    <row r="326" spans="6:6">
+    <row r="326" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F326" s="1"/>
     </row>
-    <row r="327" spans="6:6">
+    <row r="327" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F327" s="1"/>
     </row>
-    <row r="328" spans="6:6">
+    <row r="328" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F328" s="1"/>
     </row>
-    <row r="329" spans="6:6">
+    <row r="329" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F329" s="1"/>
     </row>
-    <row r="330" spans="6:6">
+    <row r="330" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F330" s="1"/>
     </row>
-    <row r="331" spans="6:6">
+    <row r="331" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F331" s="1"/>
     </row>
-    <row r="332" spans="6:6">
+    <row r="332" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F332" s="1"/>
     </row>
-    <row r="333" spans="6:6">
+    <row r="333" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F333" s="1"/>
     </row>
-    <row r="334" spans="6:6">
+    <row r="334" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F334" s="1"/>
     </row>
-    <row r="335" spans="6:6">
+    <row r="335" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F335" s="1"/>
     </row>
-    <row r="336" spans="6:6">
+    <row r="336" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F336" s="1"/>
     </row>
-    <row r="337" spans="6:6">
+    <row r="337" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F337" s="1"/>
     </row>
-    <row r="338" spans="6:6">
+    <row r="338" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F338" s="1"/>
     </row>
-    <row r="339" spans="6:6">
+    <row r="339" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F339" s="1"/>
     </row>
-    <row r="340" spans="6:6">
+    <row r="340" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F340" s="1"/>
     </row>
-    <row r="341" spans="6:6">
+    <row r="341" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F341" s="1"/>
     </row>
-    <row r="342" spans="6:6">
+    <row r="342" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F342" s="1"/>
     </row>
-    <row r="343" spans="6:6">
+    <row r="343" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F343" s="1"/>
     </row>
-    <row r="344" spans="6:6">
+    <row r="344" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F344" s="1"/>
     </row>
-    <row r="345" spans="6:6">
+    <row r="345" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F345" s="1"/>
     </row>
-    <row r="346" spans="6:6">
+    <row r="346" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F346" s="1"/>
     </row>
-    <row r="347" spans="6:6">
+    <row r="347" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F347" s="1"/>
     </row>
-    <row r="348" spans="6:6">
+    <row r="348" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F348" s="1"/>
     </row>
-    <row r="349" spans="6:6">
+    <row r="349" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F349" s="1"/>
     </row>
-    <row r="350" spans="6:6">
+    <row r="350" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F350" s="1"/>
     </row>
-    <row r="351" spans="6:6">
+    <row r="351" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F351" s="1"/>
     </row>
-    <row r="352" spans="6:6">
+    <row r="352" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F352" s="1"/>
     </row>
-    <row r="353" spans="6:6">
+    <row r="353" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F353" s="1"/>
     </row>
-    <row r="354" spans="6:6">
+    <row r="354" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F354" s="1"/>
     </row>
-    <row r="355" spans="6:6">
+    <row r="355" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F355" s="1"/>
     </row>
-    <row r="356" spans="6:6">
+    <row r="356" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F356" s="1"/>
     </row>
-    <row r="357" spans="6:6">
+    <row r="357" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F357" s="1"/>
     </row>
-    <row r="358" spans="6:6">
+    <row r="358" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F358" s="1"/>
     </row>
-    <row r="359" spans="6:6">
+    <row r="359" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F359" s="1"/>
     </row>
-    <row r="360" spans="6:6">
+    <row r="360" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F360" s="1"/>
     </row>
-    <row r="361" spans="6:6">
+    <row r="361" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F361" s="1"/>
     </row>
-    <row r="362" spans="6:6">
+    <row r="362" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F362" s="1"/>
     </row>
-    <row r="363" spans="6:6">
+    <row r="363" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F363" s="1"/>
     </row>
-    <row r="364" spans="6:6">
+    <row r="364" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F364" s="1"/>
     </row>
-    <row r="365" spans="6:6">
+    <row r="365" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F365" s="1"/>
     </row>
-    <row r="366" spans="6:6">
+    <row r="366" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F366" s="1"/>
     </row>
-    <row r="367" spans="6:6">
+    <row r="367" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F367" s="1"/>
     </row>
-    <row r="368" spans="6:6">
+    <row r="368" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F368" s="1"/>
     </row>
-    <row r="369" spans="6:6">
+    <row r="369" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F369" s="1"/>
     </row>
-    <row r="370" spans="6:6">
+    <row r="370" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F370" s="1"/>
     </row>
-    <row r="371" spans="6:6">
+    <row r="371" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F371" s="1"/>
     </row>
-    <row r="372" spans="6:6">
+    <row r="372" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F372" s="1"/>
     </row>
-    <row r="373" spans="6:6">
+    <row r="373" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F373" s="1"/>
     </row>
-    <row r="374" spans="6:6">
+    <row r="374" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F374" s="1"/>
     </row>
-    <row r="375" spans="6:6">
+    <row r="375" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F375" s="1"/>
     </row>
-    <row r="376" spans="6:6">
+    <row r="376" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F376" s="1"/>
     </row>
-    <row r="377" spans="6:6">
+    <row r="377" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F377" s="1"/>
     </row>
-    <row r="378" spans="6:6">
+    <row r="378" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F378" s="1"/>
     </row>
-    <row r="379" spans="6:6">
+    <row r="379" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F379" s="1"/>
     </row>
-    <row r="380" spans="6:6">
+    <row r="380" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F380" s="1"/>
     </row>
-    <row r="381" spans="6:6">
+    <row r="381" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F381" s="1"/>
     </row>
-    <row r="382" spans="6:6">
+    <row r="382" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F382" s="1"/>
     </row>
-    <row r="383" spans="6:6">
+    <row r="383" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F383" s="1"/>
     </row>
-    <row r="384" spans="6:6">
+    <row r="384" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F384" s="1"/>
     </row>
-    <row r="385" spans="6:6">
+    <row r="385" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F385" s="1"/>
     </row>
-    <row r="386" spans="6:6">
+    <row r="386" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F386" s="1"/>
     </row>
-    <row r="387" spans="6:6">
+    <row r="387" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F387" s="1"/>
     </row>
-    <row r="388" spans="6:6">
+    <row r="388" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F388" s="1"/>
     </row>
-    <row r="389" spans="6:6">
+    <row r="389" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F389" s="1"/>
     </row>
-    <row r="390" spans="6:6">
+    <row r="390" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F390" s="1"/>
     </row>
-    <row r="391" spans="6:6">
+    <row r="391" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F391" s="1"/>
     </row>
-    <row r="392" spans="6:6">
+    <row r="392" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F392" s="1"/>
     </row>
-    <row r="393" spans="6:6">
+    <row r="393" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F393" s="1"/>
     </row>
-    <row r="394" spans="6:6">
+    <row r="394" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F394" s="1"/>
     </row>
-    <row r="395" spans="6:6">
+    <row r="395" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F395" s="1"/>
     </row>
-    <row r="396" spans="6:6">
+    <row r="396" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F396" s="1"/>
     </row>
-    <row r="397" spans="6:6">
+    <row r="397" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F397" s="1"/>
     </row>
-    <row r="398" spans="6:6">
+    <row r="398" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F398" s="1"/>
     </row>
-    <row r="399" spans="6:6">
+    <row r="399" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F399" s="1"/>
     </row>
-    <row r="400" spans="6:6">
+    <row r="400" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F400" s="1"/>
     </row>
-    <row r="401" spans="6:6">
+    <row r="401" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F401" s="1"/>
     </row>
-    <row r="402" spans="6:6">
+    <row r="402" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F402" s="1"/>
     </row>
-    <row r="403" spans="6:6">
+    <row r="403" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F403" s="1"/>
     </row>
-    <row r="404" spans="6:6">
+    <row r="404" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F404" s="1"/>
     </row>
-    <row r="405" spans="6:6">
+    <row r="405" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F405" s="1"/>
     </row>
-    <row r="406" spans="6:6">
+    <row r="406" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F406" s="1"/>
     </row>
-    <row r="407" spans="6:6">
+    <row r="407" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F407" s="1"/>
     </row>
-    <row r="408" spans="6:6">
+    <row r="408" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F408" s="1"/>
     </row>
-    <row r="409" spans="6:6">
+    <row r="409" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F409" s="1"/>
     </row>
-    <row r="410" spans="6:6">
+    <row r="410" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F410" s="1"/>
     </row>
-    <row r="411" spans="6:6">
+    <row r="411" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F411" s="1"/>
     </row>
-    <row r="412" spans="6:6">
+    <row r="412" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F412" s="1"/>
     </row>
-    <row r="413" spans="6:6">
+    <row r="413" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F413" s="1"/>
     </row>
-    <row r="414" spans="6:6">
+    <row r="414" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F414" s="1"/>
     </row>
-    <row r="415" spans="6:6">
+    <row r="415" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F415" s="1"/>
     </row>
-    <row r="416" spans="6:6">
+    <row r="416" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F416" s="1"/>
     </row>
-    <row r="417" spans="5:6">
+    <row r="417" spans="5:6" x14ac:dyDescent="0.3">
       <c r="F417" s="1"/>
     </row>
-    <row r="418" spans="5:6">
+    <row r="418" spans="5:6" x14ac:dyDescent="0.3">
       <c r="F418" s="1"/>
     </row>
-    <row r="419" spans="5:6">
+    <row r="419" spans="5:6" x14ac:dyDescent="0.3">
       <c r="F419" s="1"/>
     </row>
-    <row r="420" spans="5:6">
+    <row r="420" spans="5:6" x14ac:dyDescent="0.3">
       <c r="F420" s="1"/>
     </row>
-    <row r="421" spans="5:6">
+    <row r="421" spans="5:6" x14ac:dyDescent="0.3">
       <c r="F421" s="1"/>
     </row>
-    <row r="422" spans="5:6">
+    <row r="422" spans="5:6" x14ac:dyDescent="0.3">
       <c r="F422" s="1"/>
     </row>
-    <row r="423" spans="5:6">
+    <row r="423" spans="5:6" x14ac:dyDescent="0.3">
       <c r="F423" s="1"/>
     </row>
-    <row r="424" spans="5:6">
+    <row r="424" spans="5:6" x14ac:dyDescent="0.3">
       <c r="F424" s="1"/>
     </row>
-    <row r="425" spans="5:6">
+    <row r="425" spans="5:6" x14ac:dyDescent="0.3">
       <c r="F425" s="1"/>
     </row>
-    <row r="426" spans="5:6">
+    <row r="426" spans="5:6" x14ac:dyDescent="0.3">
       <c r="F426" s="1"/>
     </row>
-    <row r="427" spans="5:6">
+    <row r="427" spans="5:6" x14ac:dyDescent="0.3">
       <c r="F427" s="1"/>
     </row>
-    <row r="428" spans="5:6">
+    <row r="428" spans="5:6" x14ac:dyDescent="0.3">
       <c r="F428" s="1"/>
     </row>
-    <row r="429" spans="5:6">
+    <row r="429" spans="5:6" x14ac:dyDescent="0.3">
       <c r="F429" s="1"/>
     </row>
-    <row r="430" spans="5:6">
+    <row r="430" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E430" s="4"/>
       <c r="F430" s="1"/>
     </row>
   </sheetData>
   <sortState ref="D2:F430">
-    <sortCondition ref="F2" descending="1"/>
+    <sortCondition descending="1" ref="F2"/>
   </sortState>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <conditionalFormatting sqref="A141 A137:A139">
+    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A141:A1048576 A1:A139">
+    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O100"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.5047619047619" customWidth="1"/>
+    <col min="1" max="1" width="10.5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="B1" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="B2" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="H2" s="1"/>
       <c r="M2" s="1"/>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="B3" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="H3" s="1"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="B4" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="H4" s="1"/>
       <c r="M4" s="1"/>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="B5" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="H5" s="1"/>
       <c r="M5" s="1"/>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="B6" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="H6" s="1"/>
       <c r="M6" s="1"/>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="B7" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="M7" s="1"/>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="B8" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="H8" s="1"/>
       <c r="M8" s="1"/>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="B9" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="H9" s="1"/>
       <c r="M9" s="1"/>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="B10" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="H10" s="1"/>
       <c r="M10" s="1"/>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="B11" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="M11" s="1"/>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="B12" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="H12" s="1"/>
       <c r="M12" s="1"/>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="B13" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="H13" s="1"/>
       <c r="M13" s="1"/>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="B14" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="H14" s="1"/>
       <c r="M14" s="1"/>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="B15" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="H15" s="1"/>
       <c r="M15" s="1"/>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="B16" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="M16" s="1"/>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="B17" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="H17" s="1"/>
       <c r="M17" s="1"/>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="B18" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="H18" s="1"/>
       <c r="M18" s="1"/>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="B19" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="H19" s="1"/>
       <c r="M19" s="1"/>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="B20" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="H20" s="1"/>
       <c r="M20" s="1"/>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="B21" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="H21" s="1"/>
       <c r="M21" s="1"/>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="B22" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="M22" s="1"/>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="B23" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="H23" s="1"/>
       <c r="M23" s="1"/>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="B24" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="H24" s="1"/>
       <c r="M24" s="1"/>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="B25" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="H25" s="1"/>
       <c r="M25" s="1"/>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="B26" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="H26" s="1"/>
       <c r="M26" s="1"/>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="B27" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="M27" s="1"/>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="B28" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="H28" s="1"/>
       <c r="M28" s="1"/>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="B29" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="H29" s="1"/>
       <c r="M29" s="1"/>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="B30" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="H30" s="1"/>
       <c r="M30" s="1"/>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>494</v>
-      </c>
-      <c r="B31" t="s">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="H31" s="1"/>
       <c r="M31" s="1"/>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>496</v>
-      </c>
-      <c r="B32" t="s">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="H32" s="1"/>
       <c r="M32" s="1"/>
     </row>
-    <row r="33" spans="8:15">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A33" s="9" t="s">
+        <v>491</v>
+      </c>
       <c r="H33" s="1"/>
       <c r="M33" s="1"/>
     </row>
-    <row r="34" spans="8:15">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A34" s="9" t="s">
+        <v>492</v>
+      </c>
       <c r="M34" s="1"/>
     </row>
-    <row r="35" spans="8:15">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A35" s="9"/>
       <c r="H35" s="1"/>
       <c r="M35" s="1"/>
     </row>
-    <row r="37" spans="8:15">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A36" s="9"/>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="J37" s="1"/>
       <c r="O37" s="1"/>
     </row>
-    <row r="38" spans="8:15">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="J38" s="1"/>
       <c r="O38" s="1"/>
     </row>
-    <row r="39" spans="8:15">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O39" s="1"/>
     </row>
-    <row r="40" spans="8:15">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O40" s="1"/>
     </row>
-    <row r="41" spans="8:15">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="J41" s="1"/>
       <c r="O41" s="1"/>
     </row>
-    <row r="42" spans="8:15">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="J42" s="1"/>
       <c r="O42" s="1"/>
     </row>
-    <row r="43" spans="8:15">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="J43" s="1"/>
       <c r="O43" s="1"/>
     </row>
-    <row r="44" spans="8:15">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="J44" s="1"/>
       <c r="O44" s="1"/>
     </row>
-    <row r="45" spans="8:15">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="J45" s="1"/>
       <c r="O45" s="1"/>
     </row>
-    <row r="46" spans="8:15">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O46" s="1"/>
     </row>
-    <row r="47" spans="8:15">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="J47" s="1"/>
       <c r="O47" s="1"/>
     </row>
-    <row r="48" spans="8:15">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O48" s="1"/>
     </row>
-    <row r="49" spans="10:15">
+    <row r="49" spans="10:15" x14ac:dyDescent="0.3">
       <c r="J49" s="1"/>
       <c r="O49" s="1"/>
     </row>
-    <row r="50" spans="10:15">
+    <row r="50" spans="10:15" x14ac:dyDescent="0.3">
       <c r="J50" s="1"/>
       <c r="O50" s="1"/>
     </row>
-    <row r="51" spans="10:15">
+    <row r="51" spans="10:15" x14ac:dyDescent="0.3">
       <c r="J51" s="1"/>
       <c r="O51" s="1"/>
     </row>
-    <row r="52" spans="10:15">
+    <row r="52" spans="10:15" x14ac:dyDescent="0.3">
       <c r="O52" s="1"/>
     </row>
-    <row r="53" spans="10:15">
+    <row r="53" spans="10:15" x14ac:dyDescent="0.3">
       <c r="O53" s="1"/>
     </row>
-    <row r="54" spans="10:15">
+    <row r="54" spans="10:15" x14ac:dyDescent="0.3">
       <c r="J54" s="1"/>
       <c r="O54" s="1"/>
     </row>
-    <row r="55" spans="10:15">
+    <row r="55" spans="10:15" x14ac:dyDescent="0.3">
       <c r="O55" s="1"/>
     </row>
-    <row r="56" spans="10:15">
+    <row r="56" spans="10:15" x14ac:dyDescent="0.3">
       <c r="J56" s="1"/>
       <c r="O56" s="1"/>
     </row>
-    <row r="57" spans="10:15">
+    <row r="57" spans="10:15" x14ac:dyDescent="0.3">
       <c r="O57" s="1"/>
     </row>
-    <row r="58" spans="10:15">
+    <row r="58" spans="10:15" x14ac:dyDescent="0.3">
       <c r="O58" s="1"/>
     </row>
-    <row r="59" spans="10:15">
+    <row r="59" spans="10:15" x14ac:dyDescent="0.3">
       <c r="J59" s="1"/>
     </row>
-    <row r="60" spans="10:15">
+    <row r="60" spans="10:15" x14ac:dyDescent="0.3">
       <c r="O60" s="1"/>
     </row>
-    <row r="61" spans="10:15">
+    <row r="61" spans="10:15" x14ac:dyDescent="0.3">
       <c r="O61" s="1"/>
     </row>
-    <row r="62" spans="10:15">
+    <row r="62" spans="10:15" x14ac:dyDescent="0.3">
       <c r="J62" s="1"/>
       <c r="O62" s="1"/>
     </row>
-    <row r="63" spans="10:15">
+    <row r="63" spans="10:15" x14ac:dyDescent="0.3">
       <c r="J63" s="1"/>
       <c r="O63" s="1"/>
     </row>
-    <row r="64" spans="10:15">
+    <row r="64" spans="10:15" x14ac:dyDescent="0.3">
       <c r="J64" s="1"/>
       <c r="O64" s="1"/>
     </row>
-    <row r="65" spans="10:15">
+    <row r="65" spans="10:15" x14ac:dyDescent="0.3">
       <c r="O65" s="1"/>
     </row>
-    <row r="66" spans="10:15">
+    <row r="66" spans="10:15" x14ac:dyDescent="0.3">
       <c r="J66" s="1"/>
     </row>
-    <row r="67" spans="10:15">
+    <row r="67" spans="10:15" x14ac:dyDescent="0.3">
       <c r="J67" s="1"/>
       <c r="O67" s="1"/>
     </row>
-    <row r="68" spans="10:15">
+    <row r="68" spans="10:15" x14ac:dyDescent="0.3">
       <c r="J68" s="1"/>
       <c r="O68" s="1"/>
     </row>
-    <row r="69" spans="10:15">
+    <row r="69" spans="10:15" x14ac:dyDescent="0.3">
       <c r="J69" s="1"/>
       <c r="O69" s="1"/>
     </row>
-    <row r="70" spans="10:15">
+    <row r="70" spans="10:15" x14ac:dyDescent="0.3">
       <c r="J70" s="1"/>
       <c r="O70" s="1"/>
     </row>
-    <row r="71" spans="10:15">
+    <row r="71" spans="10:15" x14ac:dyDescent="0.3">
       <c r="J71" s="1"/>
       <c r="O71" s="1"/>
     </row>
-    <row r="72" spans="10:15">
+    <row r="72" spans="10:15" x14ac:dyDescent="0.3">
       <c r="J72" s="1"/>
       <c r="O72" s="1"/>
     </row>
-    <row r="73" spans="10:15">
+    <row r="73" spans="10:15" x14ac:dyDescent="0.3">
       <c r="J73" s="1"/>
     </row>
-    <row r="74" spans="10:15">
+    <row r="74" spans="10:15" x14ac:dyDescent="0.3">
       <c r="J74" s="1"/>
     </row>
-    <row r="75" spans="10:15">
+    <row r="75" spans="10:15" x14ac:dyDescent="0.3">
       <c r="O75" s="1"/>
     </row>
-    <row r="76" spans="10:15">
+    <row r="76" spans="10:15" x14ac:dyDescent="0.3">
       <c r="J76" s="1"/>
     </row>
-    <row r="77" spans="10:15">
+    <row r="77" spans="10:15" x14ac:dyDescent="0.3">
       <c r="J77" s="1"/>
     </row>
-    <row r="78" spans="10:15">
+    <row r="78" spans="10:15" x14ac:dyDescent="0.3">
       <c r="O78" s="1"/>
     </row>
-    <row r="79" spans="10:15">
+    <row r="79" spans="10:15" x14ac:dyDescent="0.3">
       <c r="J79" s="1"/>
       <c r="O79" s="1"/>
     </row>
-    <row r="80" spans="10:15">
+    <row r="80" spans="10:15" x14ac:dyDescent="0.3">
       <c r="O80" s="1"/>
     </row>
-    <row r="81" spans="10:15">
+    <row r="81" spans="10:15" x14ac:dyDescent="0.3">
       <c r="J81" s="1"/>
       <c r="O81" s="1"/>
     </row>
-    <row r="83" spans="10:15">
+    <row r="83" spans="10:15" x14ac:dyDescent="0.3">
       <c r="J83" s="1"/>
     </row>
-    <row r="84" spans="10:15">
+    <row r="84" spans="10:15" x14ac:dyDescent="0.3">
       <c r="J84" s="1"/>
       <c r="O84" s="1"/>
     </row>
-    <row r="85" spans="10:15">
+    <row r="85" spans="10:15" x14ac:dyDescent="0.3">
       <c r="J85" s="1"/>
       <c r="O85" s="1"/>
     </row>
-    <row r="86" spans="10:15">
+    <row r="86" spans="10:15" x14ac:dyDescent="0.3">
       <c r="J86" s="1"/>
     </row>
-    <row r="87" spans="10:15">
+    <row r="87" spans="10:15" x14ac:dyDescent="0.3">
       <c r="J87" s="1"/>
       <c r="O87" s="1"/>
     </row>
-    <row r="88" spans="10:15">
+    <row r="88" spans="10:15" x14ac:dyDescent="0.3">
       <c r="O88" s="1"/>
     </row>
-    <row r="89" spans="10:15">
+    <row r="89" spans="10:15" x14ac:dyDescent="0.3">
       <c r="J89" s="1"/>
       <c r="O89" s="1"/>
     </row>
-    <row r="90" spans="10:15">
+    <row r="90" spans="10:15" x14ac:dyDescent="0.3">
       <c r="J90" s="1"/>
       <c r="O90" s="1"/>
     </row>
-    <row r="91" spans="10:15">
+    <row r="91" spans="10:15" x14ac:dyDescent="0.3">
       <c r="J91" s="1"/>
       <c r="O91" s="1"/>
     </row>
-    <row r="92" spans="10:15">
+    <row r="92" spans="10:15" x14ac:dyDescent="0.3">
       <c r="J92" s="1"/>
     </row>
-    <row r="93" spans="10:15">
+    <row r="93" spans="10:15" x14ac:dyDescent="0.3">
       <c r="J93" s="1"/>
       <c r="O93" s="1"/>
     </row>
-    <row r="94" spans="10:15">
+    <row r="94" spans="10:15" x14ac:dyDescent="0.3">
       <c r="J94" s="1"/>
       <c r="O94" s="1"/>
     </row>
-    <row r="95" spans="10:15">
+    <row r="95" spans="10:15" x14ac:dyDescent="0.3">
       <c r="J95" s="1"/>
       <c r="O95" s="1"/>
     </row>
-    <row r="96" spans="10:15">
+    <row r="96" spans="10:15" x14ac:dyDescent="0.3">
       <c r="J96" s="1"/>
       <c r="O96" s="1"/>
     </row>
-    <row r="97" spans="10:15">
+    <row r="97" spans="10:15" x14ac:dyDescent="0.3">
       <c r="O97" s="1"/>
     </row>
-    <row r="98" spans="10:15">
+    <row r="98" spans="10:15" x14ac:dyDescent="0.3">
       <c r="J98" s="1"/>
       <c r="O98" s="1"/>
     </row>
-    <row r="99" spans="10:15">
+    <row r="99" spans="10:15" x14ac:dyDescent="0.3">
       <c r="J99" s="1"/>
       <c r="O99" s="1"/>
     </row>
-    <row r="100" spans="10:15">
+    <row r="100" spans="10:15" x14ac:dyDescent="0.3">
       <c r="J100" s="1"/>
       <c r="O100" s="1"/>
     </row>
@@ -7409,7 +6849,13 @@
   <sortState ref="A1:B100">
     <sortCondition ref="B1"/>
   </sortState>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <conditionalFormatting sqref="A1:A33 A37:A1048576">
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/TrackingList.xlsx
+++ b/TrackingList.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18096" windowHeight="7932" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18096" windowHeight="7932" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="台灣股票" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="509">
   <si>
     <t>26/05 Taiwan 50</t>
   </si>
@@ -1536,6 +1536,100 @@
   </si>
   <si>
     <t>ONDO</t>
+  </si>
+  <si>
+    <t>BX</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>COHR</t>
+  </si>
+  <si>
+    <t>ILMN</t>
+  </si>
+  <si>
+    <t>DRAM</t>
+  </si>
+  <si>
+    <t>SDNK</t>
+  </si>
+  <si>
+    <t>GLW</t>
+  </si>
+  <si>
+    <t>CIEN</t>
+  </si>
+  <si>
+    <r>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ram</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>光通訊</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RDO</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>NOK</t>
+  </si>
+  <si>
+    <t>記憶體</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>能源</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>E</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>LITE</t>
+  </si>
+  <si>
+    <t>AXTI</t>
   </si>
 </sst>
 </file>
@@ -1604,7 +1698,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1616,6 +1710,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1974,20 +2069,17 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>1519</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>2002</v>
-      </c>
-      <c r="B7" t="s">
-        <v>0</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>2059</v>
+        <v>2002</v>
       </c>
       <c r="B8" t="s">
         <v>0</v>
@@ -1995,7 +2087,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>2207</v>
+        <v>2059</v>
       </c>
       <c r="B9" t="s">
         <v>0</v>
@@ -2003,7 +2095,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>2301</v>
+        <v>2207</v>
       </c>
       <c r="B10" t="s">
         <v>0</v>
@@ -2011,7 +2103,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>2303</v>
+        <v>2301</v>
       </c>
       <c r="B11" t="s">
         <v>0</v>
@@ -2019,7 +2111,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>2308</v>
+        <v>2303</v>
       </c>
       <c r="B12" t="s">
         <v>0</v>
@@ -2027,7 +2119,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>2317</v>
+        <v>2308</v>
       </c>
       <c r="B13" t="s">
         <v>0</v>
@@ -2035,7 +2127,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>2327</v>
+        <v>2317</v>
       </c>
       <c r="B14" t="s">
         <v>0</v>
@@ -2043,7 +2135,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>2330</v>
+        <v>2327</v>
       </c>
       <c r="B15" t="s">
         <v>0</v>
@@ -2051,7 +2143,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>2344</v>
+        <v>2330</v>
       </c>
       <c r="B16" t="s">
         <v>0</v>
@@ -2059,7 +2151,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>2345</v>
+        <v>2344</v>
       </c>
       <c r="B17" t="s">
         <v>0</v>
@@ -2067,7 +2159,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>2357</v>
+        <v>2345</v>
       </c>
       <c r="B18" t="s">
         <v>0</v>
@@ -2075,7 +2167,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>2360</v>
+        <v>2357</v>
       </c>
       <c r="B19" t="s">
         <v>0</v>
@@ -2083,7 +2175,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>2368</v>
+        <v>2360</v>
       </c>
       <c r="B20" t="s">
         <v>0</v>
@@ -2091,7 +2183,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>2382</v>
+        <v>2368</v>
       </c>
       <c r="B21" t="s">
         <v>0</v>
@@ -2099,7 +2191,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>2383</v>
+        <v>2382</v>
       </c>
       <c r="B22" t="s">
         <v>0</v>
@@ -2107,7 +2199,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>2395</v>
+        <v>2383</v>
       </c>
       <c r="B23" t="s">
         <v>0</v>
@@ -2115,7 +2207,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>2408</v>
+        <v>2395</v>
       </c>
       <c r="B24" t="s">
         <v>0</v>
@@ -2123,7 +2215,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>2412</v>
+        <v>2408</v>
       </c>
       <c r="B25" t="s">
         <v>0</v>
@@ -2131,7 +2223,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>2449</v>
+        <v>2412</v>
       </c>
       <c r="B26" t="s">
         <v>0</v>
@@ -2139,7 +2231,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>2454</v>
+        <v>2449</v>
       </c>
       <c r="B27" t="s">
         <v>0</v>
@@ -2147,7 +2239,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>2603</v>
+        <v>2454</v>
       </c>
       <c r="B28" t="s">
         <v>0</v>
@@ -2155,7 +2247,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>2880</v>
+        <v>2603</v>
       </c>
       <c r="B29" t="s">
         <v>0</v>
@@ -2163,7 +2255,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>2881</v>
+        <v>2880</v>
       </c>
       <c r="B30" t="s">
         <v>0</v>
@@ -2171,7 +2263,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="B31" t="s">
         <v>0</v>
@@ -2179,7 +2271,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>2883</v>
+        <v>2882</v>
       </c>
       <c r="B32" t="s">
         <v>0</v>
@@ -2187,7 +2279,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>2884</v>
+        <v>2883</v>
       </c>
       <c r="B33" t="s">
         <v>0</v>
@@ -2195,7 +2287,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>2885</v>
+        <v>2884</v>
       </c>
       <c r="B34" t="s">
         <v>0</v>
@@ -2203,7 +2295,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>2886</v>
+        <v>2885</v>
       </c>
       <c r="B35" t="s">
         <v>0</v>
@@ -2211,7 +2303,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>2887</v>
+        <v>2886</v>
       </c>
       <c r="B36" t="s">
         <v>0</v>
@@ -2219,7 +2311,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>2890</v>
+        <v>2887</v>
       </c>
       <c r="B37" t="s">
         <v>0</v>
@@ -2227,7 +2319,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>2891</v>
+        <v>2890</v>
       </c>
       <c r="B38" t="s">
         <v>0</v>
@@ -2235,7 +2327,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>2892</v>
+        <v>2891</v>
       </c>
       <c r="B39" t="s">
         <v>0</v>
@@ -2243,7 +2335,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>3008</v>
+        <v>2892</v>
       </c>
       <c r="B40" t="s">
         <v>0</v>
@@ -2251,7 +2343,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>3017</v>
+        <v>3008</v>
       </c>
       <c r="B41" t="s">
         <v>0</v>
@@ -2259,7 +2351,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>3045</v>
+        <v>3017</v>
       </c>
       <c r="B42" t="s">
         <v>0</v>
@@ -2267,33 +2359,33 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>3131</v>
+        <v>3045</v>
+      </c>
+      <c r="B43" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>3231</v>
-      </c>
-      <c r="B44" t="s">
-        <v>0</v>
+        <v>3131</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>3324</v>
+        <v>3231</v>
+      </c>
+      <c r="B45" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>3653</v>
-      </c>
-      <c r="B46" t="s">
-        <v>0</v>
+        <v>3324</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>3661</v>
+        <v>3653</v>
       </c>
       <c r="B47" t="s">
         <v>0</v>
@@ -2301,7 +2393,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>3711</v>
+        <v>3661</v>
       </c>
       <c r="B48" t="s">
         <v>0</v>
@@ -2309,7 +2401,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>4904</v>
+        <v>3711</v>
       </c>
       <c r="B49" t="s">
         <v>0</v>
@@ -2317,7 +2409,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>5880</v>
+        <v>4904</v>
       </c>
       <c r="B50" t="s">
         <v>0</v>
@@ -2325,7 +2417,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>6505</v>
+        <v>5880</v>
       </c>
       <c r="B51" t="s">
         <v>0</v>
@@ -2333,20 +2425,20 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>6640</v>
+        <v>6505</v>
+      </c>
+      <c r="B52" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>6669</v>
-      </c>
-      <c r="B53" t="s">
-        <v>0</v>
+        <v>6640</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>6919</v>
+        <v>6669</v>
       </c>
       <c r="B54" t="s">
         <v>0</v>
@@ -2354,7 +2446,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>7769</v>
+        <v>6919</v>
       </c>
       <c r="B55" t="s">
         <v>0</v>
@@ -2362,7 +2454,10 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>1514</v>
+        <v>7769</v>
+      </c>
+      <c r="B56" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
@@ -2371,7 +2466,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="A1:B55">
+  <sortState ref="A1:B57">
     <sortCondition ref="A1"/>
   </sortState>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -2379,7 +2474,7 @@
     <cfRule type="duplicateValues" dxfId="7" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A56:A66">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3203,798 +3298,806 @@
         <v>158</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="5" t="s">
         <v>173</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" s="5" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71" s="5" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
         <v>213</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A72" s="5" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A93" s="5" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A93" s="10" t="s">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A94" s="10" t="s">
         <v>490</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A94" s="5" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A117" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A118" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A119" s="5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A120" s="5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A121" s="5" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A122" s="5" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A122" s="10" t="s">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A123" s="10" t="s">
         <v>489</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A123" s="5" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A124" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A125" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A126" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A127" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A128" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A129" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A130" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A131" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A132" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A133" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A134" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A135" s="5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A136" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A137" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A138" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A139" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A140" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A141" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A142" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A143" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A144" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A145" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A146" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A147" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A148" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A149" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A150" s="5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A151" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A152" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A153" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A154" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A155" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A156" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A157" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A158" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A159" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A160" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A161" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A162" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A163" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A164" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A165" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A166" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A167" s="5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A168" s="5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A169" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A170" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A171" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A172" s="5" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A173" s="5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A174" s="5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A175" s="5" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A176" s="5" t="s">
         <v>315</v>
       </c>
     </row>
@@ -4151,106 +4254,106 @@
       <c r="I216" s="5"/>
     </row>
   </sheetData>
-  <sortState ref="A1:A216">
-    <sortCondition ref="A124"/>
+  <sortState ref="A1:B216">
+    <sortCondition ref="A1"/>
   </sortState>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="A1:A183 A192:A1048576">
-    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A191:A1048576 A189 A1:A187">
-    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A15" r:id="rId1" tooltip="https://etfdb.com/etf/BWET/"/>
-    <hyperlink ref="A56" r:id="rId2" tooltip="https://etfdb.com/etf/HYDR/"/>
-    <hyperlink ref="A41" r:id="rId3" tooltip="https://etfdb.com/etf/EWY/"/>
-    <hyperlink ref="A44" r:id="rId4" tooltip="https://etfdb.com/etf/FLKR/"/>
-    <hyperlink ref="A50" r:id="rId5" tooltip="https://etfdb.com/etf/FTXL/"/>
-    <hyperlink ref="A92" r:id="rId6" tooltip="https://etfdb.com/etf/PSI/"/>
-    <hyperlink ref="A102" r:id="rId7" tooltip="https://etfdb.com/etf/REMX/"/>
-    <hyperlink ref="A119" r:id="rId8" tooltip="https://etfdb.com/etf/SOXX/"/>
-    <hyperlink ref="A174" r:id="rId9" tooltip="https://etfdb.com/etf/XSD/"/>
-    <hyperlink ref="A118" r:id="rId10" tooltip="https://etfdb.com/etf/SOXQ/"/>
+    <hyperlink ref="A57" r:id="rId2" tooltip="https://etfdb.com/etf/HYDR/"/>
+    <hyperlink ref="A42" r:id="rId3" tooltip="https://etfdb.com/etf/EWY/"/>
+    <hyperlink ref="A45" r:id="rId4" tooltip="https://etfdb.com/etf/FLKR/"/>
+    <hyperlink ref="A51" r:id="rId5" tooltip="https://etfdb.com/etf/FTXL/"/>
+    <hyperlink ref="A93" r:id="rId6" tooltip="https://etfdb.com/etf/PSI/"/>
+    <hyperlink ref="A103" r:id="rId7" tooltip="https://etfdb.com/etf/REMX/"/>
+    <hyperlink ref="A120" r:id="rId8" tooltip="https://etfdb.com/etf/SOXX/"/>
+    <hyperlink ref="A175" r:id="rId9" tooltip="https://etfdb.com/etf/XSD/"/>
+    <hyperlink ref="A119" r:id="rId10" tooltip="https://etfdb.com/etf/SOXQ/"/>
     <hyperlink ref="A8" r:id="rId11" tooltip="https://etfdb.com/etf/BBC/"/>
-    <hyperlink ref="A114" r:id="rId12" tooltip="https://etfdb.com/etf/SLVP/"/>
-    <hyperlink ref="A110" r:id="rId13" tooltip="https://etfdb.com/etf/SHOC/"/>
-    <hyperlink ref="A83" r:id="rId14" tooltip="https://etfdb.com/etf/PBW/"/>
-    <hyperlink ref="A133" r:id="rId15" tooltip="https://etfdb.com/etf/UFO/"/>
+    <hyperlink ref="A115" r:id="rId12" tooltip="https://etfdb.com/etf/SLVP/"/>
+    <hyperlink ref="A111" r:id="rId13" tooltip="https://etfdb.com/etf/SHOC/"/>
+    <hyperlink ref="A84" r:id="rId14" tooltip="https://etfdb.com/etf/PBW/"/>
+    <hyperlink ref="A134" r:id="rId15" tooltip="https://etfdb.com/etf/UFO/"/>
     <hyperlink ref="A24" r:id="rId16" tooltip="https://etfdb.com/etf/CTEC/"/>
     <hyperlink ref="A21" r:id="rId17" tooltip="https://etfdb.com/etf/COPX/"/>
     <hyperlink ref="A5" r:id="rId18" tooltip="https://etfdb.com/etf/AIVC/"/>
     <hyperlink ref="A25" r:id="rId19" tooltip="https://etfdb.com/etf/CTEX/"/>
-    <hyperlink ref="A175" r:id="rId20" tooltip="https://etfdb.com/etf/XTL/"/>
-    <hyperlink ref="A77" r:id="rId21" tooltip="https://etfdb.com/etf/MNRS/"/>
-    <hyperlink ref="A137" r:id="rId22" tooltip="https://etfdb.com/etf/URA/"/>
-    <hyperlink ref="A127" r:id="rId23" tooltip="https://etfdb.com/etf/TINY/"/>
-    <hyperlink ref="A64" r:id="rId24" tooltip="https://etfdb.com/etf/IGPT/"/>
+    <hyperlink ref="A176" r:id="rId20" tooltip="https://etfdb.com/etf/XTL/"/>
+    <hyperlink ref="A78" r:id="rId21" tooltip="https://etfdb.com/etf/MNRS/"/>
+    <hyperlink ref="A138" r:id="rId22" tooltip="https://etfdb.com/etf/URA/"/>
+    <hyperlink ref="A128" r:id="rId23" tooltip="https://etfdb.com/etf/TINY/"/>
+    <hyperlink ref="A65" r:id="rId24" tooltip="https://etfdb.com/etf/IGPT/"/>
     <hyperlink ref="A20" r:id="rId25" tooltip="https://etfdb.com/etf/CNXT/"/>
-    <hyperlink ref="A104" r:id="rId26" tooltip="https://etfdb.com/etf/ROKT/"/>
+    <hyperlink ref="A105" r:id="rId26" tooltip="https://etfdb.com/etf/ROKT/"/>
     <hyperlink ref="A16" r:id="rId27" tooltip="https://etfdb.com/etf/CARZ/"/>
-    <hyperlink ref="A96" r:id="rId28" tooltip="https://etfdb.com/etf/QCLN/"/>
-    <hyperlink ref="A159" r:id="rId29" tooltip="https://etfdb.com/etf/XES/"/>
-    <hyperlink ref="A53" r:id="rId30" tooltip="https://etfdb.com/etf/GOEX/"/>
-    <hyperlink ref="A52" r:id="rId31" tooltip="https://etfdb.com/etf/GDXJ/"/>
-    <hyperlink ref="A45" r:id="rId32" tooltip="https://etfdb.com/etf/FLTW/"/>
+    <hyperlink ref="A97" r:id="rId28" tooltip="https://etfdb.com/etf/QCLN/"/>
+    <hyperlink ref="A160" r:id="rId29" tooltip="https://etfdb.com/etf/XES/"/>
+    <hyperlink ref="A54" r:id="rId30" tooltip="https://etfdb.com/etf/GOEX/"/>
+    <hyperlink ref="A53" r:id="rId31" tooltip="https://etfdb.com/etf/GDXJ/"/>
+    <hyperlink ref="A46" r:id="rId32" tooltip="https://etfdb.com/etf/FLTW/"/>
     <hyperlink ref="A19" r:id="rId33" tooltip="https://etfdb.com/etf/CNRG/"/>
-    <hyperlink ref="A94" r:id="rId34" tooltip="https://etfdb.com/etf/PTF/"/>
-    <hyperlink ref="A103" r:id="rId35" tooltip="https://etfdb.com/etf/RING/"/>
-    <hyperlink ref="A107" r:id="rId36" tooltip="https://etfdb.com/etf/SBIO/"/>
-    <hyperlink ref="A95" r:id="rId37" tooltip="https://etfdb.com/etf/PXJ/"/>
-    <hyperlink ref="A108" r:id="rId38" tooltip="https://etfdb.com/etf/SGDJ/"/>
-    <hyperlink ref="A81" r:id="rId39" tooltip="https://etfdb.com/etf/OIH/"/>
-    <hyperlink ref="A82" r:id="rId40" tooltip="https://etfdb.com/etf/PBD/"/>
-    <hyperlink ref="A40" r:id="rId41" tooltip="https://etfdb.com/etf/EWT/"/>
-    <hyperlink ref="A91" r:id="rId42" tooltip="https://etfdb.com/etf/PSCT/"/>
+    <hyperlink ref="A95" r:id="rId34" tooltip="https://etfdb.com/etf/PTF/"/>
+    <hyperlink ref="A104" r:id="rId35" tooltip="https://etfdb.com/etf/RING/"/>
+    <hyperlink ref="A108" r:id="rId36" tooltip="https://etfdb.com/etf/SBIO/"/>
+    <hyperlink ref="A96" r:id="rId37" tooltip="https://etfdb.com/etf/PXJ/"/>
+    <hyperlink ref="A109" r:id="rId38" tooltip="https://etfdb.com/etf/SGDJ/"/>
+    <hyperlink ref="A82" r:id="rId39" tooltip="https://etfdb.com/etf/OIH/"/>
+    <hyperlink ref="A83" r:id="rId40" tooltip="https://etfdb.com/etf/PBD/"/>
+    <hyperlink ref="A41" r:id="rId41" tooltip="https://etfdb.com/etf/EWT/"/>
+    <hyperlink ref="A92" r:id="rId42" tooltip="https://etfdb.com/etf/PSCT/"/>
     <hyperlink ref="A3" r:id="rId43" tooltip="https://etfdb.com/etf/AIA/"/>
-    <hyperlink ref="A49" r:id="rId44" tooltip="https://etfdb.com/etf/FRNW/"/>
-    <hyperlink ref="A59" r:id="rId45" tooltip="https://etfdb.com/etf/IBLC/"/>
-    <hyperlink ref="A31" r:id="rId46" tooltip="https://etfdb.com/etf/DRIV/"/>
+    <hyperlink ref="A50" r:id="rId44" tooltip="https://etfdb.com/etf/FRNW/"/>
+    <hyperlink ref="A60" r:id="rId45" tooltip="https://etfdb.com/etf/IBLC/"/>
+    <hyperlink ref="A32" r:id="rId46" tooltip="https://etfdb.com/etf/DRIV/"/>
     <hyperlink ref="A26" r:id="rId47" tooltip="https://etfdb.com/etf/DAPP/"/>
-    <hyperlink ref="A63" r:id="rId48" tooltip="https://etfdb.com/etf/IEZ/"/>
-    <hyperlink ref="A124" r:id="rId49" tooltip="https://etfdb.com/etf/STCE/"/>
-    <hyperlink ref="A130" r:id="rId50" tooltip="https://etfdb.com/etf/TRFK/"/>
-    <hyperlink ref="A37" r:id="rId51" tooltip="https://etfdb.com/etf/EPU/"/>
-    <hyperlink ref="A48" r:id="rId52" tooltip="https://etfdb.com/etf/FRDM/"/>
-    <hyperlink ref="A100" r:id="rId53" tooltip="https://etfdb.com/etf/QQQS/"/>
-    <hyperlink ref="A101" r:id="rId54" tooltip="https://etfdb.com/etf/QTUM/"/>
-    <hyperlink ref="A109" r:id="rId55" tooltip="https://etfdb.com/etf/SGDM/"/>
+    <hyperlink ref="A64" r:id="rId48" tooltip="https://etfdb.com/etf/IEZ/"/>
+    <hyperlink ref="A125" r:id="rId49" tooltip="https://etfdb.com/etf/STCE/"/>
+    <hyperlink ref="A131" r:id="rId50" tooltip="https://etfdb.com/etf/TRFK/"/>
+    <hyperlink ref="A38" r:id="rId51" tooltip="https://etfdb.com/etf/EPU/"/>
+    <hyperlink ref="A49" r:id="rId52" tooltip="https://etfdb.com/etf/FRDM/"/>
+    <hyperlink ref="A101" r:id="rId53" tooltip="https://etfdb.com/etf/QQQS/"/>
+    <hyperlink ref="A102" r:id="rId54" tooltip="https://etfdb.com/etf/QTUM/"/>
+    <hyperlink ref="A110" r:id="rId55" tooltip="https://etfdb.com/etf/SGDM/"/>
     <hyperlink ref="A7" r:id="rId56" tooltip="https://etfdb.com/etf/AUMI/"/>
-    <hyperlink ref="A47" r:id="rId57" tooltip="https://etfdb.com/etf/FPA/"/>
-    <hyperlink ref="A69" r:id="rId58" tooltip="https://etfdb.com/etf/KNCT/"/>
-    <hyperlink ref="A32" r:id="rId59" tooltip="https://etfdb.com/etf/DTCR/"/>
-    <hyperlink ref="A61" r:id="rId60" tooltip="https://etfdb.com/etf/ICLN/"/>
+    <hyperlink ref="A48" r:id="rId57" tooltip="https://etfdb.com/etf/FPA/"/>
+    <hyperlink ref="A70" r:id="rId58" tooltip="https://etfdb.com/etf/KNCT/"/>
+    <hyperlink ref="A33" r:id="rId59" tooltip="https://etfdb.com/etf/DTCR/"/>
+    <hyperlink ref="A62" r:id="rId60" tooltip="https://etfdb.com/etf/ICLN/"/>
     <hyperlink ref="A11" r:id="rId61" tooltip="https://etfdb.com/etf/BITQ/"/>
-    <hyperlink ref="A149" r:id="rId62" tooltip="https://etfdb.com/etf/VLUE/"/>
-    <hyperlink ref="A116" r:id="rId63" tooltip="https://etfdb.com/etf/SLX/"/>
-    <hyperlink ref="A67" r:id="rId64" tooltip="https://etfdb.com/etf/KARS/"/>
+    <hyperlink ref="A150" r:id="rId62" tooltip="https://etfdb.com/etf/VLUE/"/>
+    <hyperlink ref="A117" r:id="rId63" tooltip="https://etfdb.com/etf/SLX/"/>
+    <hyperlink ref="A68" r:id="rId64" tooltip="https://etfdb.com/etf/KARS/"/>
     <hyperlink ref="A4" r:id="rId65" tooltip="https://etfdb.com/etf/AIRR/"/>
     <hyperlink ref="A23" r:id="rId66" tooltip="https://etfdb.com/etf/CSD/"/>
     <hyperlink ref="A22" r:id="rId67" tooltip="https://etfdb.com/etf/CRAK/"/>
-    <hyperlink ref="A158" r:id="rId68" tooltip="https://etfdb.com/etf/XBI/"/>
-    <hyperlink ref="A99" r:id="rId69" tooltip="https://etfdb.com/etf/QQQA/"/>
-    <hyperlink ref="A68" r:id="rId70" tooltip="https://etfdb.com/etf/KEMX/"/>
-    <hyperlink ref="A73" r:id="rId71" tooltip="https://etfdb.com/etf/LOUP/"/>
-    <hyperlink ref="A87" r:id="rId72" tooltip="https://etfdb.com/etf/PIE/"/>
-    <hyperlink ref="A36" r:id="rId73" tooltip="https://etfdb.com/etf/EMXC/"/>
-    <hyperlink ref="A88" r:id="rId74" tooltip="https://etfdb.com/etf/PRN/"/>
+    <hyperlink ref="A159" r:id="rId68" tooltip="https://etfdb.com/etf/XBI/"/>
+    <hyperlink ref="A100" r:id="rId69" tooltip="https://etfdb.com/etf/QQQA/"/>
+    <hyperlink ref="A69" r:id="rId70" tooltip="https://etfdb.com/etf/KEMX/"/>
+    <hyperlink ref="A74" r:id="rId71" tooltip="https://etfdb.com/etf/LOUP/"/>
+    <hyperlink ref="A88" r:id="rId72" tooltip="https://etfdb.com/etf/PIE/"/>
+    <hyperlink ref="A37" r:id="rId73" tooltip="https://etfdb.com/etf/EMXC/"/>
+    <hyperlink ref="A89" r:id="rId74" tooltip="https://etfdb.com/etf/PRN/"/>
     <hyperlink ref="A13" r:id="rId75" tooltip="https://etfdb.com/etf/BOAT/"/>
-    <hyperlink ref="A120" r:id="rId76" tooltip="https://etfdb.com/etf/SPHB/"/>
-    <hyperlink ref="A89" r:id="rId77" tooltip="https://etfdb.com/etf/PSCE/"/>
-    <hyperlink ref="A66" r:id="rId78" tooltip="https://etfdb.com/etf/IXN/"/>
-    <hyperlink ref="A126" r:id="rId79" tooltip="https://etfdb.com/etf/THNQ/"/>
-    <hyperlink ref="A42" r:id="rId80" tooltip="https://etfdb.com/etf/FAN/"/>
-    <hyperlink ref="A60" r:id="rId81" tooltip="https://etfdb.com/etf/IBRN/"/>
-    <hyperlink ref="A150" r:id="rId82" tooltip="https://etfdb.com/etf/VNAM/"/>
-    <hyperlink ref="A90" r:id="rId83" tooltip="https://etfdb.com/etf/PSCM/"/>
-    <hyperlink ref="A80" r:id="rId84" tooltip="https://etfdb.com/etf/NXTG/"/>
-    <hyperlink ref="A173" r:id="rId85" tooltip="https://etfdb.com/etf/XNTK/"/>
-    <hyperlink ref="A35" r:id="rId86" tooltip="https://etfdb.com/etf/EIS/"/>
+    <hyperlink ref="A121" r:id="rId76" tooltip="https://etfdb.com/etf/SPHB/"/>
+    <hyperlink ref="A90" r:id="rId77" tooltip="https://etfdb.com/etf/PSCE/"/>
+    <hyperlink ref="A67" r:id="rId78" tooltip="https://etfdb.com/etf/IXN/"/>
+    <hyperlink ref="A127" r:id="rId79" tooltip="https://etfdb.com/etf/THNQ/"/>
+    <hyperlink ref="A43" r:id="rId80" tooltip="https://etfdb.com/etf/FAN/"/>
+    <hyperlink ref="A61" r:id="rId81" tooltip="https://etfdb.com/etf/IBRN/"/>
+    <hyperlink ref="A151" r:id="rId82" tooltip="https://etfdb.com/etf/VNAM/"/>
+    <hyperlink ref="A91" r:id="rId83" tooltip="https://etfdb.com/etf/PSCM/"/>
+    <hyperlink ref="A81" r:id="rId84" tooltip="https://etfdb.com/etf/NXTG/"/>
+    <hyperlink ref="A174" r:id="rId85" tooltip="https://etfdb.com/etf/XNTK/"/>
+    <hyperlink ref="A36" r:id="rId86" tooltip="https://etfdb.com/etf/EIS/"/>
     <hyperlink ref="A2" r:id="rId87" tooltip="https://etfdb.com/etf/AGEM/"/>
     <hyperlink ref="A6" r:id="rId88" tooltip="https://etfdb.com/etf/ASHS/"/>
-    <hyperlink ref="A43" r:id="rId89" tooltip="https://etfdb.com/etf/FDTS/"/>
+    <hyperlink ref="A44" r:id="rId89" tooltip="https://etfdb.com/etf/FDTS/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4380,61 +4483,61 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>330</v>
-      </c>
-      <c r="B14" t="s">
-        <v>317</v>
+        <v>508</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>501</v>
       </c>
       <c r="F14" s="1"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>331</v>
+        <v>330</v>
+      </c>
+      <c r="B15" t="s">
+        <v>317</v>
       </c>
       <c r="F15" s="1"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>331</v>
+      </c>
+      <c r="F16" s="1"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>332</v>
       </c>
-      <c r="B16" t="s">
-        <v>317</v>
-      </c>
-      <c r="F16" s="1"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+      <c r="B17" t="s">
+        <v>317</v>
+      </c>
+      <c r="F17" s="1"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="11" t="s">
+        <v>506</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="F18" s="1"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="F17" s="1"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+      <c r="F19" s="1"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
         <v>334</v>
-      </c>
-      <c r="F18" s="1"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>335</v>
-      </c>
-      <c r="B19" t="s">
-        <v>317</v>
-      </c>
-      <c r="F19" s="1"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>336</v>
-      </c>
-      <c r="B20" t="s">
-        <v>317</v>
       </c>
       <c r="F20" s="1"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B21" t="s">
         <v>317</v>
@@ -4443,7 +4546,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B22" t="s">
         <v>317</v>
@@ -4452,7 +4555,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B23" t="s">
         <v>317</v>
@@ -4461,7 +4564,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B24" t="s">
         <v>317</v>
@@ -4470,7 +4573,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B25" t="s">
         <v>317</v>
@@ -4478,14 +4581,14 @@
       <c r="F25" s="1"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>342</v>
+      <c r="A26" s="9" t="s">
+        <v>493</v>
       </c>
       <c r="F26" s="1"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B27" t="s">
         <v>317</v>
@@ -4494,7 +4597,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B28" t="s">
         <v>317</v>
@@ -4502,50 +4605,44 @@
       <c r="F28" s="1"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>345</v>
-      </c>
-      <c r="B29" t="s">
-        <v>317</v>
+      <c r="A29" s="2" t="s">
+        <v>342</v>
       </c>
       <c r="F29" s="1"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>346</v>
-      </c>
-      <c r="B30" t="s">
-        <v>317</v>
+      <c r="A30" s="9" t="s">
+        <v>487</v>
       </c>
       <c r="F30" s="1"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>347</v>
-      </c>
-      <c r="B31" t="s">
-        <v>317</v>
+      <c r="A31" s="9" t="s">
+        <v>486</v>
       </c>
       <c r="F31" s="1"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>348</v>
-      </c>
-      <c r="B32" t="s">
-        <v>317</v>
+        <v>499</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>501</v>
       </c>
       <c r="F32" s="1"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>349</v>
+        <v>343</v>
+      </c>
+      <c r="B33" t="s">
+        <v>317</v>
       </c>
       <c r="F33" s="1"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="B34" t="s">
         <v>317</v>
@@ -4553,23 +4650,26 @@
       <c r="F34" s="1"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
-        <v>351</v>
+      <c r="A35" t="s">
+        <v>345</v>
+      </c>
+      <c r="B35" t="s">
+        <v>317</v>
       </c>
       <c r="F35" s="1"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>352</v>
-      </c>
-      <c r="B36" t="s">
-        <v>317</v>
+      <c r="A36" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>501</v>
       </c>
       <c r="F36" s="1"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="B37" t="s">
         <v>317</v>
@@ -4578,7 +4678,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="B38" t="s">
         <v>317</v>
@@ -4586,17 +4686,17 @@
       <c r="F38" s="1"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>355</v>
-      </c>
-      <c r="B39" t="s">
-        <v>317</v>
+      <c r="A39" s="11" t="s">
+        <v>502</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>501</v>
       </c>
       <c r="F39" s="1"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="B40" t="s">
         <v>317</v>
@@ -4604,14 +4704,14 @@
       <c r="F40" s="1"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
-        <v>357</v>
+      <c r="A41" t="s">
+        <v>349</v>
       </c>
       <c r="F41" s="1"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="B42" t="s">
         <v>317</v>
@@ -4619,23 +4719,23 @@
       <c r="F42" s="1"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>359</v>
-      </c>
-      <c r="B43" t="s">
-        <v>317</v>
+      <c r="A43" s="2" t="s">
+        <v>351</v>
       </c>
       <c r="F43" s="1"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>360</v>
+        <v>352</v>
+      </c>
+      <c r="B44" t="s">
+        <v>317</v>
       </c>
       <c r="F44" s="1"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="B45" t="s">
         <v>317</v>
@@ -4644,7 +4744,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="B46" t="s">
         <v>317</v>
@@ -4653,13 +4753,16 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>363</v>
+        <v>355</v>
+      </c>
+      <c r="B47" t="s">
+        <v>317</v>
       </c>
       <c r="F47" s="1"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="B48" t="s">
         <v>317</v>
@@ -4667,17 +4770,14 @@
       <c r="F48" s="1"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>365</v>
-      </c>
-      <c r="B49" t="s">
-        <v>317</v>
+      <c r="A49" s="2" t="s">
+        <v>357</v>
       </c>
       <c r="F49" s="1"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="B50" t="s">
         <v>317</v>
@@ -4686,7 +4786,7 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="B51" t="s">
         <v>317</v>
@@ -4694,26 +4794,23 @@
       <c r="F51" s="1"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>368</v>
-      </c>
-      <c r="B52" t="s">
-        <v>317</v>
+      <c r="A52" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>505</v>
       </c>
       <c r="F52" s="1"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>369</v>
-      </c>
-      <c r="B53" t="s">
-        <v>317</v>
+        <v>360</v>
       </c>
       <c r="F53" s="1"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="B54" t="s">
         <v>317</v>
@@ -4722,7 +4819,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="B55" t="s">
         <v>317</v>
@@ -4731,13 +4828,13 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="F56" s="1"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="B57" t="s">
         <v>317</v>
@@ -4746,7 +4843,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="B58" t="s">
         <v>317</v>
@@ -4755,7 +4852,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="B59" t="s">
         <v>317</v>
@@ -4763,17 +4860,17 @@
       <c r="F59" s="1"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>376</v>
-      </c>
-      <c r="B60" t="s">
-        <v>317</v>
+      <c r="A60" s="9" t="s">
+        <v>498</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>501</v>
       </c>
       <c r="F60" s="1"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="B61" t="s">
         <v>317</v>
@@ -4782,25 +4879,34 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>378</v>
+        <v>368</v>
+      </c>
+      <c r="B62" t="s">
+        <v>317</v>
       </c>
       <c r="F62" s="1"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
-        <v>379</v>
+      <c r="A63" t="s">
+        <v>369</v>
+      </c>
+      <c r="B63" t="s">
+        <v>317</v>
       </c>
       <c r="F63" s="1"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
-        <v>380</v>
+      <c r="A64" t="s">
+        <v>370</v>
+      </c>
+      <c r="B64" t="s">
+        <v>317</v>
       </c>
       <c r="F64" s="1"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="B65" t="s">
         <v>317</v>
@@ -4809,16 +4915,13 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>382</v>
-      </c>
-      <c r="B66" t="s">
-        <v>317</v>
+        <v>372</v>
       </c>
       <c r="F66" s="1"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="B67" t="s">
         <v>317</v>
@@ -4826,23 +4929,23 @@
       <c r="F67" s="1"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
-        <v>384</v>
+      <c r="A68" t="s">
+        <v>374</v>
+      </c>
+      <c r="B68" t="s">
+        <v>317</v>
       </c>
       <c r="F68" s="1"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>385</v>
-      </c>
-      <c r="B69" t="s">
-        <v>317</v>
+      <c r="A69" s="9" t="s">
+        <v>495</v>
       </c>
       <c r="F69" s="1"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="B70" t="s">
         <v>317</v>
@@ -4851,7 +4954,7 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="B71" t="s">
         <v>317</v>
@@ -4859,44 +4962,44 @@
       <c r="F71" s="1"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="2" t="s">
-        <v>388</v>
+      <c r="A72" t="s">
+        <v>377</v>
+      </c>
+      <c r="B72" t="s">
+        <v>317</v>
       </c>
       <c r="F72" s="1"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>389</v>
-      </c>
-      <c r="B73" t="s">
-        <v>317</v>
+        <v>378</v>
       </c>
       <c r="F73" s="1"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
-        <v>390</v>
-      </c>
-      <c r="B74" t="s">
-        <v>317</v>
+      <c r="A74" s="2" t="s">
+        <v>379</v>
       </c>
       <c r="F74" s="1"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>391</v>
+      <c r="A75" s="2" t="s">
+        <v>380</v>
       </c>
       <c r="F75" s="1"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
-        <v>392</v>
+      <c r="A76" t="s">
+        <v>381</v>
+      </c>
+      <c r="B76" t="s">
+        <v>317</v>
       </c>
       <c r="F76" s="1"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="B77" t="s">
         <v>317</v>
@@ -4905,7 +5008,7 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="B78" t="s">
         <v>317</v>
@@ -4913,17 +5016,14 @@
       <c r="F78" s="1"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>395</v>
-      </c>
-      <c r="B79" t="s">
-        <v>317</v>
+      <c r="A79" s="2" t="s">
+        <v>384</v>
       </c>
       <c r="F79" s="1"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="B80" t="s">
         <v>317</v>
@@ -4932,16 +5032,16 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>397</v>
-      </c>
-      <c r="B81" t="s">
-        <v>317</v>
+        <v>507</v>
+      </c>
+      <c r="B81" s="9" t="s">
+        <v>501</v>
       </c>
       <c r="F81" s="1"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="B82" t="s">
         <v>317</v>
@@ -4950,7 +5050,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="B83" t="s">
         <v>317</v>
@@ -4958,17 +5058,14 @@
       <c r="F83" s="1"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
-        <v>400</v>
-      </c>
-      <c r="B84" t="s">
-        <v>317</v>
+      <c r="A84" s="2" t="s">
+        <v>388</v>
       </c>
       <c r="F84" s="1"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>401</v>
+        <v>389</v>
       </c>
       <c r="B85" t="s">
         <v>317</v>
@@ -4977,7 +5074,7 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="B86" t="s">
         <v>317</v>
@@ -4986,22 +5083,19 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>403</v>
-      </c>
-      <c r="B87" t="s">
-        <v>317</v>
+        <v>391</v>
       </c>
       <c r="F87" s="1"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
-        <v>404</v>
+      <c r="A88" s="2" t="s">
+        <v>392</v>
       </c>
       <c r="F88" s="1"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="B89" t="s">
         <v>317</v>
@@ -5010,7 +5104,7 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="B90" t="s">
         <v>317</v>
@@ -5019,7 +5113,7 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="B91" t="s">
         <v>317</v>
@@ -5027,14 +5121,17 @@
       <c r="F91" s="1"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="2" t="s">
-        <v>408</v>
+      <c r="A92" t="s">
+        <v>396</v>
+      </c>
+      <c r="B92" t="s">
+        <v>317</v>
       </c>
       <c r="F92" s="1"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="B93" t="s">
         <v>317</v>
@@ -5043,25 +5140,34 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>410</v>
+        <v>398</v>
+      </c>
+      <c r="B94" t="s">
+        <v>317</v>
       </c>
       <c r="F94" s="1"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="2" t="s">
-        <v>411</v>
+      <c r="A95" t="s">
+        <v>399</v>
+      </c>
+      <c r="B95" t="s">
+        <v>317</v>
       </c>
       <c r="F95" s="1"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>412</v>
+        <v>400</v>
+      </c>
+      <c r="B96" t="s">
+        <v>317</v>
       </c>
       <c r="F96" s="1"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="B97" t="s">
         <v>317</v>
@@ -5070,7 +5176,7 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="B98" t="s">
         <v>317</v>
@@ -5079,25 +5185,31 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>415</v>
+        <v>403</v>
+      </c>
+      <c r="B99" t="s">
+        <v>317</v>
       </c>
       <c r="F99" s="1"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="F100" s="1"/>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="2" t="s">
-        <v>417</v>
+      <c r="A101" t="s">
+        <v>405</v>
+      </c>
+      <c r="B101" t="s">
+        <v>317</v>
       </c>
       <c r="F101" s="1"/>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="B102" t="s">
         <v>317</v>
@@ -5106,7 +5218,7 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="B103" t="s">
         <v>317</v>
@@ -5114,26 +5226,23 @@
       <c r="F103" s="1"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
-        <v>420</v>
-      </c>
-      <c r="B104" t="s">
-        <v>317</v>
+      <c r="A104" s="2" t="s">
+        <v>408</v>
       </c>
       <c r="F104" s="1"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>421</v>
-      </c>
-      <c r="B105" t="s">
-        <v>317</v>
+        <v>503</v>
+      </c>
+      <c r="B105" s="9" t="s">
+        <v>501</v>
       </c>
       <c r="F105" s="1"/>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="B106" t="s">
         <v>317</v>
@@ -5142,31 +5251,25 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>423</v>
-      </c>
-      <c r="B107" t="s">
-        <v>317</v>
+        <v>410</v>
       </c>
       <c r="F107" s="1"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
-        <v>424</v>
-      </c>
-      <c r="B108" t="s">
-        <v>317</v>
+      <c r="A108" s="2" t="s">
+        <v>411</v>
       </c>
       <c r="F108" s="1"/>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="3" t="s">
-        <v>425</v>
+      <c r="A109" t="s">
+        <v>412</v>
       </c>
       <c r="F109" s="1"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
       <c r="B110" t="s">
         <v>317</v>
@@ -5175,7 +5278,7 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="B111" t="s">
         <v>317</v>
@@ -5184,28 +5287,25 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="F112" s="1"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>429</v>
-      </c>
-      <c r="B113" t="s">
-        <v>317</v>
+        <v>416</v>
       </c>
       <c r="F113" s="1"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
-        <v>430</v>
+      <c r="A114" s="2" t="s">
+        <v>417</v>
       </c>
       <c r="F114" s="1"/>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>431</v>
+        <v>418</v>
       </c>
       <c r="B115" t="s">
         <v>317</v>
@@ -5213,14 +5313,17 @@
       <c r="F115" s="1"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="2" t="s">
-        <v>432</v>
+      <c r="A116" t="s">
+        <v>419</v>
+      </c>
+      <c r="B116" t="s">
+        <v>317</v>
       </c>
       <c r="F116" s="1"/>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>433</v>
+        <v>420</v>
       </c>
       <c r="B117" t="s">
         <v>317</v>
@@ -5229,19 +5332,25 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>434</v>
+        <v>421</v>
+      </c>
+      <c r="B118" t="s">
+        <v>317</v>
       </c>
       <c r="F118" s="1"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>435</v>
+        <v>422</v>
+      </c>
+      <c r="B119" t="s">
+        <v>317</v>
       </c>
       <c r="F119" s="1"/>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="B120" t="s">
         <v>317</v>
@@ -5250,7 +5359,7 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="B121" t="s">
         <v>317</v>
@@ -5258,17 +5367,14 @@
       <c r="F121" s="1"/>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" t="s">
-        <v>438</v>
-      </c>
-      <c r="B122" t="s">
-        <v>317</v>
+      <c r="A122" s="3" t="s">
+        <v>425</v>
       </c>
       <c r="F122" s="1"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>439</v>
+        <v>426</v>
       </c>
       <c r="B123" t="s">
         <v>317</v>
@@ -5277,7 +5383,7 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="B124" t="s">
         <v>317</v>
@@ -5285,26 +5391,23 @@
       <c r="F124" s="1"/>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" t="s">
-        <v>441</v>
-      </c>
-      <c r="B125" t="s">
-        <v>317</v>
+      <c r="A125" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="B125" s="9" t="s">
+        <v>500</v>
       </c>
       <c r="F125" s="1"/>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>442</v>
-      </c>
-      <c r="B126" t="s">
-        <v>317</v>
+        <v>428</v>
       </c>
       <c r="F126" s="1"/>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>443</v>
+        <v>429</v>
       </c>
       <c r="B127" t="s">
         <v>317</v>
@@ -5313,16 +5416,13 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>444</v>
-      </c>
-      <c r="B128" t="s">
-        <v>317</v>
+        <v>430</v>
       </c>
       <c r="F128" s="1"/>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>445</v>
+        <v>431</v>
       </c>
       <c r="B129" t="s">
         <v>317</v>
@@ -5331,13 +5431,13 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
-        <v>446</v>
+        <v>432</v>
       </c>
       <c r="F130" s="1"/>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="B131" t="s">
         <v>317</v>
@@ -5345,23 +5445,20 @@
       <c r="F131" s="1"/>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="2" t="s">
-        <v>448</v>
+      <c r="A132" t="s">
+        <v>434</v>
       </c>
       <c r="F132" s="1"/>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>449</v>
-      </c>
-      <c r="B133" t="s">
-        <v>317</v>
+        <v>435</v>
       </c>
       <c r="F133" s="1"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>450</v>
+        <v>436</v>
       </c>
       <c r="B134" t="s">
         <v>317</v>
@@ -5370,102 +5467,167 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
+        <v>437</v>
+      </c>
+      <c r="B135" t="s">
+        <v>317</v>
+      </c>
+      <c r="F135" s="1"/>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>438</v>
+      </c>
+      <c r="B136" t="s">
+        <v>317</v>
+      </c>
+      <c r="F136" s="1"/>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>439</v>
+      </c>
+      <c r="B137" t="s">
+        <v>317</v>
+      </c>
+      <c r="F137" s="1"/>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>440</v>
+      </c>
+      <c r="B138" t="s">
+        <v>317</v>
+      </c>
+      <c r="F138" s="1"/>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>441</v>
+      </c>
+      <c r="B139" t="s">
+        <v>317</v>
+      </c>
+      <c r="F139" s="1"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>442</v>
+      </c>
+      <c r="B140" t="s">
+        <v>317</v>
+      </c>
+      <c r="F140" s="1"/>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>443</v>
+      </c>
+      <c r="B141" t="s">
+        <v>317</v>
+      </c>
+      <c r="F141" s="1"/>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>444</v>
+      </c>
+      <c r="B142" t="s">
+        <v>317</v>
+      </c>
+      <c r="F142" s="1"/>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>445</v>
+      </c>
+      <c r="B143" t="s">
+        <v>317</v>
+      </c>
+      <c r="F143" s="1"/>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A144" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="F144" s="1"/>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>447</v>
+      </c>
+      <c r="B145" t="s">
+        <v>317</v>
+      </c>
+      <c r="F145" s="1"/>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A146" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="F146" s="1"/>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>449</v>
+      </c>
+      <c r="B147" t="s">
+        <v>317</v>
+      </c>
+      <c r="F147" s="1"/>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>450</v>
+      </c>
+      <c r="B148" t="s">
+        <v>317</v>
+      </c>
+      <c r="F148" s="1"/>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
         <v>451</v>
       </c>
-      <c r="B135" t="s">
-        <v>317</v>
-      </c>
-      <c r="F135" s="1"/>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="2" t="s">
+      <c r="B149" t="s">
+        <v>317</v>
+      </c>
+      <c r="F149" s="1"/>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A150" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="F136" s="1"/>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="9" t="s">
-        <v>486</v>
-      </c>
-      <c r="F137" s="1"/>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="9" t="s">
-        <v>487</v>
-      </c>
-      <c r="F138" s="1"/>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="9" t="s">
-        <v>488</v>
-      </c>
-      <c r="F139" s="1"/>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="F140" s="1"/>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="9"/>
-      <c r="F141" s="1"/>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="9"/>
-      <c r="F142" s="1"/>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="9"/>
-      <c r="F143" s="1"/>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="9"/>
-      <c r="F144" s="1"/>
-    </row>
-    <row r="145" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F145" s="1"/>
-    </row>
-    <row r="146" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F146" s="1"/>
-    </row>
-    <row r="147" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F147" s="1"/>
-    </row>
-    <row r="148" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F148" s="1"/>
-    </row>
-    <row r="149" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F149" s="1"/>
-    </row>
-    <row r="150" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F150" s="1"/>
     </row>
-    <row r="151" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F151" s="1"/>
     </row>
-    <row r="152" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F152" s="1"/>
     </row>
-    <row r="153" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F153" s="1"/>
     </row>
-    <row r="154" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F154" s="1"/>
     </row>
-    <row r="155" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F155" s="1"/>
     </row>
-    <row r="156" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F156" s="1"/>
     </row>
-    <row r="157" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F157" s="1"/>
     </row>
-    <row r="158" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F158" s="1"/>
     </row>
-    <row r="159" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F159" s="1"/>
     </row>
-    <row r="160" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F160" s="1"/>
     </row>
     <row r="161" spans="6:6" x14ac:dyDescent="0.3">
@@ -6268,15 +6430,15 @@
       <c r="F430" s="1"/>
     </row>
   </sheetData>
-  <sortState ref="D2:F430">
-    <sortCondition descending="1" ref="F2"/>
+  <sortState ref="A1:B430">
+    <sortCondition ref="A1"/>
   </sortState>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="A141 A137:A139">
-    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
+  <conditionalFormatting sqref="A137:A141">
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A141:A1048576 A1:A139">
-    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6293,25 +6455,22 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="B1" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>455</v>
-      </c>
-      <c r="B2" t="s">
-        <v>454</v>
+      <c r="A2" s="9" t="s">
+        <v>491</v>
       </c>
       <c r="H2" s="1"/>
       <c r="M2" s="1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>456</v>
+        <v>473</v>
       </c>
       <c r="B3" t="s">
         <v>454</v>
@@ -6321,7 +6480,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="B4" t="s">
         <v>454</v>
@@ -6331,7 +6490,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B5" t="s">
         <v>454</v>
@@ -6341,7 +6500,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="B6" t="s">
         <v>454</v>
@@ -6351,7 +6510,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="B7" t="s">
         <v>454</v>
@@ -6360,7 +6519,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>461</v>
+        <v>478</v>
       </c>
       <c r="B8" t="s">
         <v>454</v>
@@ -6370,7 +6529,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B9" t="s">
         <v>454</v>
@@ -6380,7 +6539,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>463</v>
+        <v>482</v>
       </c>
       <c r="B10" t="s">
         <v>454</v>
@@ -6390,7 +6549,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="B11" t="s">
         <v>454</v>
@@ -6399,7 +6558,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="B12" t="s">
         <v>454</v>
@@ -6409,7 +6568,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="B13" t="s">
         <v>454</v>
@@ -6419,7 +6578,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B14" t="s">
         <v>454</v>
@@ -6429,7 +6588,7 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B15" t="s">
         <v>454</v>
@@ -6439,7 +6598,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B16" t="s">
         <v>454</v>
@@ -6448,17 +6607,14 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>470</v>
-      </c>
-      <c r="B17" t="s">
-        <v>454</v>
+        <v>484</v>
       </c>
       <c r="H17" s="1"/>
       <c r="M17" s="1"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B18" t="s">
         <v>454</v>
@@ -6468,7 +6624,7 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="B19" t="s">
         <v>454</v>
@@ -6477,18 +6633,15 @@
       <c r="M19" s="1"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>473</v>
-      </c>
-      <c r="B20" t="s">
-        <v>454</v>
+      <c r="A20" s="9" t="s">
+        <v>492</v>
       </c>
       <c r="H20" s="1"/>
       <c r="M20" s="1"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="B21" t="s">
         <v>454</v>
@@ -6498,10 +6651,7 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>475</v>
-      </c>
-      <c r="B22" t="s">
-        <v>454</v>
+        <v>485</v>
       </c>
       <c r="M22" s="1"/>
     </row>
@@ -6517,7 +6667,7 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>477</v>
+        <v>458</v>
       </c>
       <c r="B24" t="s">
         <v>454</v>
@@ -6527,7 +6677,7 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="B25" t="s">
         <v>454</v>
@@ -6537,7 +6687,7 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B26" t="s">
         <v>454</v>
@@ -6547,7 +6697,7 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="B27" t="s">
         <v>454</v>
@@ -6556,7 +6706,7 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>481</v>
+        <v>459</v>
       </c>
       <c r="B28" t="s">
         <v>454</v>
@@ -6566,7 +6716,7 @@
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B29" t="s">
         <v>454</v>
@@ -6576,7 +6726,7 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="B30" t="s">
         <v>454</v>
@@ -6586,28 +6736,40 @@
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>484</v>
+        <v>470</v>
+      </c>
+      <c r="B31" t="s">
+        <v>454</v>
       </c>
       <c r="H31" s="1"/>
       <c r="M31" s="1"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>485</v>
+        <v>467</v>
+      </c>
+      <c r="B32" t="s">
+        <v>454</v>
       </c>
       <c r="H32" s="1"/>
       <c r="M32" s="1"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A33" s="9" t="s">
-        <v>491</v>
+      <c r="A33" t="s">
+        <v>456</v>
+      </c>
+      <c r="B33" t="s">
+        <v>454</v>
       </c>
       <c r="H33" s="1"/>
       <c r="M33" s="1"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A34" s="9" t="s">
-        <v>492</v>
+      <c r="A34" t="s">
+        <v>463</v>
+      </c>
+      <c r="B34" t="s">
+        <v>454</v>
       </c>
       <c r="M34" s="1"/>
     </row>
@@ -6847,14 +7009,14 @@
     </row>
   </sheetData>
   <sortState ref="A1:B100">
-    <sortCondition ref="B1"/>
+    <sortCondition ref="A22"/>
   </sortState>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="A1:A33 A37:A1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TrackingList.xlsx
+++ b/TrackingList.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18096" windowHeight="7932" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18096" windowHeight="7932"/>
   </bookViews>
   <sheets>
     <sheet name="台灣股票" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="524">
   <si>
     <t>26/05 Taiwan 50</t>
   </si>
@@ -1511,11 +1511,11 @@
   </si>
   <si>
     <t>SRVR</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>PSLY</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1532,14 +1532,14 @@
       </rPr>
       <t>R</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>ONDO</t>
   </si>
   <si>
     <t>BX</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>COHR</t>
@@ -1574,11 +1574,11 @@
       </rPr>
       <t>ram</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>光通訊</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1595,18 +1595,18 @@
       </rPr>
       <t>RDO</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>NOK</t>
   </si>
   <si>
     <t>記憶體</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>能源</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1623,38 +1623,90 @@
       </rPr>
       <t>E</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>LITE</t>
   </si>
   <si>
     <t>AXTI</t>
+  </si>
+  <si>
+    <t>TSN</t>
+  </si>
+  <si>
+    <r>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OOD</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CORN</t>
+  </si>
+  <si>
+    <t>WEAT</t>
+  </si>
+  <si>
+    <t>SOYB</t>
+  </si>
+  <si>
+    <t>UNG</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>USO</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>VEGI</t>
+  </si>
+  <si>
+    <t>MOO</t>
+  </si>
+  <si>
+    <t>銅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>XME</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ICOP</t>
+  </si>
+  <si>
+    <t>稀土</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FMTL</t>
+  </si>
+  <si>
+    <t>關鍵金屬ETF</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="新細明體"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF202122"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF232A31"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1698,19 +1750,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -2469,7 +2518,7 @@
   <sortState ref="A1:B57">
     <sortCondition ref="A1"/>
   </sortState>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A68:A1048576 A1:A55">
     <cfRule type="duplicateValues" dxfId="7" priority="2"/>
   </conditionalFormatting>
@@ -2486,718 +2535,718 @@
   <dimension ref="A1:B142"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.5" style="6" customWidth="1"/>
-    <col min="2" max="2" width="9.5" style="7" customWidth="1"/>
-    <col min="3" max="16384" width="9" style="6"/>
+    <col min="1" max="1" width="9.5" style="4" customWidth="1"/>
+    <col min="2" max="2" width="9.5" style="5" customWidth="1"/>
+    <col min="3" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="4" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="4" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="4" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="4" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="4" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="4" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="4" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="4" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="4" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" s="6" t="s">
+      <c r="A32" s="4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="4" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="4" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="4" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="4" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="4" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="4" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="4" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" s="6" t="s">
+      <c r="A41" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="4" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" s="6" t="s">
+      <c r="A44" s="4" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" s="6" t="s">
+      <c r="A45" s="4" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="4" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" s="6" t="s">
+      <c r="A47" s="4" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" s="6" t="s">
+      <c r="A48" s="4" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" s="6" t="s">
+      <c r="A49" s="4" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" s="6" t="s">
+      <c r="A50" s="4" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" s="6" t="s">
+      <c r="A51" s="4" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" s="6" t="s">
+      <c r="A52" s="4" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" s="6" t="s">
+      <c r="A53" s="4" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" s="6" t="s">
+      <c r="A54" s="4" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" s="6" t="s">
+      <c r="A55" s="4" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A56" s="6" t="s">
+      <c r="A56" s="4" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A57" s="6" t="s">
+      <c r="A57" s="4" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" s="6" t="s">
+      <c r="A58" s="4" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59" s="6" t="s">
+      <c r="A59" s="4" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60" s="6" t="s">
+      <c r="A60" s="4" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61" s="6" t="s">
+      <c r="A61" s="4" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A62" s="6" t="s">
+      <c r="A62" s="4" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A63" s="6" t="s">
+      <c r="A63" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A64" s="6" t="s">
+      <c r="A64" s="4" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" s="6" t="s">
+      <c r="A65" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" s="6" t="s">
+      <c r="A66" s="4" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" s="6" t="s">
+      <c r="A67" s="4" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" s="6" t="s">
+      <c r="A68" s="4" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69" s="6" t="s">
+      <c r="A69" s="4" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70" s="6" t="s">
+      <c r="A70" s="4" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" s="6" t="s">
+      <c r="A71" s="4" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A72" s="6" t="s">
+      <c r="A72" s="4" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A73" s="6" t="s">
+      <c r="A73" s="4" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A74" s="6" t="s">
+      <c r="A74" s="4" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A75" s="6" t="s">
+      <c r="A75" s="4" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A76" s="6" t="s">
+      <c r="A76" s="4" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A77" s="6" t="s">
+      <c r="A77" s="4" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A78" s="6" t="s">
+      <c r="A78" s="4" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A79" s="6" t="s">
+      <c r="A79" s="4" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A80" s="6" t="s">
+      <c r="A80" s="4" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A81" s="6" t="s">
+      <c r="A81" s="4" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A82" s="6" t="s">
+      <c r="A82" s="4" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A83" s="6" t="s">
+      <c r="A83" s="4" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A84" s="6" t="s">
+      <c r="A84" s="4" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A85" s="6" t="s">
+      <c r="A85" s="4" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A86" s="6" t="s">
+      <c r="A86" s="4" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A87" s="6" t="s">
+      <c r="A87" s="4" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A88" s="6" t="s">
+      <c r="A88" s="4" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A89" s="6" t="s">
+      <c r="A89" s="4" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A90" s="6" t="s">
+      <c r="A90" s="4" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A91" s="6" t="s">
+      <c r="A91" s="4" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A92" s="6" t="s">
+      <c r="A92" s="4" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A93" s="6" t="s">
+      <c r="A93" s="4" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A94" s="6" t="s">
+      <c r="A94" s="4" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A95" s="6" t="s">
+      <c r="A95" s="4" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A96" s="6" t="s">
+      <c r="A96" s="4" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A97" s="6" t="s">
+      <c r="A97" s="4" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A98" s="6" t="s">
+      <c r="A98" s="4" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A99" s="6" t="s">
+      <c r="A99" s="4" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A100" s="6" t="s">
+      <c r="A100" s="4" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A101" s="6" t="s">
+      <c r="A101" s="4" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A102" s="6" t="s">
+      <c r="A102" s="4" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A103" s="6" t="s">
+      <c r="A103" s="4" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A104" s="6" t="s">
+      <c r="A104" s="4" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A105" s="6" t="s">
+      <c r="A105" s="4" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A106" s="6" t="s">
+      <c r="A106" s="4" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A107" s="6" t="s">
+      <c r="A107" s="4" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A108" s="6" t="s">
+      <c r="A108" s="4" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A109" s="6" t="s">
+      <c r="A109" s="4" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A110" s="6" t="s">
+      <c r="A110" s="4" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A111" s="6" t="s">
+      <c r="A111" s="4" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A112" s="6" t="s">
+      <c r="A112" s="4" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A113" s="6" t="s">
+      <c r="A113" s="4" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A114" s="6" t="s">
+      <c r="A114" s="4" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A115" s="6" t="s">
+      <c r="A115" s="4" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A116" s="6" t="s">
+      <c r="A116" s="4" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A117" s="6" t="s">
+      <c r="A117" s="4" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A118" s="6" t="s">
+      <c r="A118" s="4" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A119" s="6" t="s">
+      <c r="A119" s="4" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A120" s="6" t="s">
+      <c r="A120" s="4" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A121" s="6" t="s">
+      <c r="A121" s="4" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A122" s="6" t="s">
+      <c r="A122" s="4" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A123" s="6" t="s">
+      <c r="A123" s="4" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A124" s="6" t="s">
+      <c r="A124" s="4" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A125" s="6" t="s">
+      <c r="A125" s="4" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A126" s="6" t="s">
+      <c r="A126" s="4" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A127" s="6" t="s">
+      <c r="A127" s="4" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A128" s="6" t="s">
+      <c r="A128" s="4" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A129" s="8" t="s">
+      <c r="A129" s="6" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A130" s="8" t="s">
+      <c r="A130" s="6" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A131" s="8" t="s">
+      <c r="A131" s="6" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A132" s="8" t="s">
+      <c r="A132" s="6" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A133" s="8" t="s">
+      <c r="A133" s="6" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A134" s="8" t="s">
+      <c r="A134" s="6" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A135" s="8" t="s">
+      <c r="A135" s="6" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A136" s="8" t="s">
+      <c r="A136" s="6" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A137" s="8" t="s">
+      <c r="A137" s="6" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A138" s="8" t="s">
+      <c r="A138" s="6" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A139" s="8" t="s">
+      <c r="A139" s="6" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A140" s="8" t="s">
+      <c r="A140" s="6" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A141" s="8" t="s">
+      <c r="A141" s="6" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A142" s="6" t="s">
+      <c r="A142" s="4" t="s">
         <v>142</v>
       </c>
     </row>
@@ -3205,7 +3254,7 @@
   <sortState ref="A1:A142">
     <sortCondition ref="A1"/>
   </sortState>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3215,364 +3264,364 @@
   <dimension ref="A1:I216"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="3" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="3" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="3" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="3" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="3" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="3" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="3" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="3" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="3" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="3" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="3" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="3" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="3" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="3" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="7" t="s">
         <v>504</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="3" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="3" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="3" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="3" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="3" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="3" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="3" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="3" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="3" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="3" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" s="5" t="s">
+      <c r="A42" s="3" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" s="5" t="s">
+      <c r="A43" s="3" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" s="5" t="s">
+      <c r="A44" s="3" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" s="5" t="s">
+      <c r="A45" s="3" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46" s="5" t="s">
+      <c r="A46" s="3" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" s="5" t="s">
+      <c r="A47" s="3" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" s="5" t="s">
+      <c r="A48" s="3" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" s="5" t="s">
+      <c r="A49" s="3" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" s="5" t="s">
+      <c r="A50" s="3" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" s="5" t="s">
+      <c r="A51" s="3" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" s="5" t="s">
+      <c r="A52" s="3" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" s="5" t="s">
+      <c r="A53" s="3" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" s="5" t="s">
+      <c r="A54" s="3" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" s="5" t="s">
+      <c r="A55" s="3" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A56" s="5" t="s">
+      <c r="A56" s="3" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A57" s="5" t="s">
+      <c r="A57" s="3" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" s="5" t="s">
+      <c r="A58" s="3" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59" s="5" t="s">
+      <c r="A59" s="3" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60" s="5" t="s">
+      <c r="A60" s="3" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61" s="5" t="s">
+      <c r="A61" s="3" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A62" s="5" t="s">
+      <c r="A62" s="3" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A63" s="5" t="s">
+      <c r="A63" s="3" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A64" s="5" t="s">
+      <c r="A64" s="3" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" s="5" t="s">
+      <c r="A65" s="3" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" s="5" t="s">
+      <c r="A66" s="3" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" s="5" t="s">
+      <c r="A67" s="3" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" s="5" t="s">
+      <c r="A68" s="3" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69" s="5" t="s">
+      <c r="A69" s="3" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70" s="5" t="s">
+      <c r="A70" s="3" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" s="5" t="s">
+      <c r="A71" s="3" t="s">
         <v>212</v>
       </c>
     </row>
@@ -3582,682 +3631,682 @@
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A73" s="5" t="s">
+      <c r="A73" s="3" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A74" s="5" t="s">
+      <c r="A74" s="3" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A75" s="5" t="s">
+      <c r="A75" s="3" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A76" s="5" t="s">
+      <c r="A76" s="3" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A77" s="5" t="s">
+      <c r="A77" s="3" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A78" s="5" t="s">
+      <c r="A78" s="3" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A79" s="5" t="s">
+      <c r="A79" s="3" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A80" s="5" t="s">
+      <c r="A80" s="3" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A81" s="5" t="s">
+      <c r="A81" s="3" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A82" s="5" t="s">
+      <c r="A82" s="3" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A83" s="5" t="s">
+      <c r="A83" s="3" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A84" s="5" t="s">
+      <c r="A84" s="3" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A85" s="5" t="s">
+      <c r="A85" s="3" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A86" s="5" t="s">
+      <c r="A86" s="3" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A87" s="5" t="s">
+      <c r="A87" s="3" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A88" s="5" t="s">
+      <c r="A88" s="3" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A89" s="5" t="s">
+      <c r="A89" s="3" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A90" s="5" t="s">
+      <c r="A90" s="3" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A91" s="5" t="s">
+      <c r="A91" s="3" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A92" s="5" t="s">
+      <c r="A92" s="3" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A93" s="5" t="s">
+      <c r="A93" s="3" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A94" s="10" t="s">
+      <c r="A94" s="8" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A95" s="5" t="s">
+      <c r="A95" s="3" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A96" s="5" t="s">
+      <c r="A96" s="3" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A97" s="5" t="s">
+      <c r="A97" s="3" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A98" s="5" t="s">
+      <c r="A98" s="3" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A99" s="5" t="s">
+      <c r="A99" s="3" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A100" s="5" t="s">
+      <c r="A100" s="3" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A101" s="5" t="s">
+      <c r="A101" s="3" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A102" s="5" t="s">
+      <c r="A102" s="3" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A103" s="5" t="s">
+      <c r="A103" s="3" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A104" s="5" t="s">
+      <c r="A104" s="3" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A105" s="5" t="s">
+      <c r="A105" s="3" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A106" s="5" t="s">
+      <c r="A106" s="3" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A107" s="5" t="s">
+      <c r="A107" s="3" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A108" s="5" t="s">
+      <c r="A108" s="3" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A109" s="5" t="s">
+      <c r="A109" s="3" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A110" s="5" t="s">
+      <c r="A110" s="3" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A111" s="5" t="s">
+      <c r="A111" s="3" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A112" s="5" t="s">
+      <c r="A112" s="3" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A113" s="5" t="s">
+      <c r="A113" s="3" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A114" s="5" t="s">
+      <c r="A114" s="3" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A115" s="5" t="s">
+      <c r="A115" s="3" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A116" s="5" t="s">
+      <c r="A116" s="3" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A117" s="5" t="s">
+      <c r="A117" s="3" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A118" s="5" t="s">
+      <c r="A118" s="3" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A119" s="5" t="s">
+      <c r="A119" s="3" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A120" s="5" t="s">
+      <c r="A120" s="3" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A121" s="5" t="s">
+      <c r="A121" s="3" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A122" s="5" t="s">
+      <c r="A122" s="3" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A123" s="10" t="s">
+      <c r="A123" s="8" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A124" s="5" t="s">
+      <c r="A124" s="3" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A125" s="5" t="s">
+      <c r="A125" s="3" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A126" s="5" t="s">
+      <c r="A126" s="3" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A127" s="5" t="s">
+      <c r="A127" s="3" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A128" s="5" t="s">
+      <c r="A128" s="3" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A129" s="5" t="s">
+      <c r="A129" s="3" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A130" s="5" t="s">
+      <c r="A130" s="3" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A131" s="5" t="s">
+      <c r="A131" s="3" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A132" s="5" t="s">
+      <c r="A132" s="3" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A133" s="5" t="s">
+      <c r="A133" s="3" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A134" s="5" t="s">
+      <c r="A134" s="3" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A135" s="5" t="s">
+      <c r="A135" s="3" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A136" s="5" t="s">
+      <c r="A136" s="3" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A137" s="5" t="s">
+      <c r="A137" s="3" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A138" s="5" t="s">
+      <c r="A138" s="3" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A139" s="5" t="s">
+      <c r="A139" s="3" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A140" s="5" t="s">
+      <c r="A140" s="3" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A141" s="5" t="s">
+      <c r="A141" s="3" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A142" s="5" t="s">
+      <c r="A142" s="3" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A143" s="5" t="s">
+      <c r="A143" s="3" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A144" s="5" t="s">
+      <c r="A144" s="3" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A145" s="5" t="s">
+      <c r="A145" s="3" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A146" s="5" t="s">
+      <c r="A146" s="3" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A147" s="5" t="s">
+      <c r="A147" s="3" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A148" s="5" t="s">
+      <c r="A148" s="3" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A149" s="5" t="s">
+      <c r="A149" s="3" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A150" s="5" t="s">
+      <c r="A150" s="3" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A151" s="5" t="s">
+      <c r="A151" s="3" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A152" s="5" t="s">
+      <c r="A152" s="3" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A153" s="5" t="s">
+      <c r="A153" s="3" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A154" s="5" t="s">
+      <c r="A154" s="3" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A155" s="5" t="s">
+      <c r="A155" s="3" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A156" s="5" t="s">
+      <c r="A156" s="3" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A157" s="5" t="s">
+      <c r="A157" s="3" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A158" s="5" t="s">
+      <c r="A158" s="3" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A159" s="5" t="s">
+      <c r="A159" s="3" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A160" s="5" t="s">
+      <c r="A160" s="3" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A161" s="5" t="s">
+      <c r="A161" s="3" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A162" s="5" t="s">
+      <c r="A162" s="3" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A163" s="5" t="s">
+      <c r="A163" s="3" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A164" s="5" t="s">
+      <c r="A164" s="3" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A165" s="5" t="s">
+      <c r="A165" s="3" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A166" s="5" t="s">
+      <c r="A166" s="3" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A167" s="5" t="s">
+      <c r="A167" s="3" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A168" s="5" t="s">
+      <c r="A168" s="3" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A169" s="5" t="s">
+      <c r="A169" s="3" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A170" s="5" t="s">
+      <c r="A170" s="3" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A171" s="5" t="s">
+      <c r="A171" s="3" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A172" s="5" t="s">
+      <c r="A172" s="3" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A173" s="5" t="s">
+      <c r="A173" s="3" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A174" s="5" t="s">
+      <c r="A174" s="3" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A175" s="5" t="s">
+      <c r="A175" s="3" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A176" s="5" t="s">
+      <c r="A176" s="3" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A186" s="10"/>
+      <c r="A186" s="8"/>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A187" s="10"/>
+      <c r="A187" s="8"/>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A189" s="10"/>
+      <c r="A189" s="8"/>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A191" s="10"/>
+      <c r="A191" s="8"/>
     </row>
     <row r="203" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B203" s="5"/>
-      <c r="C203" s="5"/>
-      <c r="D203" s="5"/>
-      <c r="E203" s="5"/>
-      <c r="F203" s="5"/>
-      <c r="G203" s="5"/>
-      <c r="H203" s="5"/>
-      <c r="I203" s="5"/>
+      <c r="B203" s="3"/>
+      <c r="C203" s="3"/>
+      <c r="D203" s="3"/>
+      <c r="E203" s="3"/>
+      <c r="F203" s="3"/>
+      <c r="G203" s="3"/>
+      <c r="H203" s="3"/>
+      <c r="I203" s="3"/>
     </row>
     <row r="204" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B204" s="5"/>
-      <c r="C204" s="5"/>
-      <c r="D204" s="5"/>
-      <c r="E204" s="5"/>
-      <c r="F204" s="5"/>
-      <c r="G204" s="5"/>
-      <c r="H204" s="5"/>
-      <c r="I204" s="5"/>
+      <c r="B204" s="3"/>
+      <c r="C204" s="3"/>
+      <c r="D204" s="3"/>
+      <c r="E204" s="3"/>
+      <c r="F204" s="3"/>
+      <c r="G204" s="3"/>
+      <c r="H204" s="3"/>
+      <c r="I204" s="3"/>
     </row>
     <row r="205" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B205" s="5"/>
-      <c r="C205" s="5"/>
-      <c r="D205" s="5"/>
-      <c r="E205" s="5"/>
-      <c r="F205" s="5"/>
-      <c r="G205" s="5"/>
-      <c r="H205" s="5"/>
-      <c r="I205" s="5"/>
+      <c r="B205" s="3"/>
+      <c r="C205" s="3"/>
+      <c r="D205" s="3"/>
+      <c r="E205" s="3"/>
+      <c r="F205" s="3"/>
+      <c r="G205" s="3"/>
+      <c r="H205" s="3"/>
+      <c r="I205" s="3"/>
     </row>
     <row r="206" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B206" s="5"/>
-      <c r="C206" s="5"/>
-      <c r="D206" s="5"/>
-      <c r="E206" s="5"/>
-      <c r="F206" s="5"/>
-      <c r="G206" s="5"/>
-      <c r="H206" s="5"/>
-      <c r="I206" s="5"/>
+      <c r="B206" s="3"/>
+      <c r="C206" s="3"/>
+      <c r="D206" s="3"/>
+      <c r="E206" s="3"/>
+      <c r="F206" s="3"/>
+      <c r="G206" s="3"/>
+      <c r="H206" s="3"/>
+      <c r="I206" s="3"/>
     </row>
     <row r="207" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B207" s="5"/>
-      <c r="C207" s="5"/>
-      <c r="D207" s="5"/>
-      <c r="E207" s="5"/>
-      <c r="F207" s="5"/>
-      <c r="G207" s="5"/>
-      <c r="H207" s="5"/>
-      <c r="I207" s="5"/>
+      <c r="B207" s="3"/>
+      <c r="C207" s="3"/>
+      <c r="D207" s="3"/>
+      <c r="E207" s="3"/>
+      <c r="F207" s="3"/>
+      <c r="G207" s="3"/>
+      <c r="H207" s="3"/>
+      <c r="I207" s="3"/>
     </row>
     <row r="208" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B208" s="5"/>
-      <c r="C208" s="5"/>
-      <c r="D208" s="5"/>
-      <c r="E208" s="5"/>
-      <c r="F208" s="5"/>
-      <c r="G208" s="5"/>
-      <c r="H208" s="5"/>
-      <c r="I208" s="5"/>
+      <c r="B208" s="3"/>
+      <c r="C208" s="3"/>
+      <c r="D208" s="3"/>
+      <c r="E208" s="3"/>
+      <c r="F208" s="3"/>
+      <c r="G208" s="3"/>
+      <c r="H208" s="3"/>
+      <c r="I208" s="3"/>
     </row>
     <row r="209" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B209" s="5"/>
-      <c r="C209" s="5"/>
-      <c r="D209" s="5"/>
-      <c r="E209" s="5"/>
-      <c r="F209" s="5"/>
-      <c r="G209" s="5"/>
-      <c r="H209" s="5"/>
-      <c r="I209" s="5"/>
+      <c r="B209" s="3"/>
+      <c r="C209" s="3"/>
+      <c r="D209" s="3"/>
+      <c r="E209" s="3"/>
+      <c r="F209" s="3"/>
+      <c r="G209" s="3"/>
+      <c r="H209" s="3"/>
+      <c r="I209" s="3"/>
     </row>
     <row r="210" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B210" s="5"/>
-      <c r="C210" s="5"/>
-      <c r="D210" s="5"/>
-      <c r="E210" s="5"/>
-      <c r="F210" s="5"/>
-      <c r="G210" s="5"/>
-      <c r="H210" s="5"/>
-      <c r="I210" s="5"/>
+      <c r="B210" s="3"/>
+      <c r="C210" s="3"/>
+      <c r="D210" s="3"/>
+      <c r="E210" s="3"/>
+      <c r="F210" s="3"/>
+      <c r="G210" s="3"/>
+      <c r="H210" s="3"/>
+      <c r="I210" s="3"/>
     </row>
     <row r="211" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B211" s="5"/>
-      <c r="C211" s="5"/>
-      <c r="D211" s="5"/>
-      <c r="E211" s="5"/>
-      <c r="F211" s="5"/>
-      <c r="G211" s="5"/>
-      <c r="H211" s="5"/>
-      <c r="I211" s="5"/>
+      <c r="B211" s="3"/>
+      <c r="C211" s="3"/>
+      <c r="D211" s="3"/>
+      <c r="E211" s="3"/>
+      <c r="F211" s="3"/>
+      <c r="G211" s="3"/>
+      <c r="H211" s="3"/>
+      <c r="I211" s="3"/>
     </row>
     <row r="212" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B212" s="5"/>
-      <c r="C212" s="5"/>
-      <c r="D212" s="5"/>
-      <c r="E212" s="5"/>
-      <c r="F212" s="5"/>
-      <c r="G212" s="5"/>
-      <c r="H212" s="5"/>
-      <c r="I212" s="5"/>
+      <c r="B212" s="3"/>
+      <c r="C212" s="3"/>
+      <c r="D212" s="3"/>
+      <c r="E212" s="3"/>
+      <c r="F212" s="3"/>
+      <c r="G212" s="3"/>
+      <c r="H212" s="3"/>
+      <c r="I212" s="3"/>
     </row>
     <row r="213" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B213" s="5"/>
-      <c r="C213" s="5"/>
-      <c r="D213" s="5"/>
-      <c r="E213" s="5"/>
-      <c r="F213" s="5"/>
-      <c r="G213" s="5"/>
-      <c r="H213" s="5"/>
-      <c r="I213" s="5"/>
+      <c r="B213" s="3"/>
+      <c r="C213" s="3"/>
+      <c r="D213" s="3"/>
+      <c r="E213" s="3"/>
+      <c r="F213" s="3"/>
+      <c r="G213" s="3"/>
+      <c r="H213" s="3"/>
+      <c r="I213" s="3"/>
     </row>
     <row r="214" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B214" s="5"/>
-      <c r="C214" s="5"/>
-      <c r="D214" s="5"/>
-      <c r="E214" s="5"/>
-      <c r="F214" s="5"/>
-      <c r="G214" s="5"/>
-      <c r="H214" s="5"/>
-      <c r="I214" s="5"/>
+      <c r="B214" s="3"/>
+      <c r="C214" s="3"/>
+      <c r="D214" s="3"/>
+      <c r="E214" s="3"/>
+      <c r="F214" s="3"/>
+      <c r="G214" s="3"/>
+      <c r="H214" s="3"/>
+      <c r="I214" s="3"/>
     </row>
     <row r="215" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B215" s="5"/>
-      <c r="C215" s="5"/>
-      <c r="D215" s="5"/>
-      <c r="E215" s="5"/>
-      <c r="F215" s="5"/>
-      <c r="G215" s="5"/>
-      <c r="H215" s="5"/>
-      <c r="I215" s="5"/>
+      <c r="B215" s="3"/>
+      <c r="C215" s="3"/>
+      <c r="D215" s="3"/>
+      <c r="E215" s="3"/>
+      <c r="F215" s="3"/>
+      <c r="G215" s="3"/>
+      <c r="H215" s="3"/>
+      <c r="I215" s="3"/>
     </row>
     <row r="216" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B216" s="5"/>
-      <c r="C216" s="5"/>
-      <c r="D216" s="5"/>
-      <c r="E216" s="5"/>
-      <c r="F216" s="5"/>
-      <c r="G216" s="5"/>
-      <c r="H216" s="5"/>
-      <c r="I216" s="5"/>
+      <c r="B216" s="3"/>
+      <c r="C216" s="3"/>
+      <c r="D216" s="3"/>
+      <c r="E216" s="3"/>
+      <c r="F216" s="3"/>
+      <c r="G216" s="3"/>
+      <c r="H216" s="3"/>
+      <c r="I216" s="3"/>
     </row>
   </sheetData>
   <sortState ref="A1:B216">
     <sortCondition ref="A1"/>
   </sortState>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1:A183 A192:A1048576">
     <cfRule type="duplicateValues" dxfId="5" priority="3"/>
   </conditionalFormatting>
@@ -4485,7 +4534,7 @@
       <c r="A14" t="s">
         <v>508</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" t="s">
         <v>501</v>
       </c>
       <c r="F14" s="1"/>
@@ -4515,22 +4564,22 @@
       <c r="F17" s="1"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="11" t="s">
+      <c r="A18" t="s">
         <v>506</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" t="s">
         <v>505</v>
       </c>
       <c r="F18" s="1"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+      <c r="A19" t="s">
         <v>333</v>
       </c>
       <c r="F19" s="1"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
+      <c r="A20" t="s">
         <v>334</v>
       </c>
       <c r="F20" s="1"/>
@@ -4581,7 +4630,7 @@
       <c r="F25" s="1"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="9" t="s">
+      <c r="A26" t="s">
         <v>493</v>
       </c>
       <c r="F26" s="1"/>
@@ -4605,19 +4654,19 @@
       <c r="F28" s="1"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
+      <c r="A29" t="s">
         <v>342</v>
       </c>
       <c r="F29" s="1"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="9" t="s">
+      <c r="A30" t="s">
         <v>487</v>
       </c>
       <c r="F30" s="1"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="9" t="s">
+      <c r="A31" t="s">
         <v>486</v>
       </c>
       <c r="F31" s="1"/>
@@ -4626,7 +4675,7 @@
       <c r="A32" t="s">
         <v>499</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" t="s">
         <v>501</v>
       </c>
       <c r="F32" s="1"/>
@@ -4659,10 +4708,10 @@
       <c r="F35" s="1"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="9" t="s">
+      <c r="A36" t="s">
         <v>494</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="B36" t="s">
         <v>501</v>
       </c>
       <c r="F36" s="1"/>
@@ -4678,25 +4727,25 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>347</v>
+        <v>163</v>
       </c>
       <c r="B38" t="s">
-        <v>317</v>
+        <v>518</v>
       </c>
       <c r="F38" s="1"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="11" t="s">
-        <v>502</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>501</v>
+      <c r="A39" t="s">
+        <v>511</v>
+      </c>
+      <c r="B39" t="s">
+        <v>510</v>
       </c>
       <c r="F39" s="1"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B40" t="s">
         <v>317</v>
@@ -4705,13 +4754,16 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>349</v>
+        <v>502</v>
+      </c>
+      <c r="B41" t="s">
+        <v>501</v>
       </c>
       <c r="F41" s="1"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B42" t="s">
         <v>317</v>
@@ -4719,14 +4771,14 @@
       <c r="F42" s="1"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
-        <v>351</v>
+      <c r="A43" t="s">
+        <v>349</v>
       </c>
       <c r="F43" s="1"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B44" t="s">
         <v>317</v>
@@ -4735,16 +4787,13 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>353</v>
-      </c>
-      <c r="B45" t="s">
-        <v>317</v>
+        <v>351</v>
       </c>
       <c r="F45" s="1"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B46" t="s">
         <v>317</v>
@@ -4753,7 +4802,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B47" t="s">
         <v>317</v>
@@ -4762,22 +4811,25 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>356</v>
+        <v>169</v>
       </c>
       <c r="B48" t="s">
-        <v>317</v>
+        <v>510</v>
       </c>
       <c r="F48" s="1"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
-        <v>357</v>
+      <c r="A49" t="s">
+        <v>354</v>
+      </c>
+      <c r="B49" t="s">
+        <v>317</v>
       </c>
       <c r="F49" s="1"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B50" t="s">
         <v>317</v>
@@ -4786,7 +4838,7 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B51" t="s">
         <v>317</v>
@@ -4794,23 +4846,23 @@
       <c r="F51" s="1"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="9" t="s">
-        <v>488</v>
-      </c>
-      <c r="B52" s="9" t="s">
-        <v>505</v>
+      <c r="A52" t="s">
+        <v>357</v>
       </c>
       <c r="F52" s="1"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>360</v>
+        <v>358</v>
+      </c>
+      <c r="B53" t="s">
+        <v>317</v>
       </c>
       <c r="F53" s="1"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B54" t="s">
         <v>317</v>
@@ -4819,22 +4871,22 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>362</v>
+        <v>488</v>
       </c>
       <c r="B55" t="s">
-        <v>317</v>
+        <v>505</v>
       </c>
       <c r="F55" s="1"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="F56" s="1"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B57" t="s">
         <v>317</v>
@@ -4843,16 +4895,16 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>365</v>
+        <v>522</v>
       </c>
       <c r="B58" t="s">
-        <v>317</v>
+        <v>523</v>
       </c>
       <c r="F58" s="1"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="B59" t="s">
         <v>317</v>
@@ -4860,17 +4912,14 @@
       <c r="F59" s="1"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="9" t="s">
-        <v>498</v>
-      </c>
-      <c r="B60" s="9" t="s">
-        <v>501</v>
+      <c r="A60" t="s">
+        <v>363</v>
       </c>
       <c r="F60" s="1"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B61" t="s">
         <v>317</v>
@@ -4879,7 +4928,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B62" t="s">
         <v>317</v>
@@ -4888,7 +4937,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B63" t="s">
         <v>317</v>
@@ -4897,16 +4946,16 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>370</v>
+        <v>498</v>
       </c>
       <c r="B64" t="s">
-        <v>317</v>
+        <v>501</v>
       </c>
       <c r="F64" s="1"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="B65" t="s">
         <v>317</v>
@@ -4915,13 +4964,16 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>372</v>
+        <v>368</v>
+      </c>
+      <c r="B66" t="s">
+        <v>317</v>
       </c>
       <c r="F66" s="1"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="B67" t="s">
         <v>317</v>
@@ -4930,7 +4982,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="B68" t="s">
         <v>317</v>
@@ -4938,23 +4990,23 @@
       <c r="F68" s="1"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="9" t="s">
-        <v>495</v>
+      <c r="A69" t="s">
+        <v>371</v>
+      </c>
+      <c r="B69" t="s">
+        <v>317</v>
       </c>
       <c r="F69" s="1"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>375</v>
-      </c>
-      <c r="B70" t="s">
-        <v>317</v>
+        <v>372</v>
       </c>
       <c r="F70" s="1"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B71" t="s">
         <v>317</v>
@@ -4963,7 +5015,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B72" t="s">
         <v>317</v>
@@ -4972,25 +5024,31 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>378</v>
+        <v>520</v>
+      </c>
+      <c r="B73" t="s">
+        <v>518</v>
       </c>
       <c r="F73" s="1"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
-        <v>379</v>
+      <c r="A74" t="s">
+        <v>495</v>
       </c>
       <c r="F74" s="1"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
-        <v>380</v>
+      <c r="A75" t="s">
+        <v>375</v>
+      </c>
+      <c r="B75" t="s">
+        <v>317</v>
       </c>
       <c r="F75" s="1"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="B76" t="s">
         <v>317</v>
@@ -4999,7 +5057,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="B77" t="s">
         <v>317</v>
@@ -5008,40 +5066,34 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>383</v>
-      </c>
-      <c r="B78" t="s">
-        <v>317</v>
+        <v>378</v>
       </c>
       <c r="F78" s="1"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
-        <v>384</v>
+      <c r="A79" t="s">
+        <v>379</v>
       </c>
       <c r="F79" s="1"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>385</v>
-      </c>
-      <c r="B80" t="s">
-        <v>317</v>
+        <v>380</v>
       </c>
       <c r="F80" s="1"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>507</v>
-      </c>
-      <c r="B81" s="9" t="s">
-        <v>501</v>
+        <v>381</v>
+      </c>
+      <c r="B81" t="s">
+        <v>317</v>
       </c>
       <c r="F81" s="1"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="B82" t="s">
         <v>317</v>
@@ -5050,7 +5102,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B83" t="s">
         <v>317</v>
@@ -5058,14 +5110,14 @@
       <c r="F83" s="1"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="2" t="s">
-        <v>388</v>
+      <c r="A84" t="s">
+        <v>384</v>
       </c>
       <c r="F84" s="1"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="B85" t="s">
         <v>317</v>
@@ -5074,37 +5126,40 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>390</v>
+        <v>507</v>
       </c>
       <c r="B86" t="s">
-        <v>317</v>
+        <v>501</v>
       </c>
       <c r="F86" s="1"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>391</v>
+        <v>386</v>
+      </c>
+      <c r="B87" t="s">
+        <v>317</v>
       </c>
       <c r="F87" s="1"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="2" t="s">
-        <v>392</v>
+      <c r="A88" t="s">
+        <v>387</v>
+      </c>
+      <c r="B88" t="s">
+        <v>317</v>
       </c>
       <c r="F88" s="1"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>393</v>
-      </c>
-      <c r="B89" t="s">
-        <v>317</v>
+        <v>388</v>
       </c>
       <c r="F89" s="1"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B90" t="s">
         <v>317</v>
@@ -5113,7 +5168,7 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="B91" t="s">
         <v>317</v>
@@ -5122,25 +5177,19 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>396</v>
-      </c>
-      <c r="B92" t="s">
-        <v>317</v>
+        <v>391</v>
       </c>
       <c r="F92" s="1"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>397</v>
-      </c>
-      <c r="B93" t="s">
-        <v>317</v>
+        <v>392</v>
       </c>
       <c r="F93" s="1"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="B94" t="s">
         <v>317</v>
@@ -5149,7 +5198,7 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="B95" t="s">
         <v>317</v>
@@ -5158,7 +5207,7 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="B96" t="s">
         <v>317</v>
@@ -5167,7 +5216,7 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="B97" t="s">
         <v>317</v>
@@ -5176,7 +5225,7 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="B98" t="s">
         <v>317</v>
@@ -5185,7 +5234,7 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="B99" t="s">
         <v>317</v>
@@ -5194,22 +5243,25 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>404</v>
+        <v>399</v>
+      </c>
+      <c r="B100" t="s">
+        <v>317</v>
       </c>
       <c r="F100" s="1"/>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>405</v>
+        <v>517</v>
       </c>
       <c r="B101" t="s">
-        <v>317</v>
+        <v>510</v>
       </c>
       <c r="F101" s="1"/>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="B102" t="s">
         <v>317</v>
@@ -5218,7 +5270,7 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="B103" t="s">
         <v>317</v>
@@ -5226,95 +5278,101 @@
       <c r="F103" s="1"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="2" t="s">
-        <v>408</v>
+      <c r="A104" t="s">
+        <v>402</v>
+      </c>
+      <c r="B104" t="s">
+        <v>317</v>
       </c>
       <c r="F104" s="1"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>503</v>
-      </c>
-      <c r="B105" s="9" t="s">
-        <v>501</v>
+        <v>403</v>
+      </c>
+      <c r="B105" t="s">
+        <v>317</v>
       </c>
       <c r="F105" s="1"/>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>409</v>
-      </c>
-      <c r="B106" t="s">
-        <v>317</v>
+        <v>404</v>
       </c>
       <c r="F106" s="1"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>410</v>
+        <v>405</v>
+      </c>
+      <c r="B107" t="s">
+        <v>317</v>
       </c>
       <c r="F107" s="1"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="2" t="s">
-        <v>411</v>
+      <c r="A108" t="s">
+        <v>406</v>
+      </c>
+      <c r="B108" t="s">
+        <v>317</v>
       </c>
       <c r="F108" s="1"/>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>412</v>
+        <v>407</v>
+      </c>
+      <c r="B109" t="s">
+        <v>317</v>
       </c>
       <c r="F109" s="1"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>413</v>
-      </c>
-      <c r="B110" t="s">
-        <v>317</v>
+        <v>408</v>
       </c>
       <c r="F110" s="1"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>414</v>
+        <v>503</v>
       </c>
       <c r="B111" t="s">
-        <v>317</v>
+        <v>501</v>
       </c>
       <c r="F111" s="1"/>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>415</v>
+        <v>409</v>
+      </c>
+      <c r="B112" t="s">
+        <v>317</v>
       </c>
       <c r="F112" s="1"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="F113" s="1"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="2" t="s">
-        <v>417</v>
+      <c r="A114" t="s">
+        <v>411</v>
       </c>
       <c r="F114" s="1"/>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>418</v>
-      </c>
-      <c r="B115" t="s">
-        <v>317</v>
+        <v>412</v>
       </c>
       <c r="F115" s="1"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="B116" t="s">
         <v>317</v>
@@ -5323,7 +5381,7 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="B117" t="s">
         <v>317</v>
@@ -5332,34 +5390,25 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>421</v>
-      </c>
-      <c r="B118" t="s">
-        <v>317</v>
+        <v>415</v>
       </c>
       <c r="F118" s="1"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>422</v>
-      </c>
-      <c r="B119" t="s">
-        <v>317</v>
+        <v>416</v>
       </c>
       <c r="F119" s="1"/>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>423</v>
-      </c>
-      <c r="B120" t="s">
-        <v>317</v>
+        <v>417</v>
       </c>
       <c r="F120" s="1"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="B121" t="s">
         <v>317</v>
@@ -5367,14 +5416,17 @@
       <c r="F121" s="1"/>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="3" t="s">
-        <v>425</v>
+      <c r="A122" t="s">
+        <v>419</v>
+      </c>
+      <c r="B122" t="s">
+        <v>317</v>
       </c>
       <c r="F122" s="1"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="B123" t="s">
         <v>317</v>
@@ -5383,7 +5435,7 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="B124" t="s">
         <v>317</v>
@@ -5391,53 +5443,59 @@
       <c r="F124" s="1"/>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="9" t="s">
-        <v>497</v>
-      </c>
-      <c r="B125" s="9" t="s">
-        <v>500</v>
+      <c r="A125" t="s">
+        <v>422</v>
+      </c>
+      <c r="B125" t="s">
+        <v>317</v>
       </c>
       <c r="F125" s="1"/>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>428</v>
+        <v>423</v>
+      </c>
+      <c r="B126" t="s">
+        <v>317</v>
       </c>
       <c r="F126" s="1"/>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>429</v>
+        <v>243</v>
       </c>
       <c r="B127" t="s">
-        <v>317</v>
+        <v>521</v>
       </c>
       <c r="F127" s="1"/>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>430</v>
+        <v>424</v>
+      </c>
+      <c r="B128" t="s">
+        <v>317</v>
       </c>
       <c r="F128" s="1"/>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>431</v>
-      </c>
-      <c r="B129" t="s">
-        <v>317</v>
+        <v>425</v>
       </c>
       <c r="F129" s="1"/>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="2" t="s">
-        <v>432</v>
+      <c r="A130" t="s">
+        <v>426</v>
+      </c>
+      <c r="B130" t="s">
+        <v>317</v>
       </c>
       <c r="F130" s="1"/>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="B131" t="s">
         <v>317</v>
@@ -5446,19 +5504,22 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>434</v>
+        <v>497</v>
+      </c>
+      <c r="B132" t="s">
+        <v>500</v>
       </c>
       <c r="F132" s="1"/>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="F133" s="1"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="B134" t="s">
         <v>317</v>
@@ -5467,25 +5528,22 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>437</v>
-      </c>
-      <c r="B135" t="s">
-        <v>317</v>
+        <v>430</v>
       </c>
       <c r="F135" s="1"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>438</v>
+        <v>513</v>
       </c>
       <c r="B136" t="s">
-        <v>317</v>
+        <v>510</v>
       </c>
       <c r="F136" s="1"/>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="B137" t="s">
         <v>317</v>
@@ -5494,16 +5552,13 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>440</v>
-      </c>
-      <c r="B138" t="s">
-        <v>317</v>
+        <v>432</v>
       </c>
       <c r="F138" s="1"/>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="B139" t="s">
         <v>317</v>
@@ -5512,25 +5567,19 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>442</v>
-      </c>
-      <c r="B140" t="s">
-        <v>317</v>
+        <v>434</v>
       </c>
       <c r="F140" s="1"/>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>443</v>
-      </c>
-      <c r="B141" t="s">
-        <v>317</v>
+        <v>435</v>
       </c>
       <c r="F141" s="1"/>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="B142" t="s">
         <v>317</v>
@@ -5539,7 +5588,7 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="B143" t="s">
         <v>317</v>
@@ -5547,29 +5596,35 @@
       <c r="F143" s="1"/>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="2" t="s">
-        <v>446</v>
+      <c r="A144" t="s">
+        <v>438</v>
+      </c>
+      <c r="B144" t="s">
+        <v>317</v>
       </c>
       <c r="F144" s="1"/>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>447</v>
+        <v>509</v>
       </c>
       <c r="B145" t="s">
-        <v>317</v>
+        <v>510</v>
       </c>
       <c r="F145" s="1"/>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A146" s="2" t="s">
-        <v>448</v>
+      <c r="A146" t="s">
+        <v>439</v>
+      </c>
+      <c r="B146" t="s">
+        <v>317</v>
       </c>
       <c r="F146" s="1"/>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="B147" t="s">
         <v>317</v>
@@ -5578,104 +5633,182 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>450</v>
+        <v>514</v>
       </c>
       <c r="B148" t="s">
-        <v>317</v>
+        <v>505</v>
       </c>
       <c r="F148" s="1"/>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
+        <v>441</v>
+      </c>
+      <c r="B149" t="s">
+        <v>317</v>
+      </c>
+      <c r="F149" s="1"/>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>442</v>
+      </c>
+      <c r="B150" t="s">
+        <v>317</v>
+      </c>
+      <c r="F150" s="1"/>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>443</v>
+      </c>
+      <c r="B151" t="s">
+        <v>317</v>
+      </c>
+      <c r="F151" s="1"/>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>444</v>
+      </c>
+      <c r="B152" t="s">
+        <v>317</v>
+      </c>
+      <c r="F152" s="1"/>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>515</v>
+      </c>
+      <c r="B153" t="s">
+        <v>505</v>
+      </c>
+      <c r="F153" s="1"/>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>445</v>
+      </c>
+      <c r="B154" t="s">
+        <v>317</v>
+      </c>
+      <c r="F154" s="1"/>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>516</v>
+      </c>
+      <c r="B155" t="s">
+        <v>510</v>
+      </c>
+      <c r="F155" s="1"/>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>446</v>
+      </c>
+      <c r="F156" s="1"/>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>447</v>
+      </c>
+      <c r="B157" t="s">
+        <v>317</v>
+      </c>
+      <c r="F157" s="1"/>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>448</v>
+      </c>
+      <c r="F158" s="1"/>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>512</v>
+      </c>
+      <c r="B159" t="s">
+        <v>510</v>
+      </c>
+      <c r="F159" s="1"/>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>449</v>
+      </c>
+      <c r="B160" t="s">
+        <v>317</v>
+      </c>
+      <c r="F160" s="1"/>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>450</v>
+      </c>
+      <c r="B161" t="s">
+        <v>317</v>
+      </c>
+      <c r="F161" s="1"/>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>519</v>
+      </c>
+      <c r="B162" t="s">
+        <v>518</v>
+      </c>
+      <c r="F162" s="1"/>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
         <v>451</v>
       </c>
-      <c r="B149" t="s">
-        <v>317</v>
-      </c>
-      <c r="F149" s="1"/>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A150" s="2" t="s">
+      <c r="B163" t="s">
+        <v>317</v>
+      </c>
+      <c r="F163" s="1"/>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
         <v>452</v>
       </c>
-      <c r="F150" s="1"/>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="F151" s="1"/>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="F152" s="1"/>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="F153" s="1"/>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="F154" s="1"/>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="F155" s="1"/>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="F156" s="1"/>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="F157" s="1"/>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="F158" s="1"/>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="F159" s="1"/>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="F160" s="1"/>
-    </row>
-    <row r="161" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F161" s="1"/>
-    </row>
-    <row r="162" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F162" s="1"/>
-    </row>
-    <row r="163" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F163" s="1"/>
-    </row>
-    <row r="164" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F164" s="1"/>
     </row>
-    <row r="165" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F165" s="1"/>
     </row>
-    <row r="166" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F166" s="1"/>
     </row>
-    <row r="167" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F167" s="1"/>
     </row>
-    <row r="168" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F168" s="1"/>
     </row>
-    <row r="169" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F169" s="1"/>
     </row>
-    <row r="170" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F170" s="1"/>
     </row>
-    <row r="171" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F171" s="1"/>
     </row>
-    <row r="172" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F172" s="1"/>
     </row>
-    <row r="173" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F173" s="1"/>
     </row>
-    <row r="174" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F174" s="1"/>
     </row>
-    <row r="175" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F175" s="1"/>
     </row>
-    <row r="176" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F176" s="1"/>
     </row>
     <row r="177" spans="6:6" x14ac:dyDescent="0.3">
@@ -6426,21 +6559,32 @@
       <c r="F429" s="1"/>
     </row>
     <row r="430" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E430" s="4"/>
+      <c r="E430" s="2"/>
       <c r="F430" s="1"/>
     </row>
   </sheetData>
   <sortState ref="A1:B430">
     <sortCondition ref="A1"/>
   </sortState>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A137:A141">
     <cfRule type="duplicateValues" dxfId="3" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="2" priority="6"/>
   </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="A155" r:id="rId1" display="https://www.moneydj.com/etf/x/basic/basic0003.xdjhtm?etfid=VEGI"/>
+    <hyperlink ref="A101" r:id="rId2" display="https://www.moneydj.com/etf/x/basic/basic0003.xdjhtm?etfid=MOO"/>
+    <hyperlink ref="A48" r:id="rId3" display="https://www.moneydj.com/etf/x/basic/basic0003.xdjhtm?etfid=DBA"/>
+    <hyperlink ref="A162" r:id="rId4" display="https://www.moneydj.com/etf/x/basic/basic0003.xdjhtm?etfid=CPER"/>
+    <hyperlink ref="A73" r:id="rId5" display="https://www.moneydj.com/etf/x/basic/basic0003.xdjhtm?etfid=ICOP"/>
+    <hyperlink ref="A127" r:id="rId6" display="https://www.moneydj.com/etf/x/basic/basic0003.xdjhtm?etfid=REMX"/>
+    <hyperlink ref="A38" r:id="rId7" display="https://www.moneydj.com/etf/x/basic/basic0003.xdjhtm?etfid=COPX"/>
+    <hyperlink ref="A58" r:id="rId8" display="https://www.moneydj.com/etf/x/basic/basic0003.xdjhtm?etfid=FMTL"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId9"/>
 </worksheet>
 </file>
 
@@ -6462,7 +6606,7 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="7" t="s">
         <v>491</v>
       </c>
       <c r="H2" s="1"/>
@@ -6633,7 +6777,7 @@
       <c r="M19" s="1"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="7" t="s">
         <v>492</v>
       </c>
       <c r="H20" s="1"/>
@@ -6774,12 +6918,12 @@
       <c r="M34" s="1"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A35" s="9"/>
+      <c r="A35" s="7"/>
       <c r="H35" s="1"/>
       <c r="M35" s="1"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A36" s="9"/>
+      <c r="A36" s="7"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="J37" s="1"/>
@@ -7009,9 +7153,9 @@
     </row>
   </sheetData>
   <sortState ref="A1:B100">
-    <sortCondition ref="A22"/>
+    <sortCondition ref="A1"/>
   </sortState>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1:A33 A37:A1048576">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
